--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esolon\OneDrive - Boston Semi Equipment LLC\Github Projects\PO_Status\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519F3434-12A6-47DF-98DF-6D77C031F382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9CEBD7FEC0FBAFCEDFDF793F070D80A79" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1DB55FD-920A-4A06-8BFC-ABBEFCC9C9B3}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="PO_StatusQry" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$86</definedName>
+    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$99</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="171">
   <si>
     <t>CustName</t>
   </si>
@@ -70,10 +70,7 @@
     <t>4516351202_ASEWH</t>
   </si>
   <si>
-    <t>OverDue by 187 days</t>
-  </si>
-  <si>
-    <t>Varies (2025-08-29 → 2026-02-24)</t>
+    <t>OverDue by 255 days</t>
   </si>
   <si>
     <t>Texas Instruments SCT</t>
@@ -82,6 +79,9 @@
     <t>4516351202_SCT</t>
   </si>
   <si>
+    <t>Varies (2025-08-29 → 2026-05-13)</t>
+  </si>
+  <si>
     <t>Texas Instruments Taiwan</t>
   </si>
   <si>
@@ -94,16 +94,28 @@
     <t>4516351202_TICL-PR</t>
   </si>
   <si>
+    <t>Varies (2025-08-29 → 2026-05-11)</t>
+  </si>
+  <si>
     <t>TEXAS INSTRUMENTS  MALAYSIA</t>
   </si>
   <si>
     <t>Global PO 4516351202</t>
   </si>
   <si>
-    <t>OverDue by 121 days</t>
-  </si>
-  <si>
-    <t>Varies (2025-11-03 → 2026-02-24)</t>
+    <t>OverDue by 91 days</t>
+  </si>
+  <si>
+    <t>ASE ASSEMBLY AND TEST LIMITED</t>
+  </si>
+  <si>
+    <t>4516351202_ASESH</t>
+  </si>
+  <si>
+    <t>OverDue by 76 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-02-24 → 2026-04-08)</t>
   </si>
   <si>
     <t>TI (Philippines) Inc.</t>
@@ -112,10 +124,22 @@
     <t>4516351202_TIPI</t>
   </si>
   <si>
-    <t>OverDue by 44 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-01-19 → 2026-03-13)</t>
+    <t>OverDue by 60 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-03-12 → 2026-05-19)</t>
+  </si>
+  <si>
+    <t>ARDENTEC CORPORATION</t>
+  </si>
+  <si>
+    <t>4516351202_ARD</t>
+  </si>
+  <si>
+    <t>OverDue by 45 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-03-27 → 2026-05-19)</t>
   </si>
   <si>
     <t>Analog Devices Gen. Trias Inc. (ADGT)</t>
@@ -124,172 +148,118 @@
     <t>47270551</t>
   </si>
   <si>
-    <t>OverDue by 16 days</t>
-  </si>
-  <si>
-    <t>Hana Semiconductor (Ayutthaya) Co., Ltd (HNT)</t>
-  </si>
-  <si>
-    <t>4516351202_HNT</t>
-  </si>
-  <si>
-    <t>OverDue by 12 days</t>
-  </si>
-  <si>
-    <t>Texas Instruments AIZU</t>
-  </si>
-  <si>
-    <t>4516351202_AIZU</t>
-  </si>
-  <si>
-    <t>OverDue by 9 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-02-23 → 2026-03-05)</t>
+    <t>OverDue by 14 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-04-27 → 2026-05-13)</t>
+  </si>
+  <si>
+    <t>Lingsen Precision Industries Ltd.</t>
+  </si>
+  <si>
+    <t>4516446856</t>
+  </si>
+  <si>
+    <t>7 days before Due</t>
+  </si>
+  <si>
+    <t>NXP Malaysia Sdn. Bhd.</t>
+  </si>
+  <si>
+    <t>3T/PO262326</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
+  </si>
+  <si>
+    <t>4516351202_TII</t>
+  </si>
+  <si>
+    <t>TBA_NXP</t>
+  </si>
+  <si>
+    <t>Texas Instruments LFAB</t>
+  </si>
+  <si>
+    <t>4516351202_LFAB</t>
+  </si>
+  <si>
+    <t>ROCHESTER ELECTRONICS</t>
+  </si>
+  <si>
+    <t>252395</t>
+  </si>
+  <si>
+    <t>Texas Instruments DMOS5</t>
+  </si>
+  <si>
+    <t>4516351202_DMOS5</t>
+  </si>
+  <si>
+    <t>Completed PO</t>
+  </si>
+  <si>
+    <t>47188646</t>
+  </si>
+  <si>
+    <t>47218149</t>
+  </si>
+  <si>
+    <t>47245848</t>
+  </si>
+  <si>
+    <t>47245933</t>
+  </si>
+  <si>
+    <t>47253728</t>
+  </si>
+  <si>
+    <t>47264622</t>
+  </si>
+  <si>
+    <t>47274630</t>
+  </si>
+  <si>
+    <t>47276474</t>
+  </si>
+  <si>
+    <t>47283634</t>
+  </si>
+  <si>
+    <t>47283654</t>
+  </si>
+  <si>
+    <t>47286185</t>
+  </si>
+  <si>
+    <t>47289023</t>
+  </si>
+  <si>
+    <t>47290167</t>
+  </si>
+  <si>
+    <t>47292239</t>
+  </si>
+  <si>
+    <t>47292914</t>
+  </si>
+  <si>
+    <t>47296581</t>
+  </si>
+  <si>
+    <t>47296806</t>
   </si>
   <si>
     <t>47301012</t>
   </si>
   <si>
-    <t>19 days before Due</t>
-  </si>
-  <si>
-    <t>STMicroelectronics, Inc.</t>
-  </si>
-  <si>
-    <t>4010017970</t>
-  </si>
-  <si>
-    <t>15 days before Due</t>
-  </si>
-  <si>
-    <t>Texas Instruments LFAB</t>
-  </si>
-  <si>
-    <t>4516351202_LFAB</t>
-  </si>
-  <si>
-    <t>12 days before Due</t>
-  </si>
-  <si>
-    <t>UTAC Thai Limited ( UTL 3)</t>
-  </si>
-  <si>
-    <t>4516351202_UTL</t>
-  </si>
-  <si>
-    <t>2 days before Due</t>
-  </si>
-  <si>
-    <t>TI Philippines, Inc - Clark FT</t>
-  </si>
-  <si>
-    <t>4516351202_TICL-FT</t>
-  </si>
-  <si>
-    <t>Due Today</t>
-  </si>
-  <si>
-    <t>ARDENTEC CORPORATION</t>
-  </si>
-  <si>
-    <t>4516351202_ARD</t>
-  </si>
-  <si>
-    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
-  </si>
-  <si>
-    <t>4516351202_MIHO</t>
-  </si>
-  <si>
-    <t>Texas Instruments DMOS5</t>
-  </si>
-  <si>
-    <t>4516351202_DMOS5</t>
-  </si>
-  <si>
-    <t>NXP Malaysia Sdn. Bhd.</t>
-  </si>
-  <si>
-    <t>TBA_NXP</t>
-  </si>
-  <si>
-    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
-  </si>
-  <si>
-    <t>4516351202_TII</t>
-  </si>
-  <si>
-    <t>Texas Instruments Taiwan Limited</t>
-  </si>
-  <si>
-    <t>4516450237</t>
-  </si>
-  <si>
-    <t>ROCHESTER ELECTRONICS</t>
-  </si>
-  <si>
-    <t>252395</t>
-  </si>
-  <si>
-    <t>47188646</t>
-  </si>
-  <si>
-    <t>Completed PO</t>
-  </si>
-  <si>
-    <t>47218149</t>
-  </si>
-  <si>
-    <t>47245848</t>
-  </si>
-  <si>
-    <t>47245933</t>
-  </si>
-  <si>
-    <t>47253728</t>
-  </si>
-  <si>
-    <t>47264622</t>
-  </si>
-  <si>
-    <t>47274630</t>
-  </si>
-  <si>
-    <t>47276474</t>
-  </si>
-  <si>
-    <t>47283634</t>
-  </si>
-  <si>
-    <t>47283654</t>
-  </si>
-  <si>
-    <t>47286185</t>
-  </si>
-  <si>
-    <t>47289023</t>
-  </si>
-  <si>
-    <t>47290167</t>
-  </si>
-  <si>
-    <t>47292239</t>
-  </si>
-  <si>
-    <t>47292914</t>
-  </si>
-  <si>
-    <t>47296581</t>
-  </si>
-  <si>
-    <t>47296806</t>
-  </si>
-  <si>
     <t>47301646</t>
   </si>
   <si>
     <t>47304169</t>
+  </si>
+  <si>
+    <t>47324752</t>
   </si>
   <si>
     <t>ANALOG DEVICES INC. CAMAS</t>
@@ -311,12 +281,30 @@
     <t>8541541216</t>
   </si>
   <si>
+    <t>8541550629</t>
+  </si>
+  <si>
+    <t>8541550824</t>
+  </si>
+  <si>
+    <t>Boston Semi Equipment</t>
+  </si>
+  <si>
+    <t>TBDBSEMY</t>
+  </si>
+  <si>
     <t>Boston Semi Equipment (Thailand) Co.,Ltd.</t>
   </si>
   <si>
     <t>TBA_BSETH</t>
   </si>
   <si>
+    <t>Boston Semi Equipment Asia</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
     <t>CARDIAC PACEMAKERS INC</t>
   </si>
   <si>
@@ -332,12 +320,21 @@
     <t>7000675296</t>
   </si>
   <si>
+    <t>7000696372</t>
+  </si>
+  <si>
     <t>Hana Semiconductor (Ayutthaya) Co., Ltd</t>
   </si>
   <si>
     <t>4910173913</t>
   </si>
   <si>
+    <t>Hana Semiconductor (Ayutthaya) Co., Ltd (HNT)</t>
+  </si>
+  <si>
+    <t>4516351202_HNT</t>
+  </si>
+  <si>
     <t>4910172298</t>
   </si>
   <si>
@@ -347,15 +344,9 @@
     <t>ES072525</t>
   </si>
   <si>
-    <t>Lingsen Precision Industries Ltd.</t>
-  </si>
-  <si>
     <t>4516260169</t>
   </si>
   <si>
-    <t>4516446856</t>
-  </si>
-  <si>
     <t>LPI-2507174</t>
   </si>
   <si>
@@ -380,6 +371,21 @@
     <t>3T/PO262313</t>
   </si>
   <si>
+    <t>3T/PO262321</t>
+  </si>
+  <si>
+    <t>ON Semiconductor Philippines Inc</t>
+  </si>
+  <si>
+    <t>561000005506</t>
+  </si>
+  <si>
+    <t>Rhenus Logistics Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>TBDBSETH</t>
+  </si>
+  <si>
     <t>ST Microelectronics Pte Ltd.</t>
   </si>
   <si>
@@ -389,6 +395,9 @@
     <t>4020007647</t>
   </si>
   <si>
+    <t>STMicroelectronics, Inc.</t>
+  </si>
+  <si>
     <t>3030012690</t>
   </si>
   <si>
@@ -404,6 +413,12 @@
     <t>4010017128</t>
   </si>
   <si>
+    <t>4010017970</t>
+  </si>
+  <si>
+    <t>4010018238</t>
+  </si>
+  <si>
     <t>4330007739</t>
   </si>
   <si>
@@ -419,6 +434,12 @@
     <t>BSE-58645</t>
   </si>
   <si>
+    <t>Texas Instruments AIZU</t>
+  </si>
+  <si>
+    <t>4516351202_AIZU</t>
+  </si>
+  <si>
     <t>Texas Instruments CLAB</t>
   </si>
   <si>
@@ -458,15 +479,39 @@
     <t>4516351202_MIHO-ENG</t>
   </si>
   <si>
+    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
+  </si>
+  <si>
+    <t>4516351202_MIHO</t>
+  </si>
+  <si>
+    <t>Texas Instruments RFAB</t>
+  </si>
+  <si>
+    <t>4516351202_RFAB</t>
+  </si>
+  <si>
     <t>Texas Instruments SFAB</t>
   </si>
   <si>
     <t>4516351202_SFAB</t>
   </si>
   <si>
+    <t>Texas Instruments Taiwan Limited</t>
+  </si>
+  <si>
+    <t>4516450237</t>
+  </si>
+  <si>
     <t>4910171717</t>
   </si>
   <si>
+    <t>TI Philippines, Inc - Clark FT</t>
+  </si>
+  <si>
+    <t>4516351202_TICL-FT</t>
+  </si>
+  <si>
     <t>TKC Enterprises Inc.</t>
   </si>
   <si>
@@ -479,13 +524,19 @@
     <t>4516351202_NFME</t>
   </si>
   <si>
+    <t>UTAC Thai Limited ( UTL 3)</t>
+  </si>
+  <si>
     <t>43151446</t>
   </si>
   <si>
     <t>43156228</t>
   </si>
   <si>
-    <t>Last updated: 2026-03-04 14:06:04</t>
+    <t>4516351202_UTL</t>
+  </si>
+  <si>
+    <t>Last updated: 2026-05-11 08:55:50</t>
   </si>
 </sst>
 </file>
@@ -830,12 +881,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.5">
@@ -887,19 +938,19 @@
         <v>14</v>
       </c>
       <c r="C3">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -908,36 +959,33 @@
         <v>45898</v>
       </c>
       <c r="K3">
-        <v>-187</v>
+        <v>-255</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
       </c>
-      <c r="M3" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
       <c r="C4">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>220</v>
+        <v>259</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -946,10 +994,13 @@
         <v>45898</v>
       </c>
       <c r="K4">
-        <v>-187</v>
+        <v>-255</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
+      </c>
+      <c r="M4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.5">
@@ -960,19 +1011,19 @@
         <v>20</v>
       </c>
       <c r="C5">
-        <v>242</v>
+        <v>281</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H5">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -981,7 +1032,7 @@
         <v>45898</v>
       </c>
       <c r="K5">
-        <v>-187</v>
+        <v>-255</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -995,19 +1046,19 @@
         <v>22</v>
       </c>
       <c r="C6">
-        <v>45</v>
+        <v>156</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="H6">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1016,47 +1067,47 @@
         <v>45898</v>
       </c>
       <c r="K6">
-        <v>-187</v>
+        <v>-255</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
       </c>
+      <c r="M6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H7">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>45964</v>
+        <v>46062</v>
       </c>
       <c r="K7">
-        <v>-121</v>
+        <v>-91</v>
       </c>
       <c r="L7" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1068,28 +1119,28 @@
         <v>28</v>
       </c>
       <c r="C8">
-        <v>486</v>
+        <v>30</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>443</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J8" s="1">
-        <v>46041</v>
+        <v>46077</v>
       </c>
       <c r="K8">
-        <v>-44</v>
+        <v>-76</v>
       </c>
       <c r="L8" t="s">
         <v>29</v>
@@ -1106,302 +1157,272 @@
         <v>32</v>
       </c>
       <c r="C9">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H9">
-        <v>11</v>
+        <v>558</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>46069</v>
+        <v>46093</v>
       </c>
       <c r="K9">
-        <v>-16</v>
+        <v>-60</v>
       </c>
       <c r="L9" t="s">
         <v>33</v>
       </c>
+      <c r="M9" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10">
-        <v>19</v>
+        <v>240</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>17</v>
+        <v>191</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J10" s="1">
-        <v>46073</v>
+        <v>46108</v>
       </c>
       <c r="K10">
-        <v>-12</v>
+        <v>-45</v>
       </c>
       <c r="L10" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="M10" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C11">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>46076</v>
+        <v>46139</v>
       </c>
       <c r="K11">
-        <v>-9</v>
+        <v>-14</v>
       </c>
       <c r="L11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>46104</v>
+        <v>46160</v>
       </c>
       <c r="K12">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="L12" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>46100</v>
-      </c>
-      <c r="K13">
-        <v>15</v>
-      </c>
-      <c r="L13" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C14">
+        <v>30</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <v>2</v>
       </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
       <c r="H14">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I14">
         <v>0</v>
-      </c>
-      <c r="J14" s="1">
-        <v>46097</v>
-      </c>
-      <c r="K14">
-        <v>12</v>
-      </c>
-      <c r="L14" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
         <v>50</v>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="I15">
         <v>0</v>
-      </c>
-      <c r="J15" s="1">
-        <v>46087</v>
-      </c>
-      <c r="K15">
-        <v>2</v>
-      </c>
-      <c r="L15" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" t="s">
         <v>52</v>
       </c>
-      <c r="B16" t="s">
-        <v>53</v>
-      </c>
       <c r="C16">
-        <v>161</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="I16">
         <v>0</v>
-      </c>
-      <c r="J16" s="1">
-        <v>46085</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C17">
-        <v>164</v>
+        <v>70</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1409,13 +1430,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C18">
-        <v>123</v>
+        <v>37</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1424,24 +1445,27 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
+        <v>57</v>
       </c>
       <c r="H18">
-        <v>106</v>
+        <v>29</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C19">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1450,10 +1474,13 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>9</v>
+        <v>0</v>
+      </c>
+      <c r="G19" t="s">
+        <v>57</v>
       </c>
       <c r="H19">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1461,13 +1488,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C20">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1476,10 +1503,13 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="G20" t="s">
+        <v>57</v>
       </c>
       <c r="H20">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1487,13 +1517,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C21">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1502,10 +1532,13 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="G21" t="s">
+        <v>57</v>
       </c>
       <c r="H21">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1513,13 +1546,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1528,10 +1561,13 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="G22" t="s">
+        <v>57</v>
       </c>
       <c r="H22">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1539,25 +1575,28 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C23">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
+      <c r="G23" t="s">
+        <v>57</v>
+      </c>
       <c r="H23">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1565,13 +1604,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C24">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1583,10 +1622,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H24">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1594,13 +1633,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C25">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1612,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H25">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1623,10 +1662,10 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1641,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1652,13 +1691,13 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1670,10 +1709,10 @@
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1681,13 +1720,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1699,10 +1738,10 @@
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1710,10 +1749,10 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1728,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1739,13 +1778,13 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1757,10 +1796,10 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1768,10 +1807,10 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1786,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1797,13 +1836,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1815,10 +1854,10 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H32">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -1826,13 +1865,13 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1844,10 +1883,10 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1855,13 +1894,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1873,10 +1912,10 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -1884,10 +1923,10 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C35">
         <v>4</v>
@@ -1902,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H35">
         <v>4</v>
@@ -1913,13 +1952,13 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A36" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -1931,10 +1970,10 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1942,13 +1981,13 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A37" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -1960,10 +1999,10 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H37">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -1971,10 +2010,10 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A38" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1989,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -2000,13 +2039,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A39" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C39">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2018,10 +2057,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H39">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2029,13 +2068,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A40" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="B40" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2047,10 +2086,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2058,13 +2097,13 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A41" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="B41" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2076,10 +2115,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H41">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2087,10 +2126,10 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A42" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="B42" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -2105,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -2116,13 +2155,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2134,10 +2173,10 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2145,13 +2184,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C44">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2163,10 +2202,10 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H44">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2174,10 +2213,10 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A45" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -2192,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -2203,10 +2242,10 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A46" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -2221,7 +2260,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -2232,13 +2271,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A47" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C47">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2250,10 +2289,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H47">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2261,13 +2300,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A48" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B48" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C48">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2279,10 +2318,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H48">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2290,13 +2329,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A49" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B49" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2308,10 +2347,10 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2319,13 +2358,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A50" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B50" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2337,10 +2376,10 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2348,13 +2387,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A51" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B51" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2366,10 +2405,10 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2377,10 +2416,10 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A52" t="s">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="B52" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C52">
         <v>10</v>
@@ -2395,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H52">
         <v>10</v>
@@ -2406,13 +2445,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A53" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B53" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2424,10 +2463,10 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2435,13 +2474,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A54" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B54" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C54">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2453,10 +2492,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H54">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2464,13 +2503,13 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B55" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C55">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2482,10 +2521,10 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H55">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2493,13 +2532,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B56" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2511,10 +2550,10 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2522,13 +2561,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
-        <v>111</v>
+        <v>43</v>
       </c>
       <c r="B57" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C57">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2540,10 +2579,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H57">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2551,10 +2590,10 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
-        <v>111</v>
+        <v>43</v>
       </c>
       <c r="B58" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -2569,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H58">
         <v>1</v>
@@ -2580,13 +2619,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A59" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B59" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2598,10 +2637,10 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2609,10 +2648,10 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="B60" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -2627,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H60">
         <v>1</v>
@@ -2638,13 +2677,13 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="B61" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2656,10 +2695,10 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2667,13 +2706,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A62" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B62" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2685,10 +2724,10 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2696,13 +2735,13 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A63" t="s">
-        <v>118</v>
+        <v>46</v>
       </c>
       <c r="B63" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C63">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2714,10 +2753,10 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H63">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -2725,13 +2764,13 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A64" t="s">
-        <v>118</v>
+        <v>46</v>
       </c>
       <c r="B64" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2743,10 +2782,10 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -2754,13 +2793,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A65" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B65" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C65">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2772,10 +2811,10 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H65">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -2783,10 +2822,10 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A66" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="B66" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -2801,7 +2840,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -2812,13 +2851,13 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A67" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="B67" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2830,10 +2869,10 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -2841,13 +2880,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A68" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="B68" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2859,10 +2898,10 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H68">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -2870,13 +2909,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="B69" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2888,10 +2927,10 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -2899,13 +2938,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A70" t="s">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="B70" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C70">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -2917,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H70">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -2928,10 +2967,10 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="B71" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -2946,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -2957,13 +2996,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A72" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B72" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2975,10 +3014,10 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -2986,13 +3025,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A73" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B73" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -3004,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3015,10 +3054,10 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A74" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B74" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -3033,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H74">
         <v>1</v>
@@ -3044,10 +3083,10 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A75" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B75" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -3062,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -3073,13 +3112,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A76" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="B76" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C76">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3091,10 +3130,10 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H76">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3102,13 +3141,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A77" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="B77" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3120,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3131,13 +3170,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A78" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="B78" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3149,10 +3188,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3160,10 +3199,10 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A79" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B79" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C79">
         <v>2</v>
@@ -3178,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H79">
         <v>2</v>
@@ -3189,13 +3228,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A80" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="B80" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C80">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3207,10 +3246,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H80">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3218,13 +3257,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A81" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B81" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C81">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3236,10 +3275,10 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H81">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -3247,13 +3286,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A82" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="B82" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C82">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3265,10 +3304,10 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H82">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -3276,10 +3315,10 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B83" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -3294,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -3305,13 +3344,13 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A84" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B84" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C84">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3323,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H84">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -3334,10 +3373,10 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A85" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="B85" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -3352,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -3363,30 +3402,407 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A86" t="s">
-        <v>49</v>
+        <v>146</v>
       </c>
       <c r="B86" t="s">
+        <v>147</v>
+      </c>
+      <c r="C86">
+        <v>2</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86" t="s">
+        <v>57</v>
+      </c>
+      <c r="H86">
+        <v>2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A87" t="s">
+        <v>146</v>
+      </c>
+      <c r="B87" t="s">
+        <v>148</v>
+      </c>
+      <c r="C87">
+        <v>2</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87" t="s">
+        <v>57</v>
+      </c>
+      <c r="H87">
+        <v>2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A88" t="s">
+        <v>149</v>
+      </c>
+      <c r="B88" t="s">
+        <v>150</v>
+      </c>
+      <c r="C88">
+        <v>9</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88" t="s">
+        <v>57</v>
+      </c>
+      <c r="H88">
+        <v>9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A89" t="s">
+        <v>151</v>
+      </c>
+      <c r="B89" t="s">
         <v>152</v>
       </c>
-      <c r="C86">
-        <v>1</v>
-      </c>
-      <c r="D86">
-        <v>0</v>
-      </c>
-      <c r="E86">
-        <v>0</v>
-      </c>
-      <c r="F86">
-        <v>0</v>
-      </c>
-      <c r="G86" t="s">
-        <v>70</v>
-      </c>
-      <c r="H86">
-        <v>1</v>
-      </c>
-      <c r="I86">
+      <c r="C89">
+        <v>136</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89" t="s">
+        <v>57</v>
+      </c>
+      <c r="H89">
+        <v>136</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A90" t="s">
+        <v>153</v>
+      </c>
+      <c r="B90" t="s">
+        <v>154</v>
+      </c>
+      <c r="C90">
+        <v>2</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90" t="s">
+        <v>57</v>
+      </c>
+      <c r="H90">
+        <v>2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A91" t="s">
+        <v>155</v>
+      </c>
+      <c r="B91" t="s">
+        <v>156</v>
+      </c>
+      <c r="C91">
+        <v>9</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91" t="s">
+        <v>57</v>
+      </c>
+      <c r="H91">
+        <v>9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A92" t="s">
+        <v>157</v>
+      </c>
+      <c r="B92" t="s">
+        <v>158</v>
+      </c>
+      <c r="C92">
+        <v>16</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92" t="s">
+        <v>57</v>
+      </c>
+      <c r="H92">
+        <v>16</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A93" t="s">
+        <v>157</v>
+      </c>
+      <c r="B93" t="s">
+        <v>159</v>
+      </c>
+      <c r="C93">
+        <v>24</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93" t="s">
+        <v>57</v>
+      </c>
+      <c r="H93">
+        <v>24</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A94" t="s">
+        <v>160</v>
+      </c>
+      <c r="B94" t="s">
+        <v>161</v>
+      </c>
+      <c r="C94">
+        <v>170</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94" t="s">
+        <v>57</v>
+      </c>
+      <c r="H94">
+        <v>170</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A95" t="s">
+        <v>162</v>
+      </c>
+      <c r="B95" t="s">
+        <v>163</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95" t="s">
+        <v>57</v>
+      </c>
+      <c r="H95">
+        <v>1</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A96" t="s">
+        <v>164</v>
+      </c>
+      <c r="B96" t="s">
+        <v>165</v>
+      </c>
+      <c r="C96">
+        <v>15</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96" t="s">
+        <v>57</v>
+      </c>
+      <c r="H96">
+        <v>15</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A97" t="s">
+        <v>166</v>
+      </c>
+      <c r="B97" t="s">
+        <v>167</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97" t="s">
+        <v>57</v>
+      </c>
+      <c r="H97">
+        <v>1</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A98" t="s">
+        <v>166</v>
+      </c>
+      <c r="B98" t="s">
+        <v>168</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98" t="s">
+        <v>57</v>
+      </c>
+      <c r="H98">
+        <v>1</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A99" t="s">
+        <v>166</v>
+      </c>
+      <c r="B99" t="s">
+        <v>169</v>
+      </c>
+      <c r="C99">
+        <v>12</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99" t="s">
+        <v>57</v>
+      </c>
+      <c r="H99">
+        <v>12</v>
+      </c>
+      <c r="I99">
         <v>0</v>
       </c>
     </row>

--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9CEBD7FEC0FBAFCEDFDF793F070D80A79" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1DB55FD-920A-4A06-8BFC-ABBEFCC9C9B3}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9CFED7CC7BFBAFCDC6DF381DC71D80A79" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EEF9E45-429C-4C42-B084-F31EC0164A2F}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -190,16 +190,10 @@
     <t>252395</t>
   </si>
   <si>
-    <t>Texas Instruments DMOS5</t>
-  </si>
-  <si>
-    <t>4516351202_DMOS5</t>
+    <t>47188646</t>
   </si>
   <si>
     <t>Completed PO</t>
-  </si>
-  <si>
-    <t>47188646</t>
   </si>
   <si>
     <t>47218149</t>
@@ -458,6 +452,12 @@
     <t>4516351202_FFAB</t>
   </si>
   <si>
+    <t>Texas Instruments DMOS5</t>
+  </si>
+  <si>
+    <t>4516351202_DMOS5</t>
+  </si>
+  <si>
     <t>Texas Instruments FTLABS</t>
   </si>
   <si>
@@ -536,7 +536,7 @@
     <t>4516351202_UTL</t>
   </si>
   <si>
-    <t>Last updated: 2026-05-11 08:55:50</t>
+    <t>Last updated: 2026-05-11 09:36:59</t>
   </si>
 </sst>
 </file>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" t="s">
         <v>55</v>
       </c>
-      <c r="B18" t="s">
-        <v>56</v>
-      </c>
       <c r="C18">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1448,13 +1448,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H18">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I18">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.5">
@@ -1462,10 +1462,10 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C19">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1477,10 +1477,10 @@
         <v>0</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H19">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1491,10 +1491,10 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C20">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H20">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -1549,7 +1549,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1578,7 +1578,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -1607,7 +1607,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -1636,7 +1636,7 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -1665,10 +1665,10 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1680,10 +1680,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1694,10 +1694,10 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1709,10 +1709,10 @@
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H27">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1723,10 +1723,10 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1738,10 +1738,10 @@
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1752,10 +1752,10 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1767,10 +1767,10 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1796,10 +1796,10 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1810,10 +1810,10 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1825,10 +1825,10 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1839,10 +1839,10 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1854,10 +1854,10 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -1868,10 +1868,10 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1883,10 +1883,10 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1897,10 +1897,10 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C34">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1912,10 +1912,10 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H34">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -1926,10 +1926,10 @@
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1941,10 +1941,10 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H35">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1955,10 +1955,10 @@
         <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C36">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -1970,10 +1970,10 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H36">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1984,10 +1984,10 @@
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C37">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -1999,10 +1999,10 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H37">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2039,13 +2039,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="B39" t="s">
         <v>78</v>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2057,10 +2057,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2074,7 +2074,7 @@
         <v>80</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2086,10 +2086,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2103,7 +2103,7 @@
         <v>82</v>
       </c>
       <c r="C41">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2115,10 +2115,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H41">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2126,13 +2126,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A42" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" t="s">
         <v>83</v>
       </c>
-      <c r="B42" t="s">
-        <v>84</v>
-      </c>
       <c r="C42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2144,10 +2144,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2155,13 +2155,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2173,10 +2173,10 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2184,13 +2184,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B44" t="s">
         <v>86</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2202,10 +2202,10 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H44">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -2248,7 +2248,7 @@
         <v>90</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2260,10 +2260,10 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>92</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2289,10 +2289,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2300,13 +2300,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A48" t="s">
+        <v>91</v>
+      </c>
+      <c r="B48" t="s">
         <v>93</v>
       </c>
-      <c r="B48" t="s">
-        <v>94</v>
-      </c>
       <c r="C48">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2318,10 +2318,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H48">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2329,13 +2329,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A49" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C49">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2347,10 +2347,10 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H49">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2358,13 +2358,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A50" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B50" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2376,10 +2376,10 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2387,13 +2387,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A51" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2405,10 +2405,10 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H51">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2416,13 +2416,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A52" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B52" t="s">
         <v>98</v>
       </c>
       <c r="C52">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2434,10 +2434,10 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H52">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2451,7 +2451,7 @@
         <v>100</v>
       </c>
       <c r="C53">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2463,10 +2463,10 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H53">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2474,13 +2474,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A54" t="s">
+        <v>99</v>
+      </c>
+      <c r="B54" t="s">
         <v>101</v>
       </c>
-      <c r="B54" t="s">
-        <v>102</v>
-      </c>
       <c r="C54">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2492,10 +2492,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H54">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2503,13 +2503,13 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B55" t="s">
         <v>103</v>
       </c>
       <c r="C55">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2521,10 +2521,10 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H55">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2532,13 +2532,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
+        <v>43</v>
+      </c>
+      <c r="B56" t="s">
         <v>104</v>
       </c>
-      <c r="B56" t="s">
-        <v>105</v>
-      </c>
       <c r="C56">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2550,10 +2550,10 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H56">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2564,10 +2564,10 @@
         <v>43</v>
       </c>
       <c r="B57" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C57">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2579,10 +2579,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H57">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2590,13 +2590,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="B58" t="s">
         <v>107</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2619,13 +2619,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A59" t="s">
+        <v>106</v>
+      </c>
+      <c r="B59" t="s">
         <v>108</v>
       </c>
-      <c r="B59" t="s">
-        <v>109</v>
-      </c>
       <c r="C59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2637,10 +2637,10 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A60" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B60" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -2666,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H60">
         <v>1</v>
@@ -2677,10 +2677,10 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A61" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="B61" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -2695,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -2709,10 +2709,10 @@
         <v>46</v>
       </c>
       <c r="B62" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2724,10 +2724,10 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2738,7 +2738,7 @@
         <v>46</v>
       </c>
       <c r="B63" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C63">
         <v>3</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H63">
         <v>3</v>
@@ -2767,7 +2767,7 @@
         <v>46</v>
       </c>
       <c r="B64" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C64">
         <v>3</v>
@@ -2782,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H64">
         <v>3</v>
@@ -2793,13 +2793,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A65" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="B65" t="s">
         <v>115</v>
       </c>
       <c r="C65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2811,10 +2811,10 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -2828,7 +2828,7 @@
         <v>117</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H66">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -2857,7 +2857,7 @@
         <v>119</v>
       </c>
       <c r="C67">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2869,10 +2869,10 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H67">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -2880,13 +2880,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A68" t="s">
+        <v>118</v>
+      </c>
+      <c r="B68" t="s">
         <v>120</v>
       </c>
-      <c r="B68" t="s">
-        <v>121</v>
-      </c>
       <c r="C68">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2898,10 +2898,10 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H68">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -2909,13 +2909,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B69" t="s">
         <v>122</v>
       </c>
       <c r="C69">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2927,10 +2927,10 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H69">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -2938,13 +2938,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A70" t="s">
+        <v>121</v>
+      </c>
+      <c r="B70" t="s">
         <v>123</v>
       </c>
-      <c r="B70" t="s">
-        <v>124</v>
-      </c>
       <c r="C70">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H70">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -2967,10 +2967,10 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B71" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -2985,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A72" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B72" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -3014,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H72">
         <v>1</v>
@@ -3025,10 +3025,10 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A73" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B73" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -3043,7 +3043,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H73">
         <v>1</v>
@@ -3054,10 +3054,10 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A74" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B74" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H74">
         <v>1</v>
@@ -3083,10 +3083,10 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A75" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B75" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -3101,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -3112,13 +3112,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A76" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B76" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3130,10 +3130,10 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H76">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3141,13 +3141,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A77" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B77" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3170,13 +3170,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A78" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B78" t="s">
         <v>132</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3188,10 +3188,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3199,10 +3199,10 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A79" t="s">
+        <v>131</v>
+      </c>
+      <c r="B79" t="s">
         <v>133</v>
-      </c>
-      <c r="B79" t="s">
-        <v>134</v>
       </c>
       <c r="C79">
         <v>2</v>
@@ -3217,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H79">
         <v>2</v>
@@ -3228,13 +3228,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A80" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B80" t="s">
         <v>135</v>
       </c>
       <c r="C80">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3246,10 +3246,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H80">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3263,7 +3263,7 @@
         <v>137</v>
       </c>
       <c r="C81">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3275,10 +3275,10 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H81">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -3304,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -3321,7 +3321,7 @@
         <v>141</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -3333,10 +3333,10 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H83">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -3350,7 +3350,7 @@
         <v>143</v>
       </c>
       <c r="C84">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H84">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -3391,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -3420,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H86">
         <v>2</v>
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H87">
         <v>2</v>
@@ -3478,7 +3478,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H88">
         <v>9</v>
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H89">
         <v>136</v>
@@ -3536,7 +3536,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H90">
         <v>2</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H91">
         <v>9</v>
@@ -3594,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H92">
         <v>16</v>
@@ -3623,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H93">
         <v>24</v>
@@ -3652,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H94">
         <v>170</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -3710,7 +3710,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H96">
         <v>15</v>
@@ -3739,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -3768,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -3797,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H99">
         <v>12</v>

--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9CFED7CC7BFBAFCDC6DF381DC71D80A79" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EEF9E45-429C-4C42-B084-F31EC0164A2F}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9834DB4CCD79BE07C15F6BE2471D8047F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51BF4FE6-F5B8-49FD-B3BA-D5EBE8A2406A}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="PO_StatusQry" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$99</definedName>
+    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$101</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="173">
   <si>
     <t>CustName</t>
   </si>
@@ -70,7 +70,7 @@
     <t>4516351202_ASEWH</t>
   </si>
   <si>
-    <t>OverDue by 255 days</t>
+    <t>OverDue by 258 days</t>
   </si>
   <si>
     <t>Texas Instruments SCT</t>
@@ -94,7 +94,7 @@
     <t>4516351202_TICL-PR</t>
   </si>
   <si>
-    <t>Varies (2025-08-29 → 2026-05-11)</t>
+    <t>Varies (2025-08-29 → 2026-05-25)</t>
   </si>
   <si>
     <t>TEXAS INSTRUMENTS  MALAYSIA</t>
@@ -103,81 +103,111 @@
     <t>Global PO 4516351202</t>
   </si>
   <si>
-    <t>OverDue by 91 days</t>
-  </si>
-  <si>
-    <t>ASE ASSEMBLY AND TEST LIMITED</t>
+    <t>OverDue by 94 days</t>
+  </si>
+  <si>
+    <t>TI (Philippines) Inc.</t>
+  </si>
+  <si>
+    <t>4516351202_TIPI</t>
+  </si>
+  <si>
+    <t>OverDue by 63 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-03-12 → 2026-05-28)</t>
+  </si>
+  <si>
+    <t>ARDENTEC CORPORATION</t>
+  </si>
+  <si>
+    <t>4516351202_ARD</t>
+  </si>
+  <si>
+    <t>OverDue by 48 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-03-27 → 2026-05-19)</t>
+  </si>
+  <si>
+    <t>Analog Devices Gen. Trias Inc. (ADGT)</t>
+  </si>
+  <si>
+    <t>47270551</t>
+  </si>
+  <si>
+    <t>OverDue by 17 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-04-27 → 2026-05-13)</t>
+  </si>
+  <si>
+    <t>NXP Malaysia Sdn. Bhd.</t>
+  </si>
+  <si>
+    <t>3T/PO262326</t>
+  </si>
+  <si>
+    <t>20 days before Due</t>
+  </si>
+  <si>
+    <t>47301012</t>
+  </si>
+  <si>
+    <t>19 days before Due</t>
+  </si>
+  <si>
+    <t>Lingsen Precision Industries Ltd.</t>
+  </si>
+  <si>
+    <t>4516446856</t>
+  </si>
+  <si>
+    <t>4 days before Due</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
+  </si>
+  <si>
+    <t>4516351202_TII</t>
+  </si>
+  <si>
+    <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
   </si>
   <si>
     <t>4516351202_ASESH</t>
   </si>
   <si>
-    <t>OverDue by 76 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-02-24 → 2026-04-08)</t>
-  </si>
-  <si>
-    <t>TI (Philippines) Inc.</t>
-  </si>
-  <si>
-    <t>4516351202_TIPI</t>
-  </si>
-  <si>
-    <t>OverDue by 60 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-03-12 → 2026-05-19)</t>
-  </si>
-  <si>
-    <t>ARDENTEC CORPORATION</t>
-  </si>
-  <si>
-    <t>4516351202_ARD</t>
-  </si>
-  <si>
-    <t>OverDue by 45 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-03-27 → 2026-05-19)</t>
-  </si>
-  <si>
-    <t>Analog Devices Gen. Trias Inc. (ADGT)</t>
-  </si>
-  <si>
-    <t>47270551</t>
-  </si>
-  <si>
-    <t>OverDue by 14 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-04-27 → 2026-05-13)</t>
-  </si>
-  <si>
-    <t>Lingsen Precision Industries Ltd.</t>
-  </si>
-  <si>
-    <t>4516446856</t>
-  </si>
-  <si>
-    <t>7 days before Due</t>
-  </si>
-  <si>
-    <t>NXP Malaysia Sdn. Bhd.</t>
-  </si>
-  <si>
-    <t>3T/PO262326</t>
-  </si>
-  <si>
-    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
-  </si>
-  <si>
-    <t>4516351202_TII</t>
+    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
+  </si>
+  <si>
+    <t>4516351202_MIHO</t>
+  </si>
+  <si>
+    <t>3T/PO262331</t>
   </si>
   <si>
     <t>TBA_NXP</t>
   </si>
   <si>
+    <t>Texas Instruments AIZU</t>
+  </si>
+  <si>
+    <t>4516351202_AIZU</t>
+  </si>
+  <si>
+    <t>UTAC Thai Limited ( UTL 3)</t>
+  </si>
+  <si>
+    <t>4516351202_UTL</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS DEUTSCHLAND GMBH</t>
+  </si>
+  <si>
+    <t>4516351202_FFAB</t>
+  </si>
+  <si>
     <t>Texas Instruments LFAB</t>
   </si>
   <si>
@@ -190,12 +220,15 @@
     <t>252395</t>
   </si>
   <si>
+    <t>47343540</t>
+  </si>
+  <si>
+    <t>Completed PO</t>
+  </si>
+  <si>
     <t>47188646</t>
   </si>
   <si>
-    <t>Completed PO</t>
-  </si>
-  <si>
     <t>47218149</t>
   </si>
   <si>
@@ -242,9 +275,6 @@
   </si>
   <si>
     <t>47296806</t>
-  </si>
-  <si>
-    <t>47301012</t>
   </si>
   <si>
     <t>47301646</t>
@@ -428,12 +458,6 @@
     <t>BSE-58645</t>
   </si>
   <si>
-    <t>Texas Instruments AIZU</t>
-  </si>
-  <si>
-    <t>4516351202_AIZU</t>
-  </si>
-  <si>
     <t>Texas Instruments CLAB</t>
   </si>
   <si>
@@ -446,12 +470,6 @@
     <t>4516351202_TMX</t>
   </si>
   <si>
-    <t>TEXAS INSTRUMENTS DEUTSCHLAND GMBH</t>
-  </si>
-  <si>
-    <t>4516351202_FFAB</t>
-  </si>
-  <si>
     <t>Texas Instruments DMOS5</t>
   </si>
   <si>
@@ -479,12 +497,6 @@
     <t>4516351202_MIHO-ENG</t>
   </si>
   <si>
-    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
-  </si>
-  <si>
-    <t>4516351202_MIHO</t>
-  </si>
-  <si>
     <t>Texas Instruments RFAB</t>
   </si>
   <si>
@@ -524,19 +536,13 @@
     <t>4516351202_NFME</t>
   </si>
   <si>
-    <t>UTAC Thai Limited ( UTL 3)</t>
-  </si>
-  <si>
     <t>43151446</t>
   </si>
   <si>
     <t>43156228</t>
   </si>
   <si>
-    <t>4516351202_UTL</t>
-  </si>
-  <si>
-    <t>Last updated: 2026-05-11 09:36:59</t>
+    <t>Last updated: 2026-05-14 12:43:45</t>
   </si>
 </sst>
 </file>
@@ -881,12 +887,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M99"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.5">
@@ -959,7 +965,7 @@
         <v>45898</v>
       </c>
       <c r="K3">
-        <v>-255</v>
+        <v>-258</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -979,13 +985,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -994,7 +1000,7 @@
         <v>45898</v>
       </c>
       <c r="K4">
-        <v>-255</v>
+        <v>-258</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -1032,7 +1038,7 @@
         <v>45898</v>
       </c>
       <c r="K5">
-        <v>-255</v>
+        <v>-258</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -1049,16 +1055,16 @@
         <v>156</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="H6">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1067,7 +1073,7 @@
         <v>45898</v>
       </c>
       <c r="K6">
-        <v>-255</v>
+        <v>-258</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -1093,10 +1099,10 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1105,7 +1111,7 @@
         <v>46062</v>
       </c>
       <c r="K7">
-        <v>-91</v>
+        <v>-94</v>
       </c>
       <c r="L7" t="s">
         <v>26</v>
@@ -1119,28 +1125,28 @@
         <v>28</v>
       </c>
       <c r="C8">
-        <v>30</v>
+        <v>606</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>562</v>
       </c>
       <c r="I8">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>46077</v>
+        <v>46093</v>
       </c>
       <c r="K8">
-        <v>-76</v>
+        <v>-63</v>
       </c>
       <c r="L8" t="s">
         <v>29</v>
@@ -1157,28 +1163,28 @@
         <v>32</v>
       </c>
       <c r="C9">
-        <v>586</v>
+        <v>259</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H9">
-        <v>558</v>
+        <v>221</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>46093</v>
+        <v>46108</v>
       </c>
       <c r="K9">
-        <v>-60</v>
+        <v>-48</v>
       </c>
       <c r="L9" t="s">
         <v>33</v>
@@ -1195,28 +1201,28 @@
         <v>36</v>
       </c>
       <c r="C10">
-        <v>240</v>
+        <v>42</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>191</v>
+        <v>27</v>
       </c>
       <c r="I10">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>46108</v>
+        <v>46139</v>
       </c>
       <c r="K10">
-        <v>-45</v>
+        <v>-17</v>
       </c>
       <c r="L10" t="s">
         <v>37</v>
@@ -1233,106 +1239,112 @@
         <v>40</v>
       </c>
       <c r="C11">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>46139</v>
+        <v>46176</v>
       </c>
       <c r="K11">
-        <v>-14</v>
+        <v>20</v>
       </c>
       <c r="L11" t="s">
         <v>41</v>
       </c>
-      <c r="M11" t="s">
-        <v>42</v>
-      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12">
+        <v>13</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>11</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>46175</v>
+      </c>
+      <c r="K12">
+        <v>19</v>
+      </c>
+      <c r="L12" t="s">
         <v>43</v>
-      </c>
-      <c r="B12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12">
-        <v>18</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>3</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>14</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>46160</v>
-      </c>
-      <c r="K12">
-        <v>7</v>
-      </c>
-      <c r="L12" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13">
+        <v>19</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>18</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>46160</v>
+      </c>
+      <c r="K13">
+        <v>4</v>
+      </c>
+      <c r="L13" t="s">
         <v>46</v>
-      </c>
-      <c r="B13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>3</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
         <v>48</v>
       </c>
-      <c r="B14" t="s">
-        <v>49</v>
-      </c>
       <c r="C14">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1341,7 +1353,7 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H14">
         <v>28</v>
@@ -1352,13 +1364,13 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
         <v>50</v>
       </c>
       <c r="C15">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1367,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H15">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1384,7 +1396,7 @@
         <v>52</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1393,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1404,25 +1416,25 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
         <v>53</v>
       </c>
-      <c r="B17" t="s">
-        <v>54</v>
-      </c>
       <c r="C17">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H17">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1433,10 +1445,10 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C18">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1445,13 +1457,10 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="H18">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1459,13 +1468,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C19">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1474,13 +1483,10 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="H19">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1488,13 +1494,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B20" t="s">
         <v>58</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1503,13 +1509,10 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1517,13 +1520,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1532,13 +1535,10 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1546,13 +1546,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1561,10 +1561,7 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1575,28 +1572,25 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
-      <c r="G23" t="s">
-        <v>56</v>
-      </c>
       <c r="H23">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1604,16 +1598,16 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1622,10 +1616,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1633,13 +1627,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1651,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1662,13 +1656,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1680,10 +1674,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H26">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1691,13 +1685,13 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1709,10 +1703,10 @@
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1720,10 +1714,10 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1738,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1749,13 +1743,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1767,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1778,10 +1772,10 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1796,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1807,13 +1801,13 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1825,10 +1819,10 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1836,10 +1830,10 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1854,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -1865,13 +1859,13 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C33">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1883,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H33">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1894,13 +1888,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C34">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1912,10 +1906,10 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H34">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -1923,13 +1917,13 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C35">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1941,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H35">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1952,13 +1946,13 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -1970,10 +1964,10 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1981,10 +1975,10 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -1999,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -2010,13 +2004,13 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2028,10 +2022,10 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2039,10 +2033,10 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -2057,7 +2051,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -2068,13 +2062,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A40" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C40">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2086,10 +2080,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H40">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2097,13 +2091,13 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A41" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2115,10 +2109,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2126,13 +2120,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A42" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2144,10 +2138,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H42">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2155,13 +2149,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C43">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2173,10 +2167,10 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H43">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2184,13 +2178,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="B44" t="s">
         <v>86</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2202,10 +2196,10 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2231,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -2248,7 +2242,7 @@
         <v>90</v>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2260,10 +2254,10 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2277,7 +2271,7 @@
         <v>92</v>
       </c>
       <c r="C47">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2289,10 +2283,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H47">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2306,7 +2300,7 @@
         <v>93</v>
       </c>
       <c r="C48">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2318,10 +2312,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H48">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2335,7 +2329,7 @@
         <v>94</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2347,10 +2341,10 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2358,13 +2352,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A50" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2376,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2387,13 +2381,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A51" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B51" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C51">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2405,10 +2399,10 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H51">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2416,13 +2410,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A52" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B52" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C52">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2434,10 +2428,10 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H52">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2445,13 +2439,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A53" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B53" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C53">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2463,10 +2457,10 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H53">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2474,13 +2468,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B54" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C54">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2492,10 +2486,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H54">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2503,13 +2497,13 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B55" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2521,10 +2515,10 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2532,13 +2526,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="B56" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C56">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2550,10 +2544,10 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H56">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2561,13 +2555,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="B57" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2579,10 +2573,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2590,13 +2584,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B58" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C58">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2608,10 +2602,10 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H58">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2619,13 +2613,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A59" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B59" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2637,10 +2631,10 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2648,13 +2642,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A60" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B60" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2666,10 +2660,10 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2677,13 +2671,13 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A61" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="B61" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2695,10 +2689,10 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2706,13 +2700,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A62" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B62" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C62">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2724,10 +2718,10 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H62">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2735,13 +2729,13 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A63" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B63" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2753,10 +2747,10 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -2764,10 +2758,10 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A64" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="B64" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C64">
         <v>3</v>
@@ -2782,7 +2776,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H64">
         <v>3</v>
@@ -2793,10 +2787,10 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A65" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B65" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -2811,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -2825,10 +2819,10 @@
         <v>116</v>
       </c>
       <c r="B66" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C66">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2840,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H66">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -2851,13 +2845,13 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A67" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="B67" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C67">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2869,10 +2863,10 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H67">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -2880,13 +2874,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="B68" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2898,10 +2892,10 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -2909,13 +2903,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="B69" t="s">
         <v>122</v>
       </c>
       <c r="C69">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2927,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H69">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -2938,13 +2932,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A70" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="B70" t="s">
         <v>123</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -2956,10 +2950,10 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -2967,10 +2961,10 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B71" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -2985,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -2996,13 +2990,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A72" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B72" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3014,10 +3008,10 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3025,13 +3019,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A73" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B73" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -3043,10 +3037,10 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3054,13 +3048,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A74" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B74" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3072,10 +3066,10 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H74">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3083,13 +3077,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A75" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B75" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -3101,10 +3095,10 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H75">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3112,13 +3106,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A76" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B76" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3130,10 +3124,10 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3141,10 +3135,10 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A77" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B77" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -3159,7 +3153,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H77">
         <v>1</v>
@@ -3173,10 +3167,10 @@
         <v>131</v>
       </c>
       <c r="B78" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3188,10 +3182,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3202,10 +3196,10 @@
         <v>131</v>
       </c>
       <c r="B79" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3217,10 +3211,10 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3228,13 +3222,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A80" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B80" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C80">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3246,10 +3240,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H80">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3257,10 +3251,10 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A81" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B81" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -3275,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -3286,13 +3280,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A82" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B82" t="s">
         <v>139</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3304,10 +3298,10 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H82">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -3315,13 +3309,13 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
+        <v>131</v>
+      </c>
+      <c r="B83" t="s">
         <v>140</v>
       </c>
-      <c r="B83" t="s">
-        <v>141</v>
-      </c>
       <c r="C83">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -3333,10 +3327,10 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H83">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -3344,13 +3338,13 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A84" t="s">
+        <v>141</v>
+      </c>
+      <c r="B84" t="s">
         <v>142</v>
       </c>
-      <c r="B84" t="s">
-        <v>143</v>
-      </c>
       <c r="C84">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3362,10 +3356,10 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H84">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -3373,13 +3367,13 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A85" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B85" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3391,10 +3385,10 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -3402,13 +3396,13 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A86" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B86" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -3420,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -3434,10 +3428,10 @@
         <v>146</v>
       </c>
       <c r="B87" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -3449,10 +3443,10 @@
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -3460,13 +3454,13 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A88" t="s">
+        <v>148</v>
+      </c>
+      <c r="B88" t="s">
         <v>149</v>
       </c>
-      <c r="B88" t="s">
-        <v>150</v>
-      </c>
       <c r="C88">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3478,10 +3472,10 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H88">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -3489,13 +3483,13 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A89" t="s">
+        <v>150</v>
+      </c>
+      <c r="B89" t="s">
         <v>151</v>
       </c>
-      <c r="B89" t="s">
-        <v>152</v>
-      </c>
       <c r="C89">
-        <v>136</v>
+        <v>1</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3507,10 +3501,10 @@
         <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H89">
-        <v>136</v>
+        <v>1</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -3518,10 +3512,10 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A90" t="s">
+        <v>152</v>
+      </c>
+      <c r="B90" t="s">
         <v>153</v>
-      </c>
-      <c r="B90" t="s">
-        <v>154</v>
       </c>
       <c r="C90">
         <v>2</v>
@@ -3536,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H90">
         <v>2</v>
@@ -3547,13 +3541,13 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A91" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B91" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C91">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3565,10 +3559,10 @@
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H91">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -3576,13 +3570,13 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A92" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B92" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C92">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3594,10 +3588,10 @@
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H92">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -3608,10 +3602,10 @@
         <v>157</v>
       </c>
       <c r="B93" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C93">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3623,10 +3617,10 @@
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H93">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -3634,13 +3628,13 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A94" t="s">
+        <v>159</v>
+      </c>
+      <c r="B94" t="s">
         <v>160</v>
       </c>
-      <c r="B94" t="s">
-        <v>161</v>
-      </c>
       <c r="C94">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3652,10 +3646,10 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H94">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -3663,13 +3657,13 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A95" t="s">
+        <v>161</v>
+      </c>
+      <c r="B95" t="s">
         <v>162</v>
       </c>
-      <c r="B95" t="s">
-        <v>163</v>
-      </c>
       <c r="C95">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3681,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H95">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -3692,13 +3686,13 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A96" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B96" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C96">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3710,10 +3704,10 @@
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H96">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -3721,13 +3715,13 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A97" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B97" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3739,10 +3733,10 @@
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H97">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -3753,7 +3747,7 @@
         <v>166</v>
       </c>
       <c r="B98" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -3768,7 +3762,7 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -3779,13 +3773,13 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A99" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B99" t="s">
         <v>169</v>
       </c>
       <c r="C99">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3797,12 +3791,70 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H99">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A100" t="s">
+        <v>57</v>
+      </c>
+      <c r="B100" t="s">
+        <v>170</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100" t="s">
+        <v>66</v>
+      </c>
+      <c r="H100">
+        <v>1</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A101" t="s">
+        <v>57</v>
+      </c>
+      <c r="B101" t="s">
+        <v>171</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101" t="s">
+        <v>66</v>
+      </c>
+      <c r="H101">
+        <v>1</v>
+      </c>
+      <c r="I101">
         <v>0</v>
       </c>
     </row>

--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9834DB4CCD79BE07C15F6BE2471D8047F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51BF4FE6-F5B8-49FD-B3BA-D5EBE8A2406A}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9481575C3119BE0E35D3296EA70D8053E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28517752-7743-4F0B-A2AD-2BFACF76AE9B}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="173">
   <si>
     <t>CustName</t>
   </si>
@@ -70,7 +70,7 @@
     <t>4516351202_ASEWH</t>
   </si>
   <si>
-    <t>OverDue by 258 days</t>
+    <t>OverDue by 263 days</t>
   </si>
   <si>
     <t>Texas Instruments SCT</t>
@@ -103,7 +103,7 @@
     <t>Global PO 4516351202</t>
   </si>
   <si>
-    <t>OverDue by 94 days</t>
+    <t>OverDue by 99 days</t>
   </si>
   <si>
     <t>TI (Philippines) Inc.</t>
@@ -112,7 +112,7 @@
     <t>4516351202_TIPI</t>
   </si>
   <si>
-    <t>OverDue by 63 days</t>
+    <t>OverDue by 68 days</t>
   </si>
   <si>
     <t>Varies (2026-03-12 → 2026-05-28)</t>
@@ -124,7 +124,7 @@
     <t>4516351202_ARD</t>
   </si>
   <si>
-    <t>OverDue by 48 days</t>
+    <t>OverDue by 53 days</t>
   </si>
   <si>
     <t>Varies (2026-03-27 → 2026-05-19)</t>
@@ -136,7 +136,7 @@
     <t>47270551</t>
   </si>
   <si>
-    <t>OverDue by 17 days</t>
+    <t>OverDue by 22 days</t>
   </si>
   <si>
     <t>Varies (2026-04-27 → 2026-05-13)</t>
@@ -145,85 +145,76 @@
     <t>NXP Malaysia Sdn. Bhd.</t>
   </si>
   <si>
-    <t>3T/PO262326</t>
-  </si>
-  <si>
-    <t>20 days before Due</t>
+    <t>TBA_NXP</t>
+  </si>
+  <si>
+    <t>16 days before Due</t>
+  </si>
+  <si>
+    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
+  </si>
+  <si>
+    <t>4516351202_MIHO</t>
+  </si>
+  <si>
+    <t>14 days before Due</t>
+  </si>
+  <si>
+    <t>Texas Instruments AIZU</t>
+  </si>
+  <si>
+    <t>4516351202_AIZU</t>
+  </si>
+  <si>
+    <t>13 days before Due</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
+  </si>
+  <si>
+    <t>4516351202_TII</t>
+  </si>
+  <si>
+    <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
+  </si>
+  <si>
+    <t>4516351202_ASESH</t>
+  </si>
+  <si>
+    <t>3T/PO262331</t>
+  </si>
+  <si>
+    <t>UTAC Thai Limited ( UTL 3)</t>
+  </si>
+  <si>
+    <t>4516351202_UTL</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS DEUTSCHLAND GMBH</t>
+  </si>
+  <si>
+    <t>4516351202_FFAB</t>
+  </si>
+  <si>
+    <t>Texas Instruments LFAB</t>
+  </si>
+  <si>
+    <t>4516351202_LFAB</t>
+  </si>
+  <si>
+    <t>ROCHESTER ELECTRONICS</t>
+  </si>
+  <si>
+    <t>252395</t>
   </si>
   <si>
     <t>47301012</t>
   </si>
   <si>
-    <t>19 days before Due</t>
-  </si>
-  <si>
-    <t>Lingsen Precision Industries Ltd.</t>
-  </si>
-  <si>
-    <t>4516446856</t>
-  </si>
-  <si>
-    <t>4 days before Due</t>
-  </si>
-  <si>
-    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
-  </si>
-  <si>
-    <t>4516351202_TII</t>
-  </si>
-  <si>
-    <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
-  </si>
-  <si>
-    <t>4516351202_ASESH</t>
-  </si>
-  <si>
-    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
-  </si>
-  <si>
-    <t>4516351202_MIHO</t>
-  </si>
-  <si>
-    <t>3T/PO262331</t>
-  </si>
-  <si>
-    <t>TBA_NXP</t>
-  </si>
-  <si>
-    <t>Texas Instruments AIZU</t>
-  </si>
-  <si>
-    <t>4516351202_AIZU</t>
-  </si>
-  <si>
-    <t>UTAC Thai Limited ( UTL 3)</t>
-  </si>
-  <si>
-    <t>4516351202_UTL</t>
-  </si>
-  <si>
-    <t>TEXAS INSTRUMENTS DEUTSCHLAND GMBH</t>
-  </si>
-  <si>
-    <t>4516351202_FFAB</t>
-  </si>
-  <si>
-    <t>Texas Instruments LFAB</t>
-  </si>
-  <si>
-    <t>4516351202_LFAB</t>
-  </si>
-  <si>
-    <t>ROCHESTER ELECTRONICS</t>
-  </si>
-  <si>
-    <t>252395</t>
+    <t>Completed PO</t>
   </si>
   <si>
     <t>47343540</t>
-  </si>
-  <si>
-    <t>Completed PO</t>
   </si>
   <si>
     <t>47188646</t>
@@ -368,9 +359,15 @@
     <t>ES072525</t>
   </si>
   <si>
+    <t>Lingsen Precision Industries Ltd.</t>
+  </si>
+  <si>
     <t>4516260169</t>
   </si>
   <si>
+    <t>4516446856</t>
+  </si>
+  <si>
     <t>LPI-2507174</t>
   </si>
   <si>
@@ -398,6 +395,9 @@
     <t>3T/PO262321</t>
   </si>
   <si>
+    <t>3T/PO262326</t>
+  </si>
+  <si>
     <t>ON Semiconductor Philippines Inc</t>
   </si>
   <si>
@@ -542,7 +542,7 @@
     <t>43156228</t>
   </si>
   <si>
-    <t>Last updated: 2026-05-14 12:43:45</t>
+    <t>Last updated: 2026-05-19 10:00:22</t>
   </si>
 </sst>
 </file>
@@ -965,7 +965,7 @@
         <v>45898</v>
       </c>
       <c r="K3">
-        <v>-258</v>
+        <v>-263</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -982,10 +982,10 @@
         <v>270</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1000,7 +1000,7 @@
         <v>45898</v>
       </c>
       <c r="K4">
-        <v>-258</v>
+        <v>-263</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -1038,7 +1038,7 @@
         <v>45898</v>
       </c>
       <c r="K5">
-        <v>-258</v>
+        <v>-263</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -1055,10 +1055,10 @@
         <v>156</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -1073,7 +1073,7 @@
         <v>45898</v>
       </c>
       <c r="K6">
-        <v>-258</v>
+        <v>-263</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -1090,7 +1090,7 @@
         <v>25</v>
       </c>
       <c r="C7">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1099,7 +1099,7 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H7">
         <v>175</v>
@@ -1111,7 +1111,7 @@
         <v>46062</v>
       </c>
       <c r="K7">
-        <v>-94</v>
+        <v>-99</v>
       </c>
       <c r="L7" t="s">
         <v>26</v>
@@ -1128,10 +1128,10 @@
         <v>606</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F8">
         <v>20</v>
@@ -1146,7 +1146,7 @@
         <v>46093</v>
       </c>
       <c r="K8">
-        <v>-63</v>
+        <v>-68</v>
       </c>
       <c r="L8" t="s">
         <v>29</v>
@@ -1184,7 +1184,7 @@
         <v>46108</v>
       </c>
       <c r="K9">
-        <v>-48</v>
+        <v>-53</v>
       </c>
       <c r="L9" t="s">
         <v>33</v>
@@ -1222,7 +1222,7 @@
         <v>46139</v>
       </c>
       <c r="K10">
-        <v>-17</v>
+        <v>-22</v>
       </c>
       <c r="L10" t="s">
         <v>37</v>
@@ -1239,28 +1239,28 @@
         <v>40</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="K11">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L11" t="s">
         <v>41</v>
@@ -1268,25 +1268,25 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1295,53 +1295,53 @@
         <v>46175</v>
       </c>
       <c r="K12">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13">
         <v>45</v>
       </c>
-      <c r="C13">
-        <v>19</v>
-      </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="K13">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C14">
         <v>50</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15">
         <v>50</v>
@@ -1390,13 +1390,13 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
         <v>52</v>
       </c>
       <c r="C16">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1405,10 +1405,10 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H16">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1416,13 +1416,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1431,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1442,13 +1442,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C18">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1457,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1468,13 +1468,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C19">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1483,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1494,25 +1494,25 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C20">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1520,25 +1520,28 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G21" t="s">
+        <v>62</v>
       </c>
       <c r="H21">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1546,25 +1549,28 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G22" t="s">
+        <v>62</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1572,25 +1578,28 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
         <v>64</v>
       </c>
       <c r="C23">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
+      <c r="G23" t="s">
+        <v>62</v>
+      </c>
       <c r="H23">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1604,10 +1613,10 @@
         <v>65</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1616,10 +1625,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1630,10 +1639,10 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C25">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1645,10 +1654,10 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H25">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1659,10 +1668,10 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C26">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1674,10 +1683,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H26">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1688,7 +1697,7 @@
         <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1703,7 +1712,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -1717,7 +1726,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1732,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1746,7 +1755,7 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1761,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1775,7 +1784,7 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1790,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1804,10 +1813,10 @@
         <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1819,10 +1828,10 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1833,10 +1842,10 @@
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1848,10 +1857,10 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -1862,10 +1871,10 @@
         <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1877,10 +1886,10 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H33">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1891,10 +1900,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1906,10 +1915,10 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -1920,7 +1929,7 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -1935,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -1949,10 +1958,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -1964,10 +1973,10 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1978,7 +1987,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -1993,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -2007,10 +2016,10 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2022,10 +2031,10 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2036,10 +2045,10 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2051,10 +2060,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2065,10 +2074,10 @@
         <v>35</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C40">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2080,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H40">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2094,10 +2103,10 @@
         <v>35</v>
       </c>
       <c r="B41" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2109,10 +2118,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2123,10 +2132,10 @@
         <v>35</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2138,10 +2147,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2149,7 +2158,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="B43" t="s">
         <v>85</v>
@@ -2167,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -2178,13 +2187,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="B44" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C44">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2196,10 +2205,10 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H44">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2207,10 +2216,10 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A45" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B45" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -2225,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -2236,13 +2245,13 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B46" t="s">
         <v>90</v>
       </c>
       <c r="C46">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2254,10 +2263,10 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H46">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2265,13 +2274,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A47" t="s">
+        <v>88</v>
+      </c>
+      <c r="B47" t="s">
         <v>91</v>
       </c>
-      <c r="B47" t="s">
-        <v>92</v>
-      </c>
       <c r="C47">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2283,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2294,13 +2303,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A48" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B48" t="s">
         <v>93</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2312,10 +2321,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2323,13 +2332,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A49" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B49" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2341,10 +2350,10 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H49">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2352,13 +2361,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2370,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2381,13 +2390,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2399,10 +2408,10 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2410,13 +2419,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B52" t="s">
         <v>100</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2428,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H52">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2439,13 +2448,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A53" t="s">
+        <v>98</v>
+      </c>
+      <c r="B53" t="s">
         <v>101</v>
       </c>
-      <c r="B53" t="s">
-        <v>102</v>
-      </c>
       <c r="C53">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2457,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H53">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2468,13 +2477,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A54" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C54">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2486,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H54">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2497,13 +2506,13 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B55" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2515,10 +2524,10 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2526,13 +2535,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B56" t="s">
         <v>105</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2544,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H56">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2555,13 +2564,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B57" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C57">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2573,10 +2582,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H57">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2584,13 +2593,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B58" t="s">
         <v>108</v>
       </c>
       <c r="C58">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2602,10 +2611,10 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H58">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2619,7 +2628,7 @@
         <v>110</v>
       </c>
       <c r="C59">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2631,10 +2640,10 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H59">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2642,13 +2651,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A60" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B60" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C60">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2660,10 +2669,10 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H60">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2671,13 +2680,13 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A61" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B61" t="s">
         <v>113</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2689,10 +2698,10 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H61">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2700,13 +2709,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A62" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="B62" t="s">
         <v>114</v>
       </c>
       <c r="C62">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2718,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H62">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2729,13 +2738,13 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A63" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="B63" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2747,10 +2756,10 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -2758,13 +2767,13 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A64" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B64" t="s">
         <v>117</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2776,10 +2785,10 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -2787,7 +2796,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A65" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B65" t="s">
         <v>118</v>
@@ -2805,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -2816,7 +2825,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="B66" t="s">
         <v>119</v>
@@ -2834,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -2851,7 +2860,7 @@
         <v>120</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2863,10 +2872,10 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -2892,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H68">
         <v>3</v>
@@ -2921,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H69">
         <v>3</v>
@@ -2950,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H70">
         <v>3</v>
@@ -2979,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -3008,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H72">
         <v>8</v>
@@ -3037,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H73">
         <v>11</v>
@@ -3066,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H74">
         <v>5</v>
@@ -3095,7 +3104,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H75">
         <v>21</v>
@@ -3124,7 +3133,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H76">
         <v>1</v>
@@ -3153,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H77">
         <v>1</v>
@@ -3182,7 +3191,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -3211,7 +3220,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -3240,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -3269,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -3298,7 +3307,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H82">
         <v>4</v>
@@ -3327,7 +3336,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -3356,7 +3365,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H84">
         <v>2</v>
@@ -3385,7 +3394,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H85">
         <v>2</v>
@@ -3414,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -3443,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H87">
         <v>1</v>
@@ -3472,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H88">
         <v>37</v>
@@ -3501,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H89">
         <v>1</v>
@@ -3530,7 +3539,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H90">
         <v>2</v>
@@ -3559,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H91">
         <v>2</v>
@@ -3588,7 +3597,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H92">
         <v>9</v>
@@ -3617,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H93">
         <v>2</v>
@@ -3646,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H94">
         <v>9</v>
@@ -3675,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H95">
         <v>16</v>
@@ -3704,7 +3713,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H96">
         <v>24</v>
@@ -3733,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H97">
         <v>170</v>
@@ -3762,7 +3771,7 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -3791,7 +3800,7 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H99">
         <v>15</v>
@@ -3802,7 +3811,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A100" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B100" t="s">
         <v>170</v>
@@ -3820,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -3831,7 +3840,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A101" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B101" t="s">
         <v>171</v>
@@ -3849,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H101">
         <v>1</v>

--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9481575C3119BE0E35D3296EA70D8053E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28517752-7743-4F0B-A2AD-2BFACF76AE9B}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9989577BD439AFF9D7577B84E70D80274" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6CFDA32-1E19-420D-860E-DF638B98A1D2}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="PO_StatusQry" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$101</definedName>
+    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$104</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="177">
   <si>
     <t>CustName</t>
   </si>
@@ -70,7 +70,7 @@
     <t>4516351202_ASEWH</t>
   </si>
   <si>
-    <t>OverDue by 263 days</t>
+    <t>OverDue by 264 days</t>
   </si>
   <si>
     <t>Texas Instruments SCT</t>
@@ -79,7 +79,7 @@
     <t>4516351202_SCT</t>
   </si>
   <si>
-    <t>Varies (2025-08-29 → 2026-05-13)</t>
+    <t>Varies (2025-08-29 → 2026-04-21)</t>
   </si>
   <si>
     <t>Texas Instruments Taiwan</t>
@@ -103,7 +103,7 @@
     <t>Global PO 4516351202</t>
   </si>
   <si>
-    <t>OverDue by 99 days</t>
+    <t>OverDue by 100 days</t>
   </si>
   <si>
     <t>TI (Philippines) Inc.</t>
@@ -112,7 +112,7 @@
     <t>4516351202_TIPI</t>
   </si>
   <si>
-    <t>OverDue by 68 days</t>
+    <t>OverDue by 69 days</t>
   </si>
   <si>
     <t>Varies (2026-03-12 → 2026-05-28)</t>
@@ -124,7 +124,7 @@
     <t>4516351202_ARD</t>
   </si>
   <si>
-    <t>OverDue by 53 days</t>
+    <t>OverDue by 54 days</t>
   </si>
   <si>
     <t>Varies (2026-03-27 → 2026-05-19)</t>
@@ -136,19 +136,28 @@
     <t>47270551</t>
   </si>
   <si>
-    <t>OverDue by 22 days</t>
+    <t>OverDue by 23 days</t>
   </si>
   <si>
     <t>Varies (2026-04-27 → 2026-05-13)</t>
   </si>
   <si>
+    <t>47318424</t>
+  </si>
+  <si>
+    <t>20 days before Due</t>
+  </si>
+  <si>
     <t>NXP Malaysia Sdn. Bhd.</t>
   </si>
   <si>
+    <t>3T/PO262331</t>
+  </si>
+  <si>
     <t>TBA_NXP</t>
   </si>
   <si>
-    <t>16 days before Due</t>
+    <t>15 days before Due</t>
   </si>
   <si>
     <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
@@ -157,7 +166,7 @@
     <t>4516351202_MIHO</t>
   </si>
   <si>
-    <t>14 days before Due</t>
+    <t>13 days before Due</t>
   </si>
   <si>
     <t>Texas Instruments AIZU</t>
@@ -166,7 +175,7 @@
     <t>4516351202_AIZU</t>
   </si>
   <si>
-    <t>13 days before Due</t>
+    <t>12 days before Due</t>
   </si>
   <si>
     <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
@@ -181,15 +190,18 @@
     <t>4516351202_ASESH</t>
   </si>
   <si>
-    <t>3T/PO262331</t>
-  </si>
-  <si>
     <t>UTAC Thai Limited ( UTL 3)</t>
   </si>
   <si>
     <t>4516351202_UTL</t>
   </si>
   <si>
+    <t>STMicroelectronics, Inc.</t>
+  </si>
+  <si>
+    <t>4010018600</t>
+  </si>
+  <si>
     <t>TEXAS INSTRUMENTS DEUTSCHLAND GMBH</t>
   </si>
   <si>
@@ -202,70 +214,73 @@
     <t>4516351202_LFAB</t>
   </si>
   <si>
+    <t>47345978</t>
+  </si>
+  <si>
     <t>ROCHESTER ELECTRONICS</t>
   </si>
   <si>
     <t>252395</t>
   </si>
   <si>
+    <t>47343540</t>
+  </si>
+  <si>
+    <t>Completed PO</t>
+  </si>
+  <si>
+    <t>47188646</t>
+  </si>
+  <si>
+    <t>47218149</t>
+  </si>
+  <si>
+    <t>47245848</t>
+  </si>
+  <si>
+    <t>47245933</t>
+  </si>
+  <si>
+    <t>47253728</t>
+  </si>
+  <si>
+    <t>47264622</t>
+  </si>
+  <si>
+    <t>47274630</t>
+  </si>
+  <si>
+    <t>47276474</t>
+  </si>
+  <si>
+    <t>47283634</t>
+  </si>
+  <si>
+    <t>47283654</t>
+  </si>
+  <si>
+    <t>47286185</t>
+  </si>
+  <si>
+    <t>47289023</t>
+  </si>
+  <si>
+    <t>47290167</t>
+  </si>
+  <si>
+    <t>47292239</t>
+  </si>
+  <si>
+    <t>47292914</t>
+  </si>
+  <si>
+    <t>47296581</t>
+  </si>
+  <si>
+    <t>47296806</t>
+  </si>
+  <si>
     <t>47301012</t>
-  </si>
-  <si>
-    <t>Completed PO</t>
-  </si>
-  <si>
-    <t>47343540</t>
-  </si>
-  <si>
-    <t>47188646</t>
-  </si>
-  <si>
-    <t>47218149</t>
-  </si>
-  <si>
-    <t>47245848</t>
-  </si>
-  <si>
-    <t>47245933</t>
-  </si>
-  <si>
-    <t>47253728</t>
-  </si>
-  <si>
-    <t>47264622</t>
-  </si>
-  <si>
-    <t>47274630</t>
-  </si>
-  <si>
-    <t>47276474</t>
-  </si>
-  <si>
-    <t>47283634</t>
-  </si>
-  <si>
-    <t>47283654</t>
-  </si>
-  <si>
-    <t>47286185</t>
-  </si>
-  <si>
-    <t>47289023</t>
-  </si>
-  <si>
-    <t>47290167</t>
-  </si>
-  <si>
-    <t>47292239</t>
-  </si>
-  <si>
-    <t>47292914</t>
-  </si>
-  <si>
-    <t>47296581</t>
-  </si>
-  <si>
-    <t>47296806</t>
   </si>
   <si>
     <t>47301646</t>
@@ -419,9 +434,6 @@
     <t>4020007647</t>
   </si>
   <si>
-    <t>STMicroelectronics, Inc.</t>
-  </si>
-  <si>
     <t>3030012690</t>
   </si>
   <si>
@@ -542,7 +554,7 @@
     <t>43156228</t>
   </si>
   <si>
-    <t>Last updated: 2026-05-19 10:00:22</t>
+    <t>Last updated: 2026-05-20 13:38:21</t>
   </si>
 </sst>
 </file>
@@ -887,12 +899,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M104"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.5">
@@ -965,7 +977,7 @@
         <v>45898</v>
       </c>
       <c r="K3">
-        <v>-263</v>
+        <v>-264</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -979,19 +991,19 @@
         <v>17</v>
       </c>
       <c r="C4">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H4">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1000,7 +1012,7 @@
         <v>45898</v>
       </c>
       <c r="K4">
-        <v>-263</v>
+        <v>-264</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -1038,7 +1050,7 @@
         <v>45898</v>
       </c>
       <c r="K5">
-        <v>-263</v>
+        <v>-264</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -1055,7 +1067,7 @@
         <v>156</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>17</v>
@@ -1067,13 +1079,13 @@
         <v>128</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="1">
         <v>45898</v>
       </c>
       <c r="K6">
-        <v>-263</v>
+        <v>-264</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -1111,7 +1123,7 @@
         <v>46062</v>
       </c>
       <c r="K7">
-        <v>-99</v>
+        <v>-100</v>
       </c>
       <c r="L7" t="s">
         <v>26</v>
@@ -1128,7 +1140,7 @@
         <v>606</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>17</v>
@@ -1140,13 +1152,13 @@
         <v>562</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J8" s="1">
         <v>46093</v>
       </c>
       <c r="K8">
-        <v>-68</v>
+        <v>-69</v>
       </c>
       <c r="L8" t="s">
         <v>29</v>
@@ -1166,16 +1178,16 @@
         <v>259</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9">
         <v>19</v>
       </c>
       <c r="H9">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1184,7 +1196,7 @@
         <v>46108</v>
       </c>
       <c r="K9">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="L9" t="s">
         <v>33</v>
@@ -1222,7 +1234,7 @@
         <v>46139</v>
       </c>
       <c r="K10">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="L10" t="s">
         <v>37</v>
@@ -1233,170 +1245,188 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
         <v>39</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>9</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>46182</v>
+      </c>
+      <c r="K11">
+        <v>20</v>
+      </c>
+      <c r="L11" t="s">
         <v>40</v>
-      </c>
-      <c r="C11">
-        <v>47</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>4</v>
-      </c>
-      <c r="H11">
-        <v>42</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1">
-        <v>46177</v>
-      </c>
-      <c r="K11">
-        <v>16</v>
-      </c>
-      <c r="L11" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
         <v>42</v>
       </c>
-      <c r="B12" t="s">
-        <v>43</v>
-      </c>
       <c r="C12">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="D12">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>46175</v>
+        <v>46182</v>
       </c>
       <c r="K12">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L12" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C13">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>46174</v>
+        <v>46177</v>
       </c>
       <c r="K13">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C14">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F14">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>28</v>
+        <v>143</v>
       </c>
       <c r="I14">
         <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>46175</v>
+      </c>
+      <c r="K14">
+        <v>13</v>
+      </c>
+      <c r="L14" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15">
+        <v>45</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>43</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>46174</v>
+      </c>
+      <c r="K15">
+        <v>12</v>
+      </c>
+      <c r="L15" t="s">
         <v>50</v>
-      </c>
-      <c r="B15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15">
-        <v>50</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>20</v>
-      </c>
-      <c r="H15">
-        <v>30</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
         <v>52</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1405,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1422,7 +1452,7 @@
         <v>54</v>
       </c>
       <c r="C17">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1431,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H17">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1448,7 +1478,7 @@
         <v>56</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1457,10 +1487,10 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1474,7 +1504,7 @@
         <v>58</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1486,7 +1516,7 @@
         <v>1</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1500,19 +1530,19 @@
         <v>60</v>
       </c>
       <c r="C20">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1520,28 +1550,25 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21" t="s">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1555,19 +1582,16 @@
         <v>63</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
         <v>0</v>
-      </c>
-      <c r="G22" t="s">
-        <v>62</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -1578,28 +1602,25 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C23">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
-      <c r="G23" t="s">
-        <v>62</v>
-      </c>
       <c r="H23">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1610,13 +1631,13 @@
         <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C24">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1625,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H24">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1639,10 +1660,10 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1654,10 +1675,10 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1668,10 +1689,10 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1683,10 +1704,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1697,7 +1718,7 @@
         <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1712,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -1726,7 +1747,7 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1741,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1755,7 +1776,7 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1770,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1784,7 +1805,7 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1799,7 +1820,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1813,10 +1834,10 @@
         <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C31">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1828,10 +1849,10 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H31">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1842,10 +1863,10 @@
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1857,10 +1878,10 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -1871,10 +1892,10 @@
         <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1886,10 +1907,10 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1900,10 +1921,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C34">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1915,10 +1936,10 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H34">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -1929,7 +1950,7 @@
         <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -1944,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -1958,10 +1979,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -1973,10 +1994,10 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1987,7 +2008,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -2002,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -2016,10 +2037,10 @@
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C38">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2031,10 +2052,10 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H38">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2045,10 +2066,10 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2060,10 +2081,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2074,10 +2095,10 @@
         <v>35</v>
       </c>
       <c r="B40" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C40">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2089,10 +2110,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H40">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2103,10 +2124,10 @@
         <v>35</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2118,10 +2139,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2132,10 +2153,10 @@
         <v>35</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2147,10 +2168,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H42">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2158,13 +2179,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2176,10 +2197,10 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2187,13 +2208,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="B44" t="s">
         <v>87</v>
       </c>
       <c r="C44">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2205,10 +2226,10 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H44">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2216,13 +2237,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" t="s">
         <v>88</v>
       </c>
-      <c r="B45" t="s">
-        <v>89</v>
-      </c>
       <c r="C45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2234,10 +2255,10 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2245,13 +2266,13 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A46" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B46" t="s">
         <v>90</v>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2263,10 +2284,10 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2274,13 +2295,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A47" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B47" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2292,10 +2313,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H47">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2303,10 +2324,10 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A48" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -2321,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -2332,13 +2353,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B49" t="s">
         <v>95</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2350,10 +2371,10 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2361,13 +2382,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A50" t="s">
+        <v>93</v>
+      </c>
+      <c r="B50" t="s">
         <v>96</v>
       </c>
-      <c r="B50" t="s">
-        <v>97</v>
-      </c>
       <c r="C50">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2379,10 +2400,10 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H50">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2390,13 +2411,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A51" t="s">
+        <v>97</v>
+      </c>
+      <c r="B51" t="s">
         <v>98</v>
       </c>
-      <c r="B51" t="s">
-        <v>99</v>
-      </c>
       <c r="C51">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2408,10 +2429,10 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H51">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2419,13 +2440,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A52" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B52" t="s">
         <v>100</v>
       </c>
       <c r="C52">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2437,10 +2458,10 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H52">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2448,13 +2469,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B53" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2466,10 +2487,10 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2477,13 +2498,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A54" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B54" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2495,10 +2516,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H54">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2506,13 +2527,13 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B55" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C55">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2524,10 +2545,10 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H55">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2535,13 +2556,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B56" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C56">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2553,10 +2574,10 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H56">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2564,13 +2585,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B57" t="s">
         <v>107</v>
       </c>
       <c r="C57">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2582,10 +2603,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H57">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2593,7 +2614,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B58" t="s">
         <v>108</v>
@@ -2611,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H58">
         <v>10</v>
@@ -2628,7 +2649,7 @@
         <v>110</v>
       </c>
       <c r="C59">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2640,10 +2661,10 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H59">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2657,7 +2678,7 @@
         <v>112</v>
       </c>
       <c r="C60">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2669,10 +2690,10 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H60">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2686,7 +2707,7 @@
         <v>113</v>
       </c>
       <c r="C61">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2698,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H61">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2709,13 +2730,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A62" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B62" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2727,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2738,13 +2759,13 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A63" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B63" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C63">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2756,10 +2777,10 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H63">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -2767,13 +2788,13 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A64" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B64" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2785,10 +2806,10 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -2796,10 +2817,10 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A65" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B65" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -2814,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -2825,13 +2846,13 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A66" t="s">
-        <v>39</v>
+        <v>120</v>
       </c>
       <c r="B66" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2843,10 +2864,10 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -2854,13 +2875,13 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A67" t="s">
-        <v>39</v>
+        <v>120</v>
       </c>
       <c r="B67" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2872,10 +2893,10 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -2883,13 +2904,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A68" t="s">
-        <v>39</v>
+        <v>120</v>
       </c>
       <c r="B68" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2901,10 +2922,10 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -2912,13 +2933,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B69" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -2930,10 +2951,10 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -2941,10 +2962,10 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A70" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B70" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C70">
         <v>3</v>
@@ -2959,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H70">
         <v>3</v>
@@ -2970,13 +2991,13 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
-        <v>124</v>
+        <v>41</v>
       </c>
       <c r="B71" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -2988,10 +3009,10 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -2999,13 +3020,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A72" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="B72" t="s">
         <v>127</v>
       </c>
       <c r="C72">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3017,10 +3038,10 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H72">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3028,13 +3049,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A73" t="s">
+        <v>41</v>
+      </c>
+      <c r="B73" t="s">
         <v>128</v>
       </c>
-      <c r="B73" t="s">
-        <v>129</v>
-      </c>
       <c r="C73">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -3046,10 +3067,10 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H73">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3057,13 +3078,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A74" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B74" t="s">
         <v>130</v>
       </c>
       <c r="C74">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3075,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H74">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3092,7 +3113,7 @@
         <v>132</v>
       </c>
       <c r="C75">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -3104,10 +3125,10 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H75">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3115,13 +3136,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A76" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B76" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3133,10 +3154,10 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H76">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3144,13 +3165,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A77" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B77" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3162,10 +3183,10 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3173,13 +3194,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A78" t="s">
-        <v>131</v>
+        <v>57</v>
       </c>
       <c r="B78" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3191,10 +3212,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3202,10 +3223,10 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A79" t="s">
-        <v>131</v>
+        <v>57</v>
       </c>
       <c r="B79" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -3220,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -3231,10 +3252,10 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A80" t="s">
-        <v>131</v>
+        <v>57</v>
       </c>
       <c r="B80" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -3249,7 +3270,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -3260,10 +3281,10 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A81" t="s">
-        <v>131</v>
+        <v>57</v>
       </c>
       <c r="B81" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -3278,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -3289,13 +3310,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A82" t="s">
-        <v>131</v>
+        <v>57</v>
       </c>
       <c r="B82" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C82">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3307,10 +3328,10 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H82">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -3318,10 +3339,10 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
-        <v>131</v>
+        <v>57</v>
       </c>
       <c r="B83" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -3336,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -3347,13 +3368,13 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A84" t="s">
-        <v>141</v>
+        <v>57</v>
       </c>
       <c r="B84" t="s">
         <v>142</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3365,10 +3386,10 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -3376,13 +3397,13 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A85" t="s">
-        <v>141</v>
+        <v>57</v>
       </c>
       <c r="B85" t="s">
         <v>143</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3394,10 +3415,10 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H85">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -3405,11 +3426,11 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A86" t="s">
+        <v>57</v>
+      </c>
+      <c r="B86" t="s">
         <v>144</v>
       </c>
-      <c r="B86" t="s">
-        <v>145</v>
-      </c>
       <c r="C86">
         <v>1</v>
       </c>
@@ -3423,7 +3444,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -3434,13 +3455,13 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A87" t="s">
+        <v>145</v>
+      </c>
+      <c r="B87" t="s">
         <v>146</v>
       </c>
-      <c r="B87" t="s">
-        <v>147</v>
-      </c>
       <c r="C87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -3452,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -3463,13 +3484,13 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A88" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B88" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C88">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3481,10 +3502,10 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H88">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -3492,10 +3513,10 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A89" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B89" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -3510,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H89">
         <v>1</v>
@@ -3521,13 +3542,13 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A90" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B90" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3539,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -3553,10 +3574,10 @@
         <v>152</v>
       </c>
       <c r="B91" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3568,10 +3589,10 @@
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H91">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -3579,13 +3600,13 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A92" t="s">
+        <v>154</v>
+      </c>
+      <c r="B92" t="s">
         <v>155</v>
       </c>
-      <c r="B92" t="s">
-        <v>156</v>
-      </c>
       <c r="C92">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3597,10 +3618,10 @@
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H92">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -3608,10 +3629,10 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A93" t="s">
+        <v>156</v>
+      </c>
+      <c r="B93" t="s">
         <v>157</v>
-      </c>
-      <c r="B93" t="s">
-        <v>158</v>
       </c>
       <c r="C93">
         <v>2</v>
@@ -3626,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H93">
         <v>2</v>
@@ -3637,13 +3658,13 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A94" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B94" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C94">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3655,10 +3676,10 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H94">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -3666,13 +3687,13 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A95" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B95" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C95">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3684,10 +3705,10 @@
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H95">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -3698,10 +3719,10 @@
         <v>161</v>
       </c>
       <c r="B96" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C96">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3713,10 +3734,10 @@
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H96">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -3724,13 +3745,13 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A97" t="s">
+        <v>163</v>
+      </c>
+      <c r="B97" t="s">
         <v>164</v>
       </c>
-      <c r="B97" t="s">
-        <v>165</v>
-      </c>
       <c r="C97">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3742,10 +3763,10 @@
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H97">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -3753,13 +3774,13 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A98" t="s">
+        <v>165</v>
+      </c>
+      <c r="B98" t="s">
         <v>166</v>
       </c>
-      <c r="B98" t="s">
-        <v>167</v>
-      </c>
       <c r="C98">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3771,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H98">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -3782,13 +3803,13 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A99" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B99" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C99">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3800,10 +3821,10 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H99">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -3811,14 +3832,14 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A100" t="s">
-        <v>53</v>
+        <v>168</v>
       </c>
       <c r="B100" t="s">
+        <v>169</v>
+      </c>
+      <c r="C100">
         <v>170</v>
       </c>
-      <c r="C100">
-        <v>1</v>
-      </c>
       <c r="D100">
         <v>0</v>
       </c>
@@ -3829,10 +3850,10 @@
         <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H100">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -3840,7 +3861,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A101" t="s">
-        <v>53</v>
+        <v>170</v>
       </c>
       <c r="B101" t="s">
         <v>171</v>
@@ -3858,12 +3879,99 @@
         <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H101">
         <v>1</v>
       </c>
       <c r="I101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A102" t="s">
+        <v>172</v>
+      </c>
+      <c r="B102" t="s">
+        <v>173</v>
+      </c>
+      <c r="C102">
+        <v>15</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102" t="s">
+        <v>67</v>
+      </c>
+      <c r="H102">
+        <v>15</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A103" t="s">
+        <v>55</v>
+      </c>
+      <c r="B103" t="s">
+        <v>174</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103" t="s">
+        <v>67</v>
+      </c>
+      <c r="H103">
+        <v>1</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A104" t="s">
+        <v>55</v>
+      </c>
+      <c r="B104" t="s">
+        <v>175</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104" t="s">
+        <v>67</v>
+      </c>
+      <c r="H104">
+        <v>1</v>
+      </c>
+      <c r="I104">
         <v>0</v>
       </c>
     </row>

--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9989577BD439AFF9D7577B84E70D80274" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6CFDA32-1E19-420D-860E-DF638B98A1D2}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9CEA576832BF9E5EF1DB6AC8C70D81816" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6F2D6E8-8BAF-43AE-AC9F-889B2F32320F}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="PO_StatusQry" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$104</definedName>
+    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$107</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="184">
   <si>
     <t>CustName</t>
   </si>
@@ -70,7 +70,7 @@
     <t>4516351202_ASEWH</t>
   </si>
   <si>
-    <t>OverDue by 264 days</t>
+    <t>OverDue by 272 days</t>
   </si>
   <si>
     <t>Texas Instruments SCT</t>
@@ -79,7 +79,7 @@
     <t>4516351202_SCT</t>
   </si>
   <si>
-    <t>Varies (2025-08-29 → 2026-04-21)</t>
+    <t>Varies (2025-08-29 → 2026-06-11)</t>
   </si>
   <si>
     <t>Texas Instruments Taiwan</t>
@@ -103,7 +103,10 @@
     <t>Global PO 4516351202</t>
   </si>
   <si>
-    <t>OverDue by 100 days</t>
+    <t>OverDue by 108 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-02-09 → 2026-06-09)</t>
   </si>
   <si>
     <t>TI (Philippines) Inc.</t>
@@ -112,10 +115,10 @@
     <t>4516351202_TIPI</t>
   </si>
   <si>
-    <t>OverDue by 69 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-03-12 → 2026-05-28)</t>
+    <t>OverDue by 77 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-03-12 → 2026-06-09)</t>
   </si>
   <si>
     <t>ARDENTEC CORPORATION</t>
@@ -124,7 +127,7 @@
     <t>4516351202_ARD</t>
   </si>
   <si>
-    <t>OverDue by 54 days</t>
+    <t>OverDue by 62 days</t>
   </si>
   <si>
     <t>Varies (2026-03-27 → 2026-05-19)</t>
@@ -136,28 +139,37 @@
     <t>47270551</t>
   </si>
   <si>
-    <t>OverDue by 23 days</t>
+    <t>OverDue by 31 days</t>
   </si>
   <si>
     <t>Varies (2026-04-27 → 2026-05-13)</t>
   </si>
   <si>
+    <t>ASE CO., LTD - PHILIPPINES BRANCH 01-075</t>
+  </si>
+  <si>
+    <t>MO262002496</t>
+  </si>
+  <si>
+    <t>18 days before Due</t>
+  </si>
+  <si>
     <t>47318424</t>
   </si>
   <si>
-    <t>20 days before Due</t>
+    <t>12 days before Due</t>
   </si>
   <si>
     <t>NXP Malaysia Sdn. Bhd.</t>
   </si>
   <si>
-    <t>3T/PO262331</t>
-  </si>
-  <si>
     <t>TBA_NXP</t>
   </si>
   <si>
-    <t>15 days before Due</t>
+    <t>7 days before Due</t>
+  </si>
+  <si>
+    <t>Varies (2026-06-04 → 2026-06-16)</t>
   </si>
   <si>
     <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
@@ -166,7 +178,7 @@
     <t>4516351202_MIHO</t>
   </si>
   <si>
-    <t>13 days before Due</t>
+    <t>5 days before Due</t>
   </si>
   <si>
     <t>Texas Instruments AIZU</t>
@@ -175,7 +187,7 @@
     <t>4516351202_AIZU</t>
   </si>
   <si>
-    <t>12 days before Due</t>
+    <t>4 days before Due</t>
   </si>
   <si>
     <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
@@ -190,6 +202,15 @@
     <t>4516351202_ASESH</t>
   </si>
   <si>
+    <t>3T/PO262333</t>
+  </si>
+  <si>
+    <t>Texas Instruments DMOS5</t>
+  </si>
+  <si>
+    <t>4516351202_DMOS5</t>
+  </si>
+  <si>
     <t>UTAC Thai Limited ( UTL 3)</t>
   </si>
   <si>
@@ -202,94 +223,88 @@
     <t>4010018600</t>
   </si>
   <si>
-    <t>TEXAS INSTRUMENTS DEUTSCHLAND GMBH</t>
-  </si>
-  <si>
-    <t>4516351202_FFAB</t>
-  </si>
-  <si>
     <t>Texas Instruments LFAB</t>
   </si>
   <si>
     <t>4516351202_LFAB</t>
   </si>
   <si>
+    <t>ROCHESTER ELECTRONICS</t>
+  </si>
+  <si>
+    <t>252395</t>
+  </si>
+  <si>
+    <t>47343540</t>
+  </si>
+  <si>
+    <t>Completed PO</t>
+  </si>
+  <si>
+    <t>47188646</t>
+  </si>
+  <si>
+    <t>47218149</t>
+  </si>
+  <si>
+    <t>47245848</t>
+  </si>
+  <si>
+    <t>47245933</t>
+  </si>
+  <si>
+    <t>47253728</t>
+  </si>
+  <si>
+    <t>47264622</t>
+  </si>
+  <si>
+    <t>47274630</t>
+  </si>
+  <si>
+    <t>47276474</t>
+  </si>
+  <si>
+    <t>47283634</t>
+  </si>
+  <si>
+    <t>47283654</t>
+  </si>
+  <si>
+    <t>47286185</t>
+  </si>
+  <si>
+    <t>47289023</t>
+  </si>
+  <si>
+    <t>47290167</t>
+  </si>
+  <si>
+    <t>47292239</t>
+  </si>
+  <si>
+    <t>47292914</t>
+  </si>
+  <si>
+    <t>47296581</t>
+  </si>
+  <si>
+    <t>47296806</t>
+  </si>
+  <si>
+    <t>47301012</t>
+  </si>
+  <si>
+    <t>47301646</t>
+  </si>
+  <si>
+    <t>47304169</t>
+  </si>
+  <si>
+    <t>47324752</t>
+  </si>
+  <si>
     <t>47345978</t>
-  </si>
-  <si>
-    <t>ROCHESTER ELECTRONICS</t>
-  </si>
-  <si>
-    <t>252395</t>
-  </si>
-  <si>
-    <t>47343540</t>
-  </si>
-  <si>
-    <t>Completed PO</t>
-  </si>
-  <si>
-    <t>47188646</t>
-  </si>
-  <si>
-    <t>47218149</t>
-  </si>
-  <si>
-    <t>47245848</t>
-  </si>
-  <si>
-    <t>47245933</t>
-  </si>
-  <si>
-    <t>47253728</t>
-  </si>
-  <si>
-    <t>47264622</t>
-  </si>
-  <si>
-    <t>47274630</t>
-  </si>
-  <si>
-    <t>47276474</t>
-  </si>
-  <si>
-    <t>47283634</t>
-  </si>
-  <si>
-    <t>47283654</t>
-  </si>
-  <si>
-    <t>47286185</t>
-  </si>
-  <si>
-    <t>47289023</t>
-  </si>
-  <si>
-    <t>47290167</t>
-  </si>
-  <si>
-    <t>47292239</t>
-  </si>
-  <si>
-    <t>47292914</t>
-  </si>
-  <si>
-    <t>47296581</t>
-  </si>
-  <si>
-    <t>47296806</t>
-  </si>
-  <si>
-    <t>47301012</t>
-  </si>
-  <si>
-    <t>47301646</t>
-  </si>
-  <si>
-    <t>47304169</t>
-  </si>
-  <si>
-    <t>47324752</t>
   </si>
   <si>
     <t>ANALOG DEVICES INC. CAMAS</t>
@@ -335,6 +350,9 @@
     <t>TBD</t>
   </si>
   <si>
+    <t>TBD_BSETWN</t>
+  </si>
+  <si>
     <t>CARDIAC PACEMAKERS INC</t>
   </si>
   <si>
@@ -413,6 +431,9 @@
     <t>3T/PO262326</t>
   </si>
   <si>
+    <t>3T/PO262331</t>
+  </si>
+  <si>
     <t>ON Semiconductor Philippines Inc</t>
   </si>
   <si>
@@ -482,10 +503,10 @@
     <t>4516351202_TMX</t>
   </si>
   <si>
-    <t>Texas Instruments DMOS5</t>
-  </si>
-  <si>
-    <t>4516351202_DMOS5</t>
+    <t>TEXAS INSTRUMENTS DEUTSCHLAND GMBH</t>
+  </si>
+  <si>
+    <t>4516351202_FFAB</t>
   </si>
   <si>
     <t>Texas Instruments FTLABS</t>
@@ -554,7 +575,7 @@
     <t>43156228</t>
   </si>
   <si>
-    <t>Last updated: 2026-05-20 13:38:21</t>
+    <t>Last updated: 2026-05-28 13:19:15</t>
   </si>
 </sst>
 </file>
@@ -899,12 +920,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M104"/>
+  <dimension ref="A1:M107"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.5">
@@ -977,7 +998,7 @@
         <v>45898</v>
       </c>
       <c r="K3">
-        <v>-264</v>
+        <v>-272</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -991,19 +1012,19 @@
         <v>17</v>
       </c>
       <c r="C4">
-        <v>292</v>
+        <v>320</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1012,7 +1033,7 @@
         <v>45898</v>
       </c>
       <c r="K4">
-        <v>-264</v>
+        <v>-272</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -1050,7 +1071,7 @@
         <v>45898</v>
       </c>
       <c r="K5">
-        <v>-264</v>
+        <v>-272</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -1070,22 +1091,22 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F6">
         <v>9</v>
       </c>
       <c r="H6">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1">
         <v>45898</v>
       </c>
       <c r="K6">
-        <v>-264</v>
+        <v>-272</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -1108,13 +1129,13 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1123,56 +1144,59 @@
         <v>46062</v>
       </c>
       <c r="K7">
-        <v>-100</v>
+        <v>-108</v>
       </c>
       <c r="L7" t="s">
         <v>26</v>
       </c>
+      <c r="M7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8">
-        <v>606</v>
+        <v>616</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H8">
-        <v>562</v>
+        <v>578</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J8" s="1">
         <v>46093</v>
       </c>
       <c r="K8">
-        <v>-69</v>
+        <v>-77</v>
       </c>
       <c r="L8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>259</v>
@@ -1181,13 +1205,13 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F9">
         <v>19</v>
       </c>
       <c r="H9">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1196,21 +1220,21 @@
         <v>46108</v>
       </c>
       <c r="K9">
-        <v>-54</v>
+        <v>-62</v>
       </c>
       <c r="L9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10">
         <v>42</v>
@@ -1234,30 +1258,30 @@
         <v>46139</v>
       </c>
       <c r="K10">
-        <v>-23</v>
+        <v>-31</v>
       </c>
       <c r="L10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C11">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1269,30 +1293,30 @@
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="K11">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1307,18 +1331,18 @@
         <v>46182</v>
       </c>
       <c r="K12">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L12" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C13">
         <v>47</v>
@@ -1327,10 +1351,10 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <v>42</v>
@@ -1342,18 +1366,21 @@
         <v>46177</v>
       </c>
       <c r="K13">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L13" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="M13" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C14">
         <v>150</v>
@@ -1377,21 +1404,21 @@
         <v>46175</v>
       </c>
       <c r="K14">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C15">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1400,7 +1427,7 @@
         <v>2</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
         <v>43</v>
@@ -1412,18 +1439,18 @@
         <v>46174</v>
       </c>
       <c r="K15">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L15" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C16">
         <v>50</v>
@@ -1446,10 +1473,10 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C17">
         <v>50</v>
@@ -1472,13 +1499,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C18">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1487,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H18">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1498,13 +1525,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1513,10 +1540,10 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1524,13 +1551,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1539,10 +1566,10 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1550,13 +1577,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1568,7 +1595,7 @@
         <v>1</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1576,13 +1603,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1591,10 +1618,10 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1602,10 +1629,10 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C23">
         <v>70</v>
@@ -1628,10 +1655,10 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1646,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -1657,10 +1684,10 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C25">
         <v>19</v>
@@ -1675,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H25">
         <v>19</v>
@@ -1686,10 +1713,10 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C26">
         <v>21</v>
@@ -1704,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H26">
         <v>21</v>
@@ -1715,10 +1742,10 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1733,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -1744,10 +1771,10 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1762,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1773,10 +1800,10 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1791,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1802,10 +1829,10 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1820,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1831,10 +1858,10 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1849,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1860,10 +1887,10 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1878,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -1889,10 +1916,10 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C33">
         <v>6</v>
@@ -1907,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H33">
         <v>6</v>
@@ -1918,10 +1945,10 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -1936,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H34">
         <v>2</v>
@@ -1947,10 +1974,10 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -1965,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -1976,10 +2003,10 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C36">
         <v>4</v>
@@ -1994,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H36">
         <v>4</v>
@@ -2005,10 +2032,10 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -2023,7 +2050,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -2034,10 +2061,10 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -2052,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H38">
         <v>2</v>
@@ -2063,10 +2090,10 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -2081,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -2092,10 +2119,10 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C40">
         <v>9</v>
@@ -2110,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H40">
         <v>9</v>
@@ -2121,10 +2148,10 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A41" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C41">
         <v>4</v>
@@ -2139,7 +2166,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H41">
         <v>4</v>
@@ -2150,10 +2177,10 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B42" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C42">
         <v>13</v>
@@ -2168,7 +2195,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H42">
         <v>13</v>
@@ -2179,10 +2206,10 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C43">
         <v>5</v>
@@ -2197,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H43">
         <v>5</v>
@@ -2208,10 +2235,10 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -2226,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -2237,10 +2264,10 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A45" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B45" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -2255,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H45">
         <v>4</v>
@@ -2266,13 +2293,13 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A46" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="B46" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2284,10 +2311,10 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2295,13 +2322,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A47" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C47">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2313,10 +2340,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H47">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2324,13 +2351,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A48" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B48" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2342,10 +2369,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2353,13 +2380,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A49" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B49" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2371,10 +2398,10 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2382,13 +2409,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A50" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B50" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2400,10 +2427,10 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H50">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2411,13 +2438,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2429,10 +2456,10 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2440,10 +2467,10 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A52" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B52" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -2458,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -2469,13 +2496,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A53" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B53" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2487,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2498,13 +2525,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B54" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C54">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2516,10 +2543,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H54">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2527,13 +2554,13 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B55" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C55">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2545,10 +2572,10 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H55">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2556,13 +2583,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B56" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2574,10 +2601,10 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2585,13 +2612,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B57" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2603,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H57">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2614,13 +2641,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B58" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C58">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2632,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H58">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2646,10 +2673,10 @@
         <v>109</v>
       </c>
       <c r="B59" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C59">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2661,10 +2688,10 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H59">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2672,13 +2699,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A60" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B60" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C60">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2690,10 +2717,10 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H60">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2701,13 +2728,13 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A61" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B61" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C61">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2719,10 +2746,10 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H61">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2730,13 +2757,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A62" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B62" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2748,10 +2775,10 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H62">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2759,13 +2786,13 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A63" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B63" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C63">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2777,10 +2804,10 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H63">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -2788,13 +2815,13 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A64" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B64" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C64">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2806,10 +2833,10 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H64">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -2817,13 +2844,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A65" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B65" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2835,10 +2862,10 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -2846,13 +2873,13 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A66" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B66" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C66">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2864,10 +2891,10 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H66">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -2875,10 +2902,10 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A67" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B67" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -2893,7 +2920,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -2904,13 +2931,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A68" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B68" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2922,10 +2949,10 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -2933,10 +2960,10 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="B69" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -2951,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -2962,13 +2989,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A70" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
       <c r="B70" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -2980,10 +3007,10 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -2991,13 +3018,13 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -3009,10 +3036,10 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3020,10 +3047,10 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A72" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C72">
         <v>3</v>
@@ -3038,7 +3065,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H72">
         <v>3</v>
@@ -3049,10 +3076,10 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A73" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C73">
         <v>3</v>
@@ -3067,7 +3094,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H73">
         <v>3</v>
@@ -3078,13 +3105,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A74" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3096,10 +3123,10 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3107,13 +3134,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A75" t="s">
-        <v>131</v>
+        <v>45</v>
       </c>
       <c r="B75" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C75">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -3125,10 +3152,10 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H75">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3136,13 +3163,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A76" t="s">
-        <v>133</v>
+        <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C76">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3154,10 +3181,10 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H76">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3165,13 +3192,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A77" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B77" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C77">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3183,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H77">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3194,13 +3221,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A78" t="s">
-        <v>57</v>
+        <v>138</v>
       </c>
       <c r="B78" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C78">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3212,10 +3239,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H78">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3223,13 +3250,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A79" t="s">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="B79" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3241,10 +3268,10 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3252,13 +3279,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A80" t="s">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="B80" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3270,10 +3297,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3281,13 +3308,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A81" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B81" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3299,10 +3326,10 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H81">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -3310,10 +3337,10 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A82" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B82" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -3328,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -3339,10 +3366,10 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B83" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -3357,7 +3384,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -3368,10 +3395,10 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A84" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B84" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -3386,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -3397,13 +3424,13 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A85" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B85" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C85">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3415,10 +3442,10 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H85">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -3426,10 +3453,10 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A86" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B86" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -3444,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -3455,13 +3482,13 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A87" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="B87" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -3473,10 +3500,10 @@
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -3484,13 +3511,13 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A88" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="B88" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C88">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3502,10 +3529,10 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H88">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -3513,10 +3540,10 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A89" t="s">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="B89" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -3531,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H89">
         <v>1</v>
@@ -3542,13 +3569,13 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A90" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B90" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3560,10 +3587,10 @@
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -3574,10 +3601,10 @@
         <v>152</v>
       </c>
       <c r="B91" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C91">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3589,10 +3616,10 @@
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H91">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -3600,10 +3627,10 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A92" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B92" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -3618,7 +3645,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -3629,13 +3656,13 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A93" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B93" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3647,10 +3674,10 @@
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -3658,13 +3685,13 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A94" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B94" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3676,10 +3703,10 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H94">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -3687,13 +3714,13 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A95" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B95" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C95">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3705,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H95">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -3716,10 +3743,10 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A96" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B96" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C96">
         <v>2</v>
@@ -3734,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H96">
         <v>2</v>
@@ -3748,10 +3775,10 @@
         <v>163</v>
       </c>
       <c r="B97" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C97">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3763,10 +3790,10 @@
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H97">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -3774,13 +3801,13 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A98" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B98" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C98">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3792,10 +3819,10 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H98">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -3803,13 +3830,13 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A99" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B99" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C99">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3821,10 +3848,10 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H99">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -3832,13 +3859,13 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A100" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B100" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C100">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3850,10 +3877,10 @@
         <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H100">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -3861,13 +3888,13 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A101" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B101" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3879,10 +3906,10 @@
         <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H101">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -3893,10 +3920,10 @@
         <v>172</v>
       </c>
       <c r="B102" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C102">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3908,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="G102" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H102">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -3919,13 +3946,13 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A103" t="s">
-        <v>55</v>
+        <v>175</v>
       </c>
       <c r="B103" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3937,10 +3964,10 @@
         <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H103">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -3948,10 +3975,10 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A104" t="s">
-        <v>55</v>
+        <v>177</v>
       </c>
       <c r="B104" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -3966,12 +3993,99 @@
         <v>0</v>
       </c>
       <c r="G104" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H104">
         <v>1</v>
       </c>
       <c r="I104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A105" t="s">
+        <v>179</v>
+      </c>
+      <c r="B105" t="s">
+        <v>180</v>
+      </c>
+      <c r="C105">
+        <v>15</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105" t="s">
+        <v>71</v>
+      </c>
+      <c r="H105">
+        <v>15</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A106" t="s">
+        <v>62</v>
+      </c>
+      <c r="B106" t="s">
+        <v>181</v>
+      </c>
+      <c r="C106">
+        <v>1</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106" t="s">
+        <v>71</v>
+      </c>
+      <c r="H106">
+        <v>1</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A107" t="s">
+        <v>62</v>
+      </c>
+      <c r="B107" t="s">
+        <v>182</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107" t="s">
+        <v>71</v>
+      </c>
+      <c r="H107">
+        <v>1</v>
+      </c>
+      <c r="I107">
         <v>0</v>
       </c>
     </row>

--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9CEA576832BF9E5EF1DB6AC8C70D81816" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6F2D6E8-8BAF-43AE-AC9F-889B2F32320F}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB94645F3ADA9F9E50E15B69F8C70D81819" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB0F228F-9CB4-42F4-AEB3-D7725675274A}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="73" windowWidth="25600" windowHeight="9847" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PO_StatusQry" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
     <t>4516351202_ASEWH</t>
   </si>
   <si>
-    <t>OverDue by 272 days</t>
+    <t>OverDue by 276 days</t>
   </si>
   <si>
     <t>Texas Instruments SCT</t>
@@ -103,7 +103,7 @@
     <t>Global PO 4516351202</t>
   </si>
   <si>
-    <t>OverDue by 108 days</t>
+    <t>OverDue by 112 days</t>
   </si>
   <si>
     <t>Varies (2026-02-09 → 2026-06-09)</t>
@@ -115,7 +115,7 @@
     <t>4516351202_TIPI</t>
   </si>
   <si>
-    <t>OverDue by 77 days</t>
+    <t>OverDue by 81 days</t>
   </si>
   <si>
     <t>Varies (2026-03-12 → 2026-06-09)</t>
@@ -127,7 +127,7 @@
     <t>4516351202_ARD</t>
   </si>
   <si>
-    <t>OverDue by 62 days</t>
+    <t>OverDue by 66 days</t>
   </si>
   <si>
     <t>Varies (2026-03-27 → 2026-05-19)</t>
@@ -139,7 +139,7 @@
     <t>47270551</t>
   </si>
   <si>
-    <t>OverDue by 31 days</t>
+    <t>OverDue by 35 days</t>
   </si>
   <si>
     <t>Varies (2026-04-27 → 2026-05-13)</t>
@@ -151,13 +151,13 @@
     <t>MO262002496</t>
   </si>
   <si>
-    <t>18 days before Due</t>
+    <t>14 days before Due</t>
   </si>
   <si>
     <t>47318424</t>
   </si>
   <si>
-    <t>12 days before Due</t>
+    <t>8 days before Due</t>
   </si>
   <si>
     <t>NXP Malaysia Sdn. Bhd.</t>
@@ -166,7 +166,7 @@
     <t>TBA_NXP</t>
   </si>
   <si>
-    <t>7 days before Due</t>
+    <t>3 days before Due</t>
   </si>
   <si>
     <t>Varies (2026-06-04 → 2026-06-16)</t>
@@ -178,7 +178,7 @@
     <t>4516351202_MIHO</t>
   </si>
   <si>
-    <t>5 days before Due</t>
+    <t>1 days before Due</t>
   </si>
   <si>
     <t>Texas Instruments AIZU</t>
@@ -187,7 +187,7 @@
     <t>4516351202_AIZU</t>
   </si>
   <si>
-    <t>4 days before Due</t>
+    <t>Due Today</t>
   </si>
   <si>
     <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
@@ -575,7 +575,7 @@
     <t>43156228</t>
   </si>
   <si>
-    <t>Last updated: 2026-05-28 13:19:15</t>
+    <t>Last updated: 2026-06-01 10:10:08</t>
   </si>
 </sst>
 </file>
@@ -998,7 +998,7 @@
         <v>45898</v>
       </c>
       <c r="K3">
-        <v>-272</v>
+        <v>-276</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -1018,22 +1018,22 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H4">
         <v>267</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J4" s="1">
         <v>45898</v>
       </c>
       <c r="K4">
-        <v>-272</v>
+        <v>-276</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -1071,7 +1071,7 @@
         <v>45898</v>
       </c>
       <c r="K5">
-        <v>-272</v>
+        <v>-276</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -1088,10 +1088,10 @@
         <v>156</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -1106,7 +1106,7 @@
         <v>45898</v>
       </c>
       <c r="K6">
-        <v>-272</v>
+        <v>-276</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -1144,7 +1144,7 @@
         <v>46062</v>
       </c>
       <c r="K7">
-        <v>-108</v>
+        <v>-112</v>
       </c>
       <c r="L7" t="s">
         <v>26</v>
@@ -1182,7 +1182,7 @@
         <v>46093</v>
       </c>
       <c r="K8">
-        <v>-77</v>
+        <v>-81</v>
       </c>
       <c r="L8" t="s">
         <v>30</v>
@@ -1220,7 +1220,7 @@
         <v>46108</v>
       </c>
       <c r="K9">
-        <v>-62</v>
+        <v>-66</v>
       </c>
       <c r="L9" t="s">
         <v>34</v>
@@ -1258,7 +1258,7 @@
         <v>46139</v>
       </c>
       <c r="K10">
-        <v>-31</v>
+        <v>-35</v>
       </c>
       <c r="L10" t="s">
         <v>38</v>
@@ -1296,7 +1296,7 @@
         <v>46188</v>
       </c>
       <c r="K11">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L11" t="s">
         <v>42</v>
@@ -1331,7 +1331,7 @@
         <v>46182</v>
       </c>
       <c r="K12">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L12" t="s">
         <v>44</v>
@@ -1345,7 +1345,7 @@
         <v>46</v>
       </c>
       <c r="C13">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1354,7 +1354,7 @@
         <v>5</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13">
         <v>42</v>
@@ -1366,7 +1366,7 @@
         <v>46177</v>
       </c>
       <c r="K13">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L13" t="s">
         <v>47</v>
@@ -1404,7 +1404,7 @@
         <v>46175</v>
       </c>
       <c r="K14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L14" t="s">
         <v>51</v>
@@ -1439,7 +1439,7 @@
         <v>46174</v>
       </c>
       <c r="K15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L15" t="s">
         <v>54</v>

--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB94645F3ADA9F9E50E15B69F8C70D81819" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB0F228F-9CB4-42F4-AEB3-D7725675274A}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB90A3532DBA91BF0C4C5F0A21671D817AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C15AFFE8-56E3-4B1D-A9FE-1D76E16B4AE6}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="73" windowWidth="25600" windowHeight="9847" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PO_StatusQry" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$107</definedName>
+    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$110</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="188">
   <si>
     <t>CustName</t>
   </si>
@@ -70,7 +70,7 @@
     <t>4516351202_ASEWH</t>
   </si>
   <si>
-    <t>OverDue by 276 days</t>
+    <t>OverDue by 285 days</t>
   </si>
   <si>
     <t>Texas Instruments SCT</t>
@@ -103,7 +103,7 @@
     <t>Global PO 4516351202</t>
   </si>
   <si>
-    <t>OverDue by 112 days</t>
+    <t>OverDue by 121 days</t>
   </si>
   <si>
     <t>Varies (2026-02-09 → 2026-06-09)</t>
@@ -115,7 +115,7 @@
     <t>4516351202_TIPI</t>
   </si>
   <si>
-    <t>OverDue by 81 days</t>
+    <t>OverDue by 90 days</t>
   </si>
   <si>
     <t>Varies (2026-03-12 → 2026-06-09)</t>
@@ -127,10 +127,10 @@
     <t>4516351202_ARD</t>
   </si>
   <si>
-    <t>OverDue by 66 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-03-27 → 2026-05-19)</t>
+    <t>OverDue by 75 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-03-27 → 2026-06-18)</t>
   </si>
   <si>
     <t>Analog Devices Gen. Trias Inc. (ADGT)</t>
@@ -139,190 +139,190 @@
     <t>47270551</t>
   </si>
   <si>
-    <t>OverDue by 35 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-04-27 → 2026-05-13)</t>
-  </si>
-  <si>
-    <t>ASE CO., LTD - PHILIPPINES BRANCH 01-075</t>
-  </si>
-  <si>
-    <t>MO262002496</t>
-  </si>
-  <si>
-    <t>14 days before Due</t>
+    <t>OverDue by 44 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-04-27 → 2026-06-30)</t>
+  </si>
+  <si>
+    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
+  </si>
+  <si>
+    <t>4516351202_MIHO</t>
+  </si>
+  <si>
+    <t>OverDue by 8 days</t>
+  </si>
+  <si>
+    <t>NXP Malaysia Sdn. Bhd.</t>
+  </si>
+  <si>
+    <t>TBA_NXP</t>
+  </si>
+  <si>
+    <t>OverDue by 6 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-06-04 → 2026-06-16)</t>
   </si>
   <si>
     <t>47318424</t>
   </si>
   <si>
-    <t>8 days before Due</t>
-  </si>
-  <si>
-    <t>NXP Malaysia Sdn. Bhd.</t>
-  </si>
-  <si>
-    <t>TBA_NXP</t>
-  </si>
-  <si>
-    <t>3 days before Due</t>
-  </si>
-  <si>
-    <t>Varies (2026-06-04 → 2026-06-16)</t>
-  </si>
-  <si>
-    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
-  </si>
-  <si>
-    <t>4516351202_MIHO</t>
-  </si>
-  <si>
-    <t>1 days before Due</t>
-  </si>
-  <si>
-    <t>Texas Instruments AIZU</t>
-  </si>
-  <si>
-    <t>4516351202_AIZU</t>
-  </si>
-  <si>
-    <t>Due Today</t>
-  </si>
-  <si>
-    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
-  </si>
-  <si>
-    <t>4516351202_TII</t>
-  </si>
-  <si>
-    <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
-  </si>
-  <si>
-    <t>4516351202_ASESH</t>
-  </si>
-  <si>
-    <t>3T/PO262333</t>
-  </si>
-  <si>
-    <t>Texas Instruments DMOS5</t>
-  </si>
-  <si>
-    <t>4516351202_DMOS5</t>
-  </si>
-  <si>
-    <t>UTAC Thai Limited ( UTL 3)</t>
-  </si>
-  <si>
-    <t>4516351202_UTL</t>
-  </si>
-  <si>
-    <t>STMicroelectronics, Inc.</t>
-  </si>
-  <si>
-    <t>4010018600</t>
-  </si>
-  <si>
-    <t>Texas Instruments LFAB</t>
-  </si>
-  <si>
-    <t>4516351202_LFAB</t>
-  </si>
-  <si>
-    <t>ROCHESTER ELECTRONICS</t>
-  </si>
-  <si>
-    <t>252395</t>
-  </si>
-  <si>
-    <t>47343540</t>
-  </si>
-  <si>
-    <t>Completed PO</t>
-  </si>
-  <si>
-    <t>47188646</t>
-  </si>
-  <si>
-    <t>47218149</t>
-  </si>
-  <si>
-    <t>47245848</t>
-  </si>
-  <si>
-    <t>47245933</t>
-  </si>
-  <si>
-    <t>47253728</t>
-  </si>
-  <si>
-    <t>47264622</t>
-  </si>
-  <si>
-    <t>47274630</t>
-  </si>
-  <si>
-    <t>47276474</t>
-  </si>
-  <si>
-    <t>47283634</t>
-  </si>
-  <si>
-    <t>47283654</t>
-  </si>
-  <si>
-    <t>47286185</t>
-  </si>
-  <si>
-    <t>47289023</t>
-  </si>
-  <si>
-    <t>47290167</t>
-  </si>
-  <si>
-    <t>47292239</t>
-  </si>
-  <si>
-    <t>47292914</t>
-  </si>
-  <si>
-    <t>47296581</t>
-  </si>
-  <si>
-    <t>47296806</t>
-  </si>
-  <si>
-    <t>47301012</t>
-  </si>
-  <si>
-    <t>47301646</t>
-  </si>
-  <si>
-    <t>47304169</t>
-  </si>
-  <si>
-    <t>47324752</t>
-  </si>
-  <si>
-    <t>47345978</t>
-  </si>
-  <si>
-    <t>ANALOG DEVICES INC. CAMAS</t>
-  </si>
-  <si>
-    <t>47259467</t>
-  </si>
-  <si>
-    <t>Ardentec Korea Co., Ltd.</t>
-  </si>
-  <si>
-    <t>4516351202_ATK</t>
+    <t>OverDue by 1 days</t>
   </si>
   <si>
     <t>AVAGO TECHNOLOGIES_x000D_
 INTERNATIONAL SALES PTE LTD</t>
   </si>
   <si>
+    <t>8541563942</t>
+  </si>
+  <si>
+    <t>15 days before Due</t>
+  </si>
+  <si>
+    <t>STMicroelectronics, Inc.</t>
+  </si>
+  <si>
+    <t>4010018600</t>
+  </si>
+  <si>
+    <t>3T/PO262333</t>
+  </si>
+  <si>
+    <t>12 days before Due</t>
+  </si>
+  <si>
+    <t>ASE CO., LTD - PHILIPPINES BRANCH 01-075</t>
+  </si>
+  <si>
+    <t>MO262002496</t>
+  </si>
+  <si>
+    <t>5 days before Due</t>
+  </si>
+  <si>
+    <t>Texas Instruments DMOS5</t>
+  </si>
+  <si>
+    <t>4516351202_DMOS5</t>
+  </si>
+  <si>
+    <t>UTAC Thai Limited ( UTL 3)</t>
+  </si>
+  <si>
+    <t>4516351202_UTL</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
+  </si>
+  <si>
+    <t>4516351202_TII</t>
+  </si>
+  <si>
+    <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
+  </si>
+  <si>
+    <t>4516351202_ASESH</t>
+  </si>
+  <si>
+    <t>47301012</t>
+  </si>
+  <si>
+    <t>Texas Instruments LFAB</t>
+  </si>
+  <si>
+    <t>4516351202_LFAB</t>
+  </si>
+  <si>
+    <t>47352135</t>
+  </si>
+  <si>
+    <t>ROCHESTER ELECTRONICS</t>
+  </si>
+  <si>
+    <t>252395</t>
+  </si>
+  <si>
+    <t>47188646</t>
+  </si>
+  <si>
+    <t>Completed PO</t>
+  </si>
+  <si>
+    <t>47218149</t>
+  </si>
+  <si>
+    <t>47245848</t>
+  </si>
+  <si>
+    <t>47245933</t>
+  </si>
+  <si>
+    <t>47253728</t>
+  </si>
+  <si>
+    <t>47264622</t>
+  </si>
+  <si>
+    <t>47274630</t>
+  </si>
+  <si>
+    <t>47276474</t>
+  </si>
+  <si>
+    <t>47283634</t>
+  </si>
+  <si>
+    <t>47283654</t>
+  </si>
+  <si>
+    <t>47286185</t>
+  </si>
+  <si>
+    <t>47289023</t>
+  </si>
+  <si>
+    <t>47290167</t>
+  </si>
+  <si>
+    <t>47292239</t>
+  </si>
+  <si>
+    <t>47292914</t>
+  </si>
+  <si>
+    <t>47296581</t>
+  </si>
+  <si>
+    <t>47296806</t>
+  </si>
+  <si>
+    <t>47301646</t>
+  </si>
+  <si>
+    <t>47304169</t>
+  </si>
+  <si>
+    <t>47324752</t>
+  </si>
+  <si>
+    <t>47345978</t>
+  </si>
+  <si>
+    <t>ANALOG DEVICES INC. CAMAS</t>
+  </si>
+  <si>
+    <t>47259467</t>
+  </si>
+  <si>
+    <t>Ardentec Korea Co., Ltd.</t>
+  </si>
+  <si>
+    <t>4516351202_ATK</t>
+  </si>
+  <si>
     <t>8541541216</t>
   </si>
   <si>
@@ -440,6 +440,9 @@
     <t>561000005506</t>
   </si>
   <si>
+    <t>561000006670</t>
+  </si>
+  <si>
     <t>Rhenus Logistics Co.,Ltd.</t>
   </si>
   <si>
@@ -491,6 +494,12 @@
     <t>BSE-58645</t>
   </si>
   <si>
+    <t>Texas Instruments AIZU</t>
+  </si>
+  <si>
+    <t>4516351202_AIZU</t>
+  </si>
+  <si>
     <t>Texas Instruments CLAB</t>
   </si>
   <si>
@@ -548,6 +557,9 @@
     <t>4516450237</t>
   </si>
   <si>
+    <t>4516519979</t>
+  </si>
+  <si>
     <t>4910171717</t>
   </si>
   <si>
@@ -575,7 +587,7 @@
     <t>43156228</t>
   </si>
   <si>
-    <t>Last updated: 2026-06-01 10:10:08</t>
+    <t>Last updated: 2026-06-10 13:25:45</t>
   </si>
 </sst>
 </file>
@@ -920,12 +932,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M107"/>
+  <dimension ref="A1:M110"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.5">
@@ -998,7 +1010,7 @@
         <v>45898</v>
       </c>
       <c r="K3">
-        <v>-276</v>
+        <v>-285</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -1012,28 +1024,28 @@
         <v>17</v>
       </c>
       <c r="C4">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="H4">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="I4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J4" s="1">
         <v>45898</v>
       </c>
       <c r="K4">
-        <v>-276</v>
+        <v>-285</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -1050,7 +1062,7 @@
         <v>20</v>
       </c>
       <c r="C5">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1059,7 +1071,7 @@
         <v>2</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>262</v>
@@ -1071,7 +1083,7 @@
         <v>45898</v>
       </c>
       <c r="K5">
-        <v>-276</v>
+        <v>-285</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -1085,28 +1097,28 @@
         <v>22</v>
       </c>
       <c r="C6">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="H6">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J6" s="1">
         <v>45898</v>
       </c>
       <c r="K6">
-        <v>-276</v>
+        <v>-285</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -1144,7 +1156,7 @@
         <v>46062</v>
       </c>
       <c r="K7">
-        <v>-112</v>
+        <v>-121</v>
       </c>
       <c r="L7" t="s">
         <v>26</v>
@@ -1161,28 +1173,28 @@
         <v>29</v>
       </c>
       <c r="C8">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F8">
+        <v>20</v>
+      </c>
+      <c r="H8">
+        <v>586</v>
+      </c>
+      <c r="I8">
         <v>10</v>
-      </c>
-      <c r="H8">
-        <v>578</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
       </c>
       <c r="J8" s="1">
         <v>46093</v>
       </c>
       <c r="K8">
-        <v>-81</v>
+        <v>-90</v>
       </c>
       <c r="L8" t="s">
         <v>30</v>
@@ -1205,13 +1217,13 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F9">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1220,7 +1232,7 @@
         <v>46108</v>
       </c>
       <c r="K9">
-        <v>-66</v>
+        <v>-75</v>
       </c>
       <c r="L9" t="s">
         <v>34</v>
@@ -1237,13 +1249,13 @@
         <v>37</v>
       </c>
       <c r="C10">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1258,7 +1270,7 @@
         <v>46139</v>
       </c>
       <c r="K10">
-        <v>-35</v>
+        <v>-44</v>
       </c>
       <c r="L10" t="s">
         <v>38</v>
@@ -1275,28 +1287,28 @@
         <v>41</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>162</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>46188</v>
+        <v>46175</v>
       </c>
       <c r="K11">
-        <v>14</v>
+        <v>-8</v>
       </c>
       <c r="L11" t="s">
         <v>42</v>
@@ -1304,74 +1316,74 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C12">
+        <v>56</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12">
         <v>9</v>
       </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>9</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
       <c r="H12">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>46182</v>
+        <v>46177</v>
       </c>
       <c r="K12">
-        <v>8</v>
+        <v>-6</v>
       </c>
       <c r="L12" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="M12" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C13">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>46177</v>
+        <v>46182</v>
       </c>
       <c r="K13">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L13" t="s">
-        <v>47</v>
-      </c>
-      <c r="M13" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1383,28 +1395,28 @@
         <v>50</v>
       </c>
       <c r="C14">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>46175</v>
+        <v>46198</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L14" t="s">
         <v>51</v>
@@ -1418,198 +1430,234 @@
         <v>53</v>
       </c>
       <c r="C15">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>46174</v>
+        <v>46198</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>46195</v>
+      </c>
+      <c r="K16">
+        <v>12</v>
+      </c>
+      <c r="L16" t="s">
         <v>55</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A17" t="s">
         <v>56</v>
       </c>
-      <c r="C16">
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>46188</v>
+      </c>
+      <c r="K17">
+        <v>5</v>
+      </c>
+      <c r="L17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18">
+        <v>47</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>42</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>46188</v>
+      </c>
+      <c r="K18">
+        <v>5</v>
+      </c>
+      <c r="L18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19">
+        <v>14</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>12</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>46188</v>
+      </c>
+      <c r="K19">
+        <v>5</v>
+      </c>
+      <c r="L19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20">
         <v>50</v>
       </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
         <v>22</v>
       </c>
-      <c r="H16">
+      <c r="H20">
         <v>28</v>
       </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="A17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17">
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21">
         <v>50</v>
       </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
         <v>20</v>
       </c>
-      <c r="H17">
+      <c r="H21">
         <v>30</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="A18" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18">
-        <v>10</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>10</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="A19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19">
-        <v>47</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>10</v>
-      </c>
-      <c r="H19">
-        <v>37</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="A20" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20">
-        <v>14</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>2</v>
-      </c>
-      <c r="H20">
-        <v>12</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="A21" t="s">
-        <v>64</v>
-      </c>
-      <c r="B21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
       <c r="I21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
         <v>67</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1618,16 +1666,16 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
         <v>68</v>
       </c>
@@ -1635,25 +1683,25 @@
         <v>69</v>
       </c>
       <c r="C23">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -1661,10 +1709,10 @@
         <v>70</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1672,46 +1720,40 @@
       <c r="F24">
         <v>0</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.5">
+      <c r="A25" t="s">
         <v>71</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.5">
-      <c r="A25" t="s">
-        <v>36</v>
       </c>
       <c r="B25" t="s">
         <v>72</v>
       </c>
       <c r="C25">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
-      <c r="G25" t="s">
-        <v>71</v>
-      </c>
       <c r="H25">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -1719,7 +1761,7 @@
         <v>73</v>
       </c>
       <c r="C26">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1731,24 +1773,24 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H26">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A27" t="s">
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1760,21 +1802,21 @@
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
         <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1789,7 +1831,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1798,12 +1840,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A29" t="s">
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1818,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1827,12 +1869,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1847,7 +1889,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1856,12 +1898,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1876,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1885,12 +1927,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A32" t="s">
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1905,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -1919,10 +1961,10 @@
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1934,10 +1976,10 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H33">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1948,10 +1990,10 @@
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -1963,10 +2005,10 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -1977,10 +2019,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1992,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2006,10 +2048,10 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2021,10 +2063,10 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2035,10 +2077,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2050,10 +2092,10 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2064,10 +2106,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2079,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2093,10 +2135,10 @@
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2108,10 +2150,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2122,10 +2164,10 @@
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C40">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2137,10 +2179,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H40">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2151,10 +2193,10 @@
         <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2166,10 +2208,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2180,10 +2222,10 @@
         <v>36</v>
       </c>
       <c r="B42" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C42">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2195,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H42">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2209,7 +2251,7 @@
         <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C43">
         <v>5</v>
@@ -2224,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H43">
         <v>5</v>
@@ -2238,7 +2280,7 @@
         <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -2253,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -2267,7 +2309,7 @@
         <v>36</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -2282,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H45">
         <v>4</v>
@@ -2296,7 +2338,7 @@
         <v>36</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C46">
         <v>4</v>
@@ -2311,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H46">
         <v>4</v>
@@ -2322,10 +2364,10 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A47" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -2340,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -2351,10 +2393,10 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A48" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B48" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C48">
         <v>33</v>
@@ -2369,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H48">
         <v>33</v>
@@ -2380,7 +2422,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A49" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
         <v>99</v>
@@ -2398,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -2409,7 +2451,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A50" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="B50" t="s">
         <v>100</v>
@@ -2427,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H50">
         <v>2</v>
@@ -2438,7 +2480,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A51" t="s">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="B51" t="s">
         <v>101</v>
@@ -2456,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H51">
         <v>7</v>
@@ -2485,7 +2527,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -2514,7 +2556,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -2543,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H54">
         <v>2</v>
@@ -2572,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -2601,7 +2643,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H56">
         <v>30</v>
@@ -2630,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H57">
         <v>17</v>
@@ -2659,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H58">
         <v>1</v>
@@ -2688,7 +2730,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H59">
         <v>2</v>
@@ -2717,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H60">
         <v>10</v>
@@ -2746,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H61">
         <v>6</v>
@@ -2775,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H62">
         <v>19</v>
@@ -2804,7 +2846,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H63">
         <v>10</v>
@@ -2833,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H64">
         <v>2</v>
@@ -2862,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H65">
         <v>28</v>
@@ -2891,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H66">
         <v>19</v>
@@ -2920,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -2949,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H68">
         <v>3</v>
@@ -2978,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -3007,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -3018,7 +3060,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B71" t="s">
         <v>130</v>
@@ -3036,7 +3078,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -3047,7 +3089,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A72" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B72" t="s">
         <v>131</v>
@@ -3065,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H72">
         <v>3</v>
@@ -3076,7 +3118,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A73" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B73" t="s">
         <v>132</v>
@@ -3094,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H73">
         <v>3</v>
@@ -3105,7 +3147,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A74" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B74" t="s">
         <v>133</v>
@@ -3123,7 +3165,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H74">
         <v>3</v>
@@ -3134,7 +3176,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A75" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B75" t="s">
         <v>134</v>
@@ -3152,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H75">
         <v>3</v>
@@ -3163,7 +3205,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A76" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B76" t="s">
         <v>135</v>
@@ -3181,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H76">
         <v>5</v>
@@ -3210,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H77">
         <v>1</v>
@@ -3221,13 +3263,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A78" t="s">
+        <v>136</v>
+      </c>
+      <c r="B78" t="s">
         <v>138</v>
       </c>
-      <c r="B78" t="s">
-        <v>139</v>
-      </c>
       <c r="C78">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3239,10 +3281,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H78">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3250,13 +3292,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A79" t="s">
+        <v>139</v>
+      </c>
+      <c r="B79" t="s">
         <v>140</v>
       </c>
-      <c r="B79" t="s">
-        <v>141</v>
-      </c>
       <c r="C79">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3268,10 +3310,10 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H79">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3279,13 +3321,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A80" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B80" t="s">
         <v>142</v>
       </c>
       <c r="C80">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3297,10 +3339,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H80">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3308,13 +3350,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A81" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="B81" t="s">
         <v>143</v>
       </c>
       <c r="C81">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3326,10 +3368,10 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H81">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -3337,13 +3379,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A82" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B82" t="s">
         <v>144</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3355,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H82">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -3366,7 +3408,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B83" t="s">
         <v>145</v>
@@ -3384,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -3395,7 +3437,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A84" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B84" t="s">
         <v>146</v>
@@ -3413,7 +3455,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -3424,7 +3466,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A85" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B85" t="s">
         <v>147</v>
@@ -3442,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -3453,7 +3495,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A86" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B86" t="s">
         <v>148</v>
@@ -3471,7 +3513,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -3482,7 +3524,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A87" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B87" t="s">
         <v>149</v>
@@ -3500,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H87">
         <v>1</v>
@@ -3511,13 +3553,13 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A88" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B88" t="s">
         <v>150</v>
       </c>
       <c r="C88">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3529,10 +3571,10 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H88">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -3540,13 +3582,13 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A89" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B89" t="s">
         <v>151</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3558,10 +3600,10 @@
         <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H89">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -3569,13 +3611,13 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A90" t="s">
+        <v>52</v>
+      </c>
+      <c r="B90" t="s">
         <v>152</v>
       </c>
-      <c r="B90" t="s">
-        <v>153</v>
-      </c>
       <c r="C90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3587,10 +3629,10 @@
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -3598,7 +3640,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A91" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B91" t="s">
         <v>154</v>
@@ -3616,7 +3658,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H91">
         <v>2</v>
@@ -3627,13 +3669,13 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A92" t="s">
+        <v>153</v>
+      </c>
+      <c r="B92" t="s">
         <v>155</v>
       </c>
-      <c r="B92" t="s">
-        <v>156</v>
-      </c>
       <c r="C92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3645,10 +3687,10 @@
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -3656,13 +3698,13 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A93" t="s">
+        <v>156</v>
+      </c>
+      <c r="B93" t="s">
         <v>157</v>
       </c>
-      <c r="B93" t="s">
-        <v>158</v>
-      </c>
       <c r="C93">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3674,10 +3716,10 @@
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H93">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -3685,13 +3727,13 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A94" t="s">
+        <v>158</v>
+      </c>
+      <c r="B94" t="s">
         <v>159</v>
       </c>
-      <c r="B94" t="s">
-        <v>160</v>
-      </c>
       <c r="C94">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3703,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H94">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -3714,11 +3756,11 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A95" t="s">
+        <v>160</v>
+      </c>
+      <c r="B95" t="s">
         <v>161</v>
       </c>
-      <c r="B95" t="s">
-        <v>162</v>
-      </c>
       <c r="C95">
         <v>1</v>
       </c>
@@ -3732,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -3743,13 +3785,13 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A96" t="s">
+        <v>162</v>
+      </c>
+      <c r="B96" t="s">
         <v>163</v>
       </c>
-      <c r="B96" t="s">
-        <v>164</v>
-      </c>
       <c r="C96">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3761,10 +3803,10 @@
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H96">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -3772,13 +3814,13 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A97" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B97" t="s">
         <v>165</v>
       </c>
       <c r="C97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3790,10 +3832,10 @@
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -3807,7 +3849,7 @@
         <v>167</v>
       </c>
       <c r="C98">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3819,10 +3861,10 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H98">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -3830,10 +3872,10 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A99" t="s">
+        <v>166</v>
+      </c>
+      <c r="B99" t="s">
         <v>168</v>
-      </c>
-      <c r="B99" t="s">
-        <v>169</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -3848,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H99">
         <v>2</v>
@@ -3859,10 +3901,10 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A100" t="s">
+        <v>169</v>
+      </c>
+      <c r="B100" t="s">
         <v>170</v>
-      </c>
-      <c r="B100" t="s">
-        <v>171</v>
       </c>
       <c r="C100">
         <v>9</v>
@@ -3877,7 +3919,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H100">
         <v>9</v>
@@ -3888,13 +3930,13 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A101" t="s">
+        <v>171</v>
+      </c>
+      <c r="B101" t="s">
         <v>172</v>
       </c>
-      <c r="B101" t="s">
-        <v>173</v>
-      </c>
       <c r="C101">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3906,10 +3948,10 @@
         <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H101">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -3917,13 +3959,13 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A102" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B102" t="s">
         <v>174</v>
       </c>
       <c r="C102">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3935,10 +3977,10 @@
         <v>0</v>
       </c>
       <c r="G102" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H102">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -3952,7 +3994,7 @@
         <v>176</v>
       </c>
       <c r="C103">
-        <v>170</v>
+        <v>16</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3964,10 +4006,10 @@
         <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H103">
-        <v>170</v>
+        <v>16</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -3975,13 +4017,13 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A104" t="s">
+        <v>175</v>
+      </c>
+      <c r="B104" t="s">
         <v>177</v>
       </c>
-      <c r="B104" t="s">
-        <v>178</v>
-      </c>
       <c r="C104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -3993,10 +4035,10 @@
         <v>0</v>
       </c>
       <c r="G104" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -4004,13 +4046,13 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A105" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B105" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C105">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -4022,10 +4064,10 @@
         <v>0</v>
       </c>
       <c r="G105" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H105">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -4033,13 +4075,13 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A106" t="s">
-        <v>62</v>
+        <v>179</v>
       </c>
       <c r="B106" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -4051,10 +4093,10 @@
         <v>0</v>
       </c>
       <c r="G106" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H106">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -4062,7 +4104,7 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A107" t="s">
-        <v>62</v>
+        <v>181</v>
       </c>
       <c r="B107" t="s">
         <v>182</v>
@@ -4080,12 +4122,99 @@
         <v>0</v>
       </c>
       <c r="G107" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H107">
         <v>1</v>
       </c>
       <c r="I107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A108" t="s">
+        <v>183</v>
+      </c>
+      <c r="B108" t="s">
+        <v>184</v>
+      </c>
+      <c r="C108">
+        <v>15</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108" t="s">
+        <v>74</v>
+      </c>
+      <c r="H108">
+        <v>15</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A109" t="s">
+        <v>61</v>
+      </c>
+      <c r="B109" t="s">
+        <v>185</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109" t="s">
+        <v>74</v>
+      </c>
+      <c r="H109">
+        <v>1</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A110" t="s">
+        <v>61</v>
+      </c>
+      <c r="B110" t="s">
+        <v>186</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110" t="s">
+        <v>74</v>
+      </c>
+      <c r="H110">
+        <v>1</v>
+      </c>
+      <c r="I110">
         <v>0</v>
       </c>
     </row>

--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB90A3532DBA91BF0C4C5F0A21671D817AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C15AFFE8-56E3-4B1D-A9FE-1D76E16B4AE6}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9397DBCE577F9E6FD5D71B97270D81383" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7728E6E-91BF-4870-AD8C-756058ECFD99}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="PO_StatusQry" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$110</definedName>
+    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$112</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="191">
   <si>
     <t>CustName</t>
   </si>
@@ -70,7 +70,7 @@
     <t>4516351202_ASEWH</t>
   </si>
   <si>
-    <t>OverDue by 285 days</t>
+    <t>OverDue by 299 days</t>
   </si>
   <si>
     <t>Texas Instruments SCT</t>
@@ -79,7 +79,7 @@
     <t>4516351202_SCT</t>
   </si>
   <si>
-    <t>Varies (2025-08-29 → 2026-06-11)</t>
+    <t>Varies (2025-08-29 → 2026-07-06)</t>
   </si>
   <si>
     <t>Texas Instruments Taiwan</t>
@@ -94,19 +94,40 @@
     <t>4516351202_TICL-PR</t>
   </si>
   <si>
-    <t>Varies (2025-08-29 → 2026-05-25)</t>
-  </si>
-  <si>
     <t>TEXAS INSTRUMENTS  MALAYSIA</t>
   </si>
   <si>
     <t>Global PO 4516351202</t>
   </si>
   <si>
-    <t>OverDue by 121 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-02-09 → 2026-06-09)</t>
+    <t>OverDue by 135 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-02-09 → 2026-07-07)</t>
+  </si>
+  <si>
+    <t>ARDENTEC CORPORATION</t>
+  </si>
+  <si>
+    <t>4516351202_ARD</t>
+  </si>
+  <si>
+    <t>OverDue by 89 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-03-27 → 2026-06-18)</t>
+  </si>
+  <si>
+    <t>Analog Devices Gen. Trias Inc. (ADGT)</t>
+  </si>
+  <si>
+    <t>47270551</t>
+  </si>
+  <si>
+    <t>OverDue by 58 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-04-27 → 2026-06-30)</t>
   </si>
   <si>
     <t>TI (Philippines) Inc.</t>
@@ -115,34 +136,70 @@
     <t>4516351202_TIPI</t>
   </si>
   <si>
-    <t>OverDue by 90 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-03-12 → 2026-06-09)</t>
-  </si>
-  <si>
-    <t>ARDENTEC CORPORATION</t>
-  </si>
-  <si>
-    <t>4516351202_ARD</t>
-  </si>
-  <si>
-    <t>OverDue by 75 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-03-27 → 2026-06-18)</t>
-  </si>
-  <si>
-    <t>Analog Devices Gen. Trias Inc. (ADGT)</t>
-  </si>
-  <si>
-    <t>47270551</t>
-  </si>
-  <si>
-    <t>OverDue by 44 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-04-27 → 2026-06-30)</t>
+    <t>Varies (2026-04-27 → 2026-06-25)</t>
+  </si>
+  <si>
+    <t>47318424</t>
+  </si>
+  <si>
+    <t>OverDue by 15 days</t>
+  </si>
+  <si>
+    <t>ASE CO., LTD - PHILIPPINES BRANCH 01-075</t>
+  </si>
+  <si>
+    <t>MO262002496</t>
+  </si>
+  <si>
+    <t>OverDue by 9 days</t>
+  </si>
+  <si>
+    <t>UTAC Thai Limited ( UTL 3)</t>
+  </si>
+  <si>
+    <t>4516351202_UTL</t>
+  </si>
+  <si>
+    <t>NXP Malaysia Sdn. Bhd.</t>
+  </si>
+  <si>
+    <t>3T/PO262333</t>
+  </si>
+  <si>
+    <t>OverDue by 2 days</t>
+  </si>
+  <si>
+    <t>Lingsen Precision Industries Ltd.</t>
+  </si>
+  <si>
+    <t>4516446856</t>
+  </si>
+  <si>
+    <t>19 days before Due</t>
+  </si>
+  <si>
+    <t>TBA_NXP</t>
+  </si>
+  <si>
+    <t>14 days before Due</t>
+  </si>
+  <si>
+    <t>Varies (2026-07-08 → 2026-07-14)</t>
+  </si>
+  <si>
+    <t>47301012</t>
+  </si>
+  <si>
+    <t>12 days before Due</t>
+  </si>
+  <si>
+    <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
+  </si>
+  <si>
+    <t>4516351202_ASESH</t>
+  </si>
+  <si>
+    <t>6 days before Due</t>
   </si>
   <si>
     <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
@@ -151,187 +208,148 @@
     <t>4516351202_MIHO</t>
   </si>
   <si>
-    <t>OverDue by 8 days</t>
-  </si>
-  <si>
-    <t>NXP Malaysia Sdn. Bhd.</t>
-  </si>
-  <si>
-    <t>TBA_NXP</t>
-  </si>
-  <si>
-    <t>OverDue by 6 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-06-04 → 2026-06-16)</t>
-  </si>
-  <si>
-    <t>47318424</t>
-  </si>
-  <si>
-    <t>OverDue by 1 days</t>
+    <t>5 days before Due</t>
+  </si>
+  <si>
+    <t>STMicroelectronics, Inc.</t>
+  </si>
+  <si>
+    <t>4010018600</t>
+  </si>
+  <si>
+    <t>1 days before Due</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
+  </si>
+  <si>
+    <t>4516351202_TII</t>
+  </si>
+  <si>
+    <t>Texas Instruments DMOS5</t>
+  </si>
+  <si>
+    <t>4516351202_DMOS5</t>
+  </si>
+  <si>
+    <t>Texas Instruments LFAB</t>
+  </si>
+  <si>
+    <t>4516351202_LFAB</t>
+  </si>
+  <si>
+    <t>Texas Instruments Taiwan Limited</t>
+  </si>
+  <si>
+    <t>4516450237</t>
+  </si>
+  <si>
+    <t>ROCHESTER ELECTRONICS</t>
+  </si>
+  <si>
+    <t>252395</t>
+  </si>
+  <si>
+    <t>47188646</t>
+  </si>
+  <si>
+    <t>Completed PO</t>
+  </si>
+  <si>
+    <t>47218149</t>
+  </si>
+  <si>
+    <t>47245848</t>
+  </si>
+  <si>
+    <t>47245933</t>
+  </si>
+  <si>
+    <t>47253728</t>
+  </si>
+  <si>
+    <t>47264622</t>
+  </si>
+  <si>
+    <t>47274630</t>
+  </si>
+  <si>
+    <t>47276474</t>
+  </si>
+  <si>
+    <t>47283634</t>
+  </si>
+  <si>
+    <t>47283654</t>
+  </si>
+  <si>
+    <t>47286185</t>
+  </si>
+  <si>
+    <t>47289023</t>
+  </si>
+  <si>
+    <t>47290167</t>
+  </si>
+  <si>
+    <t>47292239</t>
+  </si>
+  <si>
+    <t>47292914</t>
+  </si>
+  <si>
+    <t>47296581</t>
+  </si>
+  <si>
+    <t>47296806</t>
+  </si>
+  <si>
+    <t>47301646</t>
+  </si>
+  <si>
+    <t>47304169</t>
+  </si>
+  <si>
+    <t>47324752</t>
+  </si>
+  <si>
+    <t>47345978</t>
+  </si>
+  <si>
+    <t>47352135</t>
+  </si>
+  <si>
+    <t>TBD_SAMPLE</t>
+  </si>
+  <si>
+    <t>ANALOG DEVICES INC. CAMAS</t>
+  </si>
+  <si>
+    <t>47259467</t>
+  </si>
+  <si>
+    <t>Ardentec Korea Co., Ltd.</t>
+  </si>
+  <si>
+    <t>4516351202_ATK</t>
   </si>
   <si>
     <t>AVAGO TECHNOLOGIES_x000D_
 INTERNATIONAL SALES PTE LTD</t>
   </si>
   <si>
+    <t>8541541216</t>
+  </si>
+  <si>
+    <t>8541550629</t>
+  </si>
+  <si>
+    <t>8541550824</t>
+  </si>
+  <si>
     <t>8541563942</t>
   </si>
   <si>
-    <t>15 days before Due</t>
-  </si>
-  <si>
-    <t>STMicroelectronics, Inc.</t>
-  </si>
-  <si>
-    <t>4010018600</t>
-  </si>
-  <si>
-    <t>3T/PO262333</t>
-  </si>
-  <si>
-    <t>12 days before Due</t>
-  </si>
-  <si>
-    <t>ASE CO., LTD - PHILIPPINES BRANCH 01-075</t>
-  </si>
-  <si>
-    <t>MO262002496</t>
-  </si>
-  <si>
-    <t>5 days before Due</t>
-  </si>
-  <si>
-    <t>Texas Instruments DMOS5</t>
-  </si>
-  <si>
-    <t>4516351202_DMOS5</t>
-  </si>
-  <si>
-    <t>UTAC Thai Limited ( UTL 3)</t>
-  </si>
-  <si>
-    <t>4516351202_UTL</t>
-  </si>
-  <si>
-    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
-  </si>
-  <si>
-    <t>4516351202_TII</t>
-  </si>
-  <si>
-    <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
-  </si>
-  <si>
-    <t>4516351202_ASESH</t>
-  </si>
-  <si>
-    <t>47301012</t>
-  </si>
-  <si>
-    <t>Texas Instruments LFAB</t>
-  </si>
-  <si>
-    <t>4516351202_LFAB</t>
-  </si>
-  <si>
-    <t>47352135</t>
-  </si>
-  <si>
-    <t>ROCHESTER ELECTRONICS</t>
-  </si>
-  <si>
-    <t>252395</t>
-  </si>
-  <si>
-    <t>47188646</t>
-  </si>
-  <si>
-    <t>Completed PO</t>
-  </si>
-  <si>
-    <t>47218149</t>
-  </si>
-  <si>
-    <t>47245848</t>
-  </si>
-  <si>
-    <t>47245933</t>
-  </si>
-  <si>
-    <t>47253728</t>
-  </si>
-  <si>
-    <t>47264622</t>
-  </si>
-  <si>
-    <t>47274630</t>
-  </si>
-  <si>
-    <t>47276474</t>
-  </si>
-  <si>
-    <t>47283634</t>
-  </si>
-  <si>
-    <t>47283654</t>
-  </si>
-  <si>
-    <t>47286185</t>
-  </si>
-  <si>
-    <t>47289023</t>
-  </si>
-  <si>
-    <t>47290167</t>
-  </si>
-  <si>
-    <t>47292239</t>
-  </si>
-  <si>
-    <t>47292914</t>
-  </si>
-  <si>
-    <t>47296581</t>
-  </si>
-  <si>
-    <t>47296806</t>
-  </si>
-  <si>
-    <t>47301646</t>
-  </si>
-  <si>
-    <t>47304169</t>
-  </si>
-  <si>
-    <t>47324752</t>
-  </si>
-  <si>
-    <t>47345978</t>
-  </si>
-  <si>
-    <t>ANALOG DEVICES INC. CAMAS</t>
-  </si>
-  <si>
-    <t>47259467</t>
-  </si>
-  <si>
-    <t>Ardentec Korea Co., Ltd.</t>
-  </si>
-  <si>
-    <t>4516351202_ATK</t>
-  </si>
-  <si>
-    <t>8541541216</t>
-  </si>
-  <si>
-    <t>8541550629</t>
-  </si>
-  <si>
-    <t>8541550824</t>
-  </si>
-  <si>
     <t>Boston Semi Equipment</t>
   </si>
   <si>
@@ -377,6 +395,9 @@
     <t>4910173913</t>
   </si>
   <si>
+    <t>TBD_EVALUATION</t>
+  </si>
+  <si>
     <t>Hana Semiconductor (Ayutthaya) Co., Ltd (HNT)</t>
   </si>
   <si>
@@ -392,15 +413,9 @@
     <t>ES072525</t>
   </si>
   <si>
-    <t>Lingsen Precision Industries Ltd.</t>
-  </si>
-  <si>
     <t>4516260169</t>
   </si>
   <si>
-    <t>4516446856</t>
-  </si>
-  <si>
     <t>LPI-2507174</t>
   </si>
   <si>
@@ -551,12 +566,6 @@
     <t>4516351202_SFAB</t>
   </si>
   <si>
-    <t>Texas Instruments Taiwan Limited</t>
-  </si>
-  <si>
-    <t>4516450237</t>
-  </si>
-  <si>
     <t>4516519979</t>
   </si>
   <si>
@@ -587,7 +596,7 @@
     <t>43156228</t>
   </si>
   <si>
-    <t>Last updated: 2026-06-10 13:25:45</t>
+    <t>Last updated: 2026-06-24 11:38:42</t>
   </si>
 </sst>
 </file>
@@ -932,12 +941,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M110"/>
+  <dimension ref="A1:M112"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.5">
@@ -1010,7 +1019,7 @@
         <v>45898</v>
       </c>
       <c r="K3">
-        <v>-285</v>
+        <v>-299</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -1027,25 +1036,25 @@
         <v>333</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" s="1">
         <v>45898</v>
       </c>
       <c r="K4">
-        <v>-285</v>
+        <v>-299</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -1083,7 +1092,7 @@
         <v>45898</v>
       </c>
       <c r="K5">
-        <v>-285</v>
+        <v>-299</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -1103,77 +1112,77 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="H6">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J6" s="1">
         <v>45898</v>
       </c>
       <c r="K6">
-        <v>-285</v>
+        <v>-299</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
       </c>
       <c r="M6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
       <c r="C7">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="1">
         <v>46062</v>
       </c>
       <c r="K7">
-        <v>-121</v>
+        <v>-135</v>
       </c>
       <c r="L7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" t="s">
         <v>26</v>
-      </c>
-      <c r="M7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
         <v>28</v>
       </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
       <c r="C8">
-        <v>626</v>
+        <v>259</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1182,381 +1191,381 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>586</v>
+        <v>244</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J8" s="1">
-        <v>46093</v>
+        <v>46108</v>
       </c>
       <c r="K8">
-        <v>-90</v>
+        <v>-89</v>
       </c>
       <c r="L8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s">
         <v>30</v>
-      </c>
-      <c r="M8" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
         <v>32</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9">
+        <v>45</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>18</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>27</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>46139</v>
+      </c>
+      <c r="K9">
+        <v>-58</v>
+      </c>
+      <c r="L9" t="s">
         <v>33</v>
       </c>
-      <c r="C9">
-        <v>259</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>17</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>242</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1">
-        <v>46108</v>
-      </c>
-      <c r="K9">
-        <v>-75</v>
-      </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>34</v>
-      </c>
-      <c r="M9" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
         <v>36</v>
       </c>
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
       <c r="C10">
-        <v>45</v>
+        <v>646</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H10">
-        <v>27</v>
+        <v>612</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J10" s="1">
         <v>46139</v>
       </c>
       <c r="K10">
-        <v>-44</v>
+        <v>-58</v>
       </c>
       <c r="L10" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C11">
-        <v>162</v>
+        <v>9</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>46175</v>
+        <v>46182</v>
       </c>
       <c r="K11">
-        <v>-8</v>
+        <v>-15</v>
       </c>
       <c r="L11" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C12">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>46188</v>
+      </c>
+      <c r="K12">
+        <v>-9</v>
+      </c>
+      <c r="L12" t="s">
         <v>42</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>46177</v>
-      </c>
-      <c r="K12">
-        <v>-6</v>
-      </c>
-      <c r="L12" t="s">
-        <v>45</v>
-      </c>
-      <c r="M12" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C13">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="L13" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>46198</v>
+        <v>46195</v>
       </c>
       <c r="K14">
-        <v>15</v>
+        <v>-2</v>
       </c>
       <c r="L14" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>46198</v>
+        <v>46216</v>
       </c>
       <c r="K15">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>46195</v>
+        <v>46211</v>
       </c>
       <c r="K16">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L16" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="M16" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>46188</v>
+        <v>46209</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L17" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C18">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>46188</v>
+        <v>46203</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L18" t="s">
         <v>58</v>
@@ -1564,63 +1573,72 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C19">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>12</v>
+        <v>159</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>46188</v>
+        <v>46202</v>
       </c>
       <c r="K19">
         <v>5</v>
       </c>
       <c r="L19" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" t="s">
         <v>63</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1">
+        <v>46198</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20" t="s">
         <v>64</v>
-      </c>
-      <c r="C20">
-        <v>50</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>22</v>
-      </c>
-      <c r="H20">
-        <v>28</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.5">
@@ -1640,10 +1658,10 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H21">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1651,13 +1669,13 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C22">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1666,10 +1684,10 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1677,10 +1695,10 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -1703,25 +1721,25 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1729,10 +1747,10 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C25">
         <v>70</v>
@@ -1755,10 +1773,10 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C26">
         <v>19</v>
@@ -1773,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H26">
         <v>19</v>
@@ -1784,13 +1802,13 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C27">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1802,10 +1820,10 @@
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H27">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1813,10 +1831,10 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1831,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1842,10 +1860,10 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1860,7 +1878,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1871,10 +1889,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1889,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1900,10 +1918,10 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1918,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1929,10 +1947,10 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A32" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1947,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -1958,10 +1976,10 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1976,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -1987,10 +2005,10 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C34">
         <v>6</v>
@@ -2005,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H34">
         <v>6</v>
@@ -2016,10 +2034,10 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C35">
         <v>2</v>
@@ -2034,7 +2052,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H35">
         <v>2</v>
@@ -2045,10 +2063,10 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -2063,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -2074,10 +2092,10 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C37">
         <v>4</v>
@@ -2092,7 +2110,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H37">
         <v>4</v>
@@ -2103,10 +2121,10 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -2121,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -2132,10 +2150,10 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -2150,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H39">
         <v>2</v>
@@ -2161,10 +2179,10 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -2179,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -2190,10 +2208,10 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C41">
         <v>9</v>
@@ -2208,7 +2226,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H41">
         <v>9</v>
@@ -2219,10 +2237,10 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A42" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C42">
         <v>4</v>
@@ -2237,7 +2255,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H42">
         <v>4</v>
@@ -2248,10 +2266,10 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B43" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C43">
         <v>5</v>
@@ -2266,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H43">
         <v>5</v>
@@ -2277,10 +2295,10 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -2295,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -2306,10 +2324,10 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A45" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -2324,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H45">
         <v>4</v>
@@ -2335,10 +2353,10 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A46" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C46">
         <v>4</v>
@@ -2353,7 +2371,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H46">
         <v>4</v>
@@ -2364,13 +2382,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A47" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2382,10 +2400,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2393,13 +2411,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A48" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="B48" t="s">
         <v>98</v>
       </c>
       <c r="C48">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2411,10 +2429,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H48">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2422,10 +2440,10 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="B49" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -2440,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -2451,13 +2469,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="B50" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2469,10 +2487,10 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H50">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2480,13 +2498,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2498,10 +2516,10 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H51">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2509,13 +2527,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B52" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2527,10 +2545,10 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2538,13 +2556,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A53" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B53" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2556,10 +2574,10 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2567,13 +2585,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A54" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B54" t="s">
         <v>107</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2585,10 +2603,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2596,10 +2614,10 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B55" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -2614,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -2625,13 +2643,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B56" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C56">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2643,10 +2661,10 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H56">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2654,13 +2672,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B57" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C57">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2672,10 +2690,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H57">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2683,10 +2701,10 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B58" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -2701,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H58">
         <v>1</v>
@@ -2712,13 +2730,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A59" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B59" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C59">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2730,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H59">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2741,13 +2759,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A60" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B60" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C60">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2759,10 +2777,10 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H60">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2773,10 +2791,10 @@
         <v>115</v>
       </c>
       <c r="B61" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C61">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2788,10 +2806,10 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H61">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2799,13 +2817,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A62" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B62" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C62">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2817,10 +2835,10 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H62">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2828,10 +2846,10 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A63" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B63" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C63">
         <v>10</v>
@@ -2846,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H63">
         <v>10</v>
@@ -2857,13 +2875,13 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A64" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B64" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2875,10 +2893,10 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H64">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -2886,13 +2904,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A65" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B65" t="s">
         <v>123</v>
       </c>
       <c r="C65">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2904,10 +2922,10 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H65">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -2915,10 +2933,10 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A66" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B66" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C66">
         <v>19</v>
@@ -2933,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H66">
         <v>19</v>
@@ -2944,13 +2962,13 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A67" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B67" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2962,10 +2980,10 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -2973,13 +2991,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A68" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B68" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2991,10 +3009,10 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3002,13 +3020,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="B69" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -3020,10 +3038,10 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -3031,10 +3049,10 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A70" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="B70" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -3049,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -3060,13 +3078,13 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
-        <v>43</v>
+        <v>131</v>
       </c>
       <c r="B71" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -3078,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3089,13 +3107,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A72" t="s">
-        <v>43</v>
+        <v>131</v>
       </c>
       <c r="B72" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3107,10 +3125,10 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3118,13 +3136,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A73" t="s">
-        <v>43</v>
+        <v>131</v>
       </c>
       <c r="B73" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -3136,10 +3154,10 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3147,13 +3165,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A74" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3165,10 +3183,10 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3176,10 +3194,10 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A75" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B75" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C75">
         <v>3</v>
@@ -3194,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H75">
         <v>3</v>
@@ -3205,13 +3223,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A76" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C76">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3223,10 +3241,10 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H76">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3234,13 +3252,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A77" t="s">
-        <v>136</v>
+        <v>45</v>
       </c>
       <c r="B77" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3252,10 +3270,10 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3263,13 +3281,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A78" t="s">
-        <v>136</v>
+        <v>45</v>
       </c>
       <c r="B78" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C78">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3281,10 +3299,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H78">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3292,13 +3310,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A79" t="s">
-        <v>139</v>
+        <v>45</v>
       </c>
       <c r="B79" t="s">
         <v>140</v>
       </c>
       <c r="C79">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3310,10 +3328,10 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H79">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3327,7 +3345,7 @@
         <v>142</v>
       </c>
       <c r="C80">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3339,10 +3357,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H80">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3368,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H81">
         <v>5</v>
@@ -3379,13 +3397,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A82" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="B82" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C82">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3397,10 +3415,10 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H82">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -3408,13 +3426,13 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="B83" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -3426,10 +3444,10 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H83">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -3437,13 +3455,13 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A84" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="B84" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3455,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H84">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -3466,13 +3484,13 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A85" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B85" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3484,10 +3502,10 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H85">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -3495,10 +3513,10 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A86" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B86" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -3513,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -3524,10 +3542,10 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A87" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B87" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -3542,7 +3560,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H87">
         <v>1</v>
@@ -3553,10 +3571,10 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A88" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B88" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -3571,7 +3589,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H88">
         <v>1</v>
@@ -3582,13 +3600,13 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A89" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B89" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C89">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3600,10 +3618,10 @@
         <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H89">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -3611,10 +3629,10 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A90" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B90" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -3629,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H90">
         <v>1</v>
@@ -3640,13 +3658,13 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A91" t="s">
-        <v>153</v>
+        <v>62</v>
       </c>
       <c r="B91" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3658,10 +3676,10 @@
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -3669,13 +3687,13 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A92" t="s">
-        <v>153</v>
+        <v>62</v>
       </c>
       <c r="B92" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C92">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3687,10 +3705,10 @@
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H92">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -3698,13 +3716,13 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A93" t="s">
-        <v>156</v>
+        <v>62</v>
       </c>
       <c r="B93" t="s">
         <v>157</v>
       </c>
       <c r="C93">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3716,10 +3734,10 @@
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H93">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -3733,7 +3751,7 @@
         <v>159</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3745,10 +3763,10 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -3756,13 +3774,13 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A95" t="s">
+        <v>158</v>
+      </c>
+      <c r="B95" t="s">
         <v>160</v>
       </c>
-      <c r="B95" t="s">
-        <v>161</v>
-      </c>
       <c r="C95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3774,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -3785,13 +3803,13 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A96" t="s">
+        <v>161</v>
+      </c>
+      <c r="B96" t="s">
         <v>162</v>
       </c>
-      <c r="B96" t="s">
-        <v>163</v>
-      </c>
       <c r="C96">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3803,10 +3821,10 @@
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H96">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -3814,11 +3832,11 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A97" t="s">
+        <v>163</v>
+      </c>
+      <c r="B97" t="s">
         <v>164</v>
       </c>
-      <c r="B97" t="s">
-        <v>165</v>
-      </c>
       <c r="C97">
         <v>1</v>
       </c>
@@ -3832,7 +3850,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -3843,13 +3861,13 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A98" t="s">
+        <v>165</v>
+      </c>
+      <c r="B98" t="s">
         <v>166</v>
       </c>
-      <c r="B98" t="s">
-        <v>167</v>
-      </c>
       <c r="C98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3861,10 +3879,10 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -3872,13 +3890,13 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A99" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B99" t="s">
         <v>168</v>
       </c>
       <c r="C99">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3890,10 +3908,10 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H99">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -3907,7 +3925,7 @@
         <v>170</v>
       </c>
       <c r="C100">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3919,10 +3937,10 @@
         <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H100">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -3948,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H101">
         <v>2</v>
@@ -3959,13 +3977,13 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A102" t="s">
+        <v>171</v>
+      </c>
+      <c r="B102" t="s">
         <v>173</v>
       </c>
-      <c r="B102" t="s">
-        <v>174</v>
-      </c>
       <c r="C102">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3977,10 +3995,10 @@
         <v>0</v>
       </c>
       <c r="G102" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H102">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -3988,13 +4006,13 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A103" t="s">
+        <v>174</v>
+      </c>
+      <c r="B103" t="s">
         <v>175</v>
       </c>
-      <c r="B103" t="s">
-        <v>176</v>
-      </c>
       <c r="C103">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -4006,10 +4024,10 @@
         <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H103">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -4017,7 +4035,7 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A104" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B104" t="s">
         <v>177</v>
@@ -4035,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H104">
         <v>2</v>
@@ -4046,13 +4064,13 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A105" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B105" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C105">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -4064,10 +4082,10 @@
         <v>0</v>
       </c>
       <c r="G105" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H105">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -4075,13 +4093,13 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A106" t="s">
-        <v>179</v>
+        <v>71</v>
       </c>
       <c r="B106" t="s">
         <v>180</v>
       </c>
       <c r="C106">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -4093,10 +4111,10 @@
         <v>0</v>
       </c>
       <c r="G106" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H106">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -4104,13 +4122,13 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A107" t="s">
+        <v>71</v>
+      </c>
+      <c r="B107" t="s">
         <v>181</v>
       </c>
-      <c r="B107" t="s">
-        <v>182</v>
-      </c>
       <c r="C107">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -4122,10 +4140,10 @@
         <v>0</v>
       </c>
       <c r="G107" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H107">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I107">
         <v>0</v>
@@ -4133,13 +4151,13 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A108" t="s">
+        <v>182</v>
+      </c>
+      <c r="B108" t="s">
         <v>183</v>
       </c>
-      <c r="B108" t="s">
-        <v>184</v>
-      </c>
       <c r="C108">
-        <v>15</v>
+        <v>170</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -4151,10 +4169,10 @@
         <v>0</v>
       </c>
       <c r="G108" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H108">
-        <v>15</v>
+        <v>170</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -4162,7 +4180,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A109" t="s">
-        <v>61</v>
+        <v>184</v>
       </c>
       <c r="B109" t="s">
         <v>185</v>
@@ -4180,7 +4198,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H109">
         <v>1</v>
@@ -4191,13 +4209,13 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A110" t="s">
-        <v>61</v>
+        <v>186</v>
       </c>
       <c r="B110" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -4209,12 +4227,70 @@
         <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H110">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A111" t="s">
+        <v>43</v>
+      </c>
+      <c r="B111" t="s">
+        <v>188</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111" t="s">
+        <v>76</v>
+      </c>
+      <c r="H111">
+        <v>1</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A112" t="s">
+        <v>43</v>
+      </c>
+      <c r="B112" t="s">
+        <v>189</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112" t="s">
+        <v>76</v>
+      </c>
+      <c r="H112">
+        <v>1</v>
+      </c>
+      <c r="I112">
         <v>0</v>
       </c>
     </row>

--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB9397DBCE577F9E6FD5D71B97270D81383" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7728E6E-91BF-4870-AD8C-756058ECFD99}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB98E9D3AB8AB9AE35E7DB6955471D9EBD6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{172113FB-37B3-46B8-A13E-1B1DEB003088}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="PO_StatusQry" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$112</definedName>
+    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$118</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="197">
   <si>
     <t>CustName</t>
   </si>
@@ -70,7 +70,7 @@
     <t>4516351202_ASEWH</t>
   </si>
   <si>
-    <t>OverDue by 299 days</t>
+    <t>OverDue by 312 days</t>
   </si>
   <si>
     <t>Texas Instruments SCT</t>
@@ -94,13 +94,16 @@
     <t>4516351202_TICL-PR</t>
   </si>
   <si>
+    <t>Varies (2025-08-29 → 2026-07-16)</t>
+  </si>
+  <si>
     <t>TEXAS INSTRUMENTS  MALAYSIA</t>
   </si>
   <si>
     <t>Global PO 4516351202</t>
   </si>
   <si>
-    <t>OverDue by 135 days</t>
+    <t>OverDue by 148 days</t>
   </si>
   <si>
     <t>Varies (2026-02-09 → 2026-07-07)</t>
@@ -112,10 +115,10 @@
     <t>4516351202_ARD</t>
   </si>
   <si>
-    <t>OverDue by 89 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-03-27 → 2026-06-18)</t>
+    <t>OverDue by 102 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-03-27 → 2026-05-19)</t>
   </si>
   <si>
     <t>Analog Devices Gen. Trias Inc. (ADGT)</t>
@@ -124,7 +127,7 @@
     <t>47270551</t>
   </si>
   <si>
-    <t>OverDue by 58 days</t>
+    <t>OverDue by 71 days</t>
   </si>
   <si>
     <t>Varies (2026-04-27 → 2026-06-30)</t>
@@ -136,22 +139,97 @@
     <t>4516351202_TIPI</t>
   </si>
   <si>
-    <t>Varies (2026-04-27 → 2026-06-25)</t>
+    <t>Varies (2026-04-27 → 2026-07-13)</t>
   </si>
   <si>
     <t>47318424</t>
   </si>
   <si>
+    <t>OverDue by 28 days</t>
+  </si>
+  <si>
+    <t>ASE CO., LTD - PHILIPPINES BRANCH 01-075</t>
+  </si>
+  <si>
+    <t>MO262002496</t>
+  </si>
+  <si>
+    <t>OverDue by 22 days</t>
+  </si>
+  <si>
+    <t>NXP Malaysia Sdn. Bhd.</t>
+  </si>
+  <si>
+    <t>3T/PO262333</t>
+  </si>
+  <si>
     <t>OverDue by 15 days</t>
   </si>
   <si>
-    <t>ASE CO., LTD - PHILIPPINES BRANCH 01-075</t>
-  </si>
-  <si>
-    <t>MO262002496</t>
-  </si>
-  <si>
-    <t>OverDue by 9 days</t>
+    <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
+  </si>
+  <si>
+    <t>4516351202_ASESH</t>
+  </si>
+  <si>
+    <t>OverDue by 7 days</t>
+  </si>
+  <si>
+    <t>47301012</t>
+  </si>
+  <si>
+    <t>OverDue by 1 days</t>
+  </si>
+  <si>
+    <t>3T/PO262338</t>
+  </si>
+  <si>
+    <t>17 days before Due</t>
+  </si>
+  <si>
+    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
+  </si>
+  <si>
+    <t>4516351202_MIHO</t>
+  </si>
+  <si>
+    <t>13 days before Due</t>
+  </si>
+  <si>
+    <t>TBA_NXP</t>
+  </si>
+  <si>
+    <t>7 days before Due</t>
+  </si>
+  <si>
+    <t>Lingsen Precision Industries Ltd.</t>
+  </si>
+  <si>
+    <t>4516446856</t>
+  </si>
+  <si>
+    <t>6 days before Due</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
+  </si>
+  <si>
+    <t>4516351202_TII</t>
+  </si>
+  <si>
+    <t>47364135</t>
+  </si>
+  <si>
+    <t>Texas Instruments DMOS5</t>
+  </si>
+  <si>
+    <t>4516351202_DMOS5</t>
+  </si>
+  <si>
+    <t>Texas Instruments LFAB</t>
+  </si>
+  <si>
+    <t>4516351202_LFAB</t>
   </si>
   <si>
     <t>UTAC Thai Limited ( UTL 3)</t>
@@ -160,82 +238,19 @@
     <t>4516351202_UTL</t>
   </si>
   <si>
-    <t>NXP Malaysia Sdn. Bhd.</t>
-  </si>
-  <si>
-    <t>3T/PO262333</t>
-  </si>
-  <si>
-    <t>OverDue by 2 days</t>
-  </si>
-  <si>
-    <t>Lingsen Precision Industries Ltd.</t>
-  </si>
-  <si>
-    <t>4516446856</t>
-  </si>
-  <si>
-    <t>19 days before Due</t>
-  </si>
-  <si>
-    <t>TBA_NXP</t>
-  </si>
-  <si>
-    <t>14 days before Due</t>
-  </si>
-  <si>
-    <t>Varies (2026-07-08 → 2026-07-14)</t>
-  </si>
-  <si>
-    <t>47301012</t>
-  </si>
-  <si>
-    <t>12 days before Due</t>
-  </si>
-  <si>
-    <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
-  </si>
-  <si>
-    <t>4516351202_ASESH</t>
-  </si>
-  <si>
-    <t>6 days before Due</t>
-  </si>
-  <si>
-    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
-  </si>
-  <si>
-    <t>4516351202_MIHO</t>
-  </si>
-  <si>
-    <t>5 days before Due</t>
-  </si>
-  <si>
-    <t>STMicroelectronics, Inc.</t>
-  </si>
-  <si>
-    <t>4010018600</t>
-  </si>
-  <si>
-    <t>1 days before Due</t>
-  </si>
-  <si>
-    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
-  </si>
-  <si>
-    <t>4516351202_TII</t>
-  </si>
-  <si>
-    <t>Texas Instruments DMOS5</t>
-  </si>
-  <si>
-    <t>4516351202_DMOS5</t>
-  </si>
-  <si>
-    <t>Texas Instruments LFAB</t>
-  </si>
-  <si>
-    <t>4516351202_LFAB</t>
+    <t>47361669</t>
+  </si>
+  <si>
+    <t>47362207</t>
+  </si>
+  <si>
+    <t>47362715</t>
+  </si>
+  <si>
+    <t>ROCHESTER ELECTRONICS</t>
+  </si>
+  <si>
+    <t>252395</t>
   </si>
   <si>
     <t>Texas Instruments Taiwan Limited</t>
@@ -244,12 +259,6 @@
     <t>4516450237</t>
   </si>
   <si>
-    <t>ROCHESTER ELECTRONICS</t>
-  </si>
-  <si>
-    <t>252395</t>
-  </si>
-  <si>
     <t>47188646</t>
   </si>
   <si>
@@ -317,6 +326,9 @@
   </si>
   <si>
     <t>47352135</t>
+  </si>
+  <si>
+    <t>47361598</t>
   </si>
   <si>
     <t>TBD_SAMPLE</t>
@@ -473,6 +485,9 @@
     <t>4020007647</t>
   </si>
   <si>
+    <t>STMicroelectronics, Inc.</t>
+  </si>
+  <si>
     <t>3030012690</t>
   </si>
   <si>
@@ -494,6 +509,9 @@
     <t>4010018238</t>
   </si>
   <si>
+    <t>4010018600</t>
+  </si>
+  <si>
     <t>4330007739</t>
   </si>
   <si>
@@ -596,7 +614,7 @@
     <t>43156228</t>
   </si>
   <si>
-    <t>Last updated: 2026-06-24 11:38:42</t>
+    <t>Last updated: 2026-07-07 09:24:17</t>
   </si>
 </sst>
 </file>
@@ -941,12 +959,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M112"/>
+  <dimension ref="A1:M118"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.5">
@@ -1019,7 +1037,7 @@
         <v>45898</v>
       </c>
       <c r="K3">
-        <v>-299</v>
+        <v>-312</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -1033,28 +1051,28 @@
         <v>17</v>
       </c>
       <c r="C4">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H4">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J4" s="1">
         <v>45898</v>
       </c>
       <c r="K4">
-        <v>-299</v>
+        <v>-312</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -1092,7 +1110,7 @@
         <v>45898</v>
       </c>
       <c r="K5">
-        <v>-299</v>
+        <v>-312</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -1106,80 +1124,80 @@
         <v>22</v>
       </c>
       <c r="C6">
-        <v>184</v>
+        <v>221</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F6">
         <v>9</v>
       </c>
       <c r="H6">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J6" s="1">
         <v>45898</v>
       </c>
       <c r="K6">
-        <v>-299</v>
+        <v>-312</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
       </c>
       <c r="M6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7">
         <v>197</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="1">
         <v>46062</v>
       </c>
       <c r="K7">
-        <v>-135</v>
+        <v>-148</v>
       </c>
       <c r="L7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>259</v>
@@ -1188,36 +1206,36 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J8" s="1">
         <v>46108</v>
       </c>
       <c r="K8">
-        <v>-89</v>
+        <v>-102</v>
       </c>
       <c r="L8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>45</v>
@@ -1241,59 +1259,59 @@
         <v>46139</v>
       </c>
       <c r="K9">
-        <v>-58</v>
+        <v>-71</v>
       </c>
       <c r="L9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10">
         <v>646</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>612</v>
+        <v>631</v>
       </c>
       <c r="I10">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J10" s="1">
         <v>46139</v>
       </c>
       <c r="K10">
-        <v>-58</v>
+        <v>-71</v>
       </c>
       <c r="L10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11">
         <v>9</v>
@@ -1317,18 +1335,18 @@
         <v>46182</v>
       </c>
       <c r="K11">
-        <v>-15</v>
+        <v>-28</v>
       </c>
       <c r="L11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1352,220 +1370,217 @@
         <v>46188</v>
       </c>
       <c r="K12">
-        <v>-9</v>
+        <v>-22</v>
       </c>
       <c r="L12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13" s="1">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="K13">
-        <v>-9</v>
+        <v>-15</v>
       </c>
       <c r="L13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="K14">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="L14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H15">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>46216</v>
+        <v>46209</v>
       </c>
       <c r="K15">
-        <v>19</v>
+        <v>-1</v>
       </c>
       <c r="L15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C16">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="1">
-        <v>46211</v>
+        <v>46227</v>
       </c>
       <c r="K16">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L16" t="s">
-        <v>52</v>
-      </c>
-      <c r="M16" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="H17">
+        <v>162</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>46223</v>
+      </c>
+      <c r="K17">
         <v>13</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1">
-        <v>46209</v>
-      </c>
-      <c r="K17">
-        <v>12</v>
-      </c>
       <c r="L17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
         <v>57</v>
       </c>
       <c r="C18">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
         <v>4</v>
       </c>
-      <c r="E18">
-        <v>16</v>
-      </c>
       <c r="F18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="1">
-        <v>46203</v>
+        <v>46217</v>
       </c>
       <c r="K18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L18" t="s">
         <v>58</v>
@@ -1579,28 +1594,28 @@
         <v>60</v>
       </c>
       <c r="C19">
-        <v>162</v>
+        <v>21</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>159</v>
+        <v>19</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>46202</v>
+        <v>46216</v>
       </c>
       <c r="K19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L19" t="s">
         <v>61</v>
@@ -1614,42 +1629,33 @@
         <v>63</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I20">
         <v>0</v>
-      </c>
-      <c r="J20" s="1">
-        <v>46198</v>
-      </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-      <c r="L20" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C21">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1658,10 +1664,10 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1669,10 +1675,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C22">
         <v>47</v>
@@ -1695,10 +1701,10 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -1721,25 +1727,25 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C24">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="H24">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1747,25 +1753,25 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C25">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1773,13 +1779,13 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C26">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1790,11 +1796,8 @@
       <c r="F26">
         <v>0</v>
       </c>
-      <c r="G26" t="s">
-        <v>76</v>
-      </c>
       <c r="H26">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1802,16 +1805,16 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C27">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1819,11 +1822,8 @@
       <c r="F27">
         <v>0</v>
       </c>
-      <c r="G27" t="s">
-        <v>76</v>
-      </c>
       <c r="H27">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1831,28 +1831,25 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
-      <c r="G28" t="s">
-        <v>76</v>
-      </c>
       <c r="H28">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1860,28 +1857,25 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
-      <c r="G29" t="s">
-        <v>76</v>
-      </c>
       <c r="H29">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1889,13 +1883,13 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1907,10 +1901,10 @@
         <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1918,13 +1912,13 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1936,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1947,10 +1941,10 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1965,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -1976,10 +1970,10 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1994,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -2005,13 +1999,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -2023,10 +2017,10 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H34">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2034,13 +2028,13 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -2052,10 +2046,10 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2063,10 +2057,10 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -2081,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -2092,13 +2086,13 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2110,10 +2104,10 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2121,13 +2115,13 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2139,10 +2133,10 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2150,10 +2144,10 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -2168,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H39">
         <v>2</v>
@@ -2179,10 +2173,10 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A40" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -2197,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -2208,13 +2202,13 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A41" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C41">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2226,10 +2220,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H41">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2237,13 +2231,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A42" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2255,10 +2249,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2266,13 +2260,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2284,10 +2278,10 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H43">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2295,10 +2289,10 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -2313,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -2324,13 +2318,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A45" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2342,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H45">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2353,10 +2347,10 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A46" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C46">
         <v>4</v>
@@ -2371,7 +2365,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H46">
         <v>4</v>
@@ -2382,13 +2376,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A47" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C47">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2400,10 +2394,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H47">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2411,10 +2405,10 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A48" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -2429,7 +2423,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -2440,13 +2434,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2458,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2469,13 +2463,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A50" t="s">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C50">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2487,10 +2481,10 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H50">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2498,13 +2492,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A51" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2516,10 +2510,10 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2527,13 +2521,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A52" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="B52" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2545,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2556,13 +2550,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C53">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2574,10 +2568,10 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H53">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2588,10 +2582,10 @@
         <v>103</v>
       </c>
       <c r="B54" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2603,10 +2597,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2614,13 +2608,13 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B55" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2632,10 +2626,10 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2643,10 +2637,10 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B56" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -2661,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -2672,10 +2666,10 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B57" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -2690,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H57">
         <v>2</v>
@@ -2701,13 +2695,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B58" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2719,10 +2713,10 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2730,13 +2724,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A59" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B59" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C59">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2748,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H59">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2759,13 +2753,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A60" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B60" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C60">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2777,10 +2771,10 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H60">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2788,11 +2782,11 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A61" t="s">
+        <v>114</v>
+      </c>
+      <c r="B61" t="s">
         <v>115</v>
       </c>
-      <c r="B61" t="s">
-        <v>118</v>
-      </c>
       <c r="C61">
         <v>1</v>
       </c>
@@ -2806,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -2817,10 +2811,10 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A62" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B62" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C62">
         <v>2</v>
@@ -2835,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H62">
         <v>2</v>
@@ -2846,13 +2840,13 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A63" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B63" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C63">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2864,10 +2858,10 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H63">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -2875,13 +2869,13 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A64" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B64" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C64">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2893,10 +2887,10 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H64">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -2904,13 +2898,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A65" t="s">
+        <v>119</v>
+      </c>
+      <c r="B65" t="s">
         <v>121</v>
       </c>
-      <c r="B65" t="s">
-        <v>123</v>
-      </c>
       <c r="C65">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2922,10 +2916,10 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H65">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -2933,13 +2927,13 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A66" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B66" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C66">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2951,10 +2945,10 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H66">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -2962,13 +2956,13 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A67" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B67" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C67">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2980,10 +2974,10 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H67">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -2991,13 +2985,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A68" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B68" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -3009,10 +3003,10 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H68">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3020,13 +3014,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="B69" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C69">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -3038,10 +3032,10 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H69">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -3049,13 +3043,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A70" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="B70" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -3067,10 +3061,10 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -3078,13 +3072,13 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B71" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C71">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -3096,10 +3090,10 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H71">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3107,13 +3101,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A72" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B72" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3125,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3139,10 +3133,10 @@
         <v>131</v>
       </c>
       <c r="B73" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -3154,10 +3148,10 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3165,13 +3159,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A74" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B74" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3183,10 +3177,10 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H74">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3194,13 +3188,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A75" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B75" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -3212,10 +3206,10 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3223,10 +3217,10 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A76" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="B76" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C76">
         <v>3</v>
@@ -3241,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H76">
         <v>3</v>
@@ -3252,13 +3246,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A77" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="B77" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3270,10 +3264,10 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3281,13 +3275,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A78" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="B78" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3299,10 +3293,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3310,13 +3304,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A79" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B79" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C79">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3328,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H79">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3339,13 +3333,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A80" t="s">
-        <v>141</v>
+        <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3357,10 +3351,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3368,13 +3362,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A81" t="s">
+        <v>44</v>
+      </c>
+      <c r="B81" t="s">
         <v>141</v>
       </c>
-      <c r="B81" t="s">
-        <v>143</v>
-      </c>
       <c r="C81">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3386,10 +3380,10 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H81">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -3397,13 +3391,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A82" t="s">
-        <v>144</v>
+        <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C82">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3415,10 +3409,10 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H82">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -3426,13 +3420,13 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
-        <v>146</v>
+        <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C83">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -3444,10 +3438,10 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H83">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -3455,10 +3449,10 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A84" t="s">
-        <v>146</v>
+        <v>44</v>
       </c>
       <c r="B84" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C84">
         <v>5</v>
@@ -3473,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H84">
         <v>5</v>
@@ -3484,13 +3478,13 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A85" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="B85" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C85">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3502,10 +3496,10 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H85">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -3513,13 +3507,13 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A86" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="B86" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -3531,10 +3525,10 @@
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H86">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -3542,13 +3536,13 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A87" t="s">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="B87" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -3560,10 +3554,10 @@
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H87">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -3571,13 +3565,13 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A88" t="s">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="B88" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3589,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H88">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -3600,13 +3594,13 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A89" t="s">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="B89" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3618,10 +3612,10 @@
         <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H89">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -3629,13 +3623,13 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A90" t="s">
-        <v>62</v>
+        <v>153</v>
       </c>
       <c r="B90" t="s">
         <v>154</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3647,10 +3641,10 @@
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H90">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -3658,7 +3652,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A91" t="s">
-        <v>62</v>
+        <v>153</v>
       </c>
       <c r="B91" t="s">
         <v>155</v>
@@ -3676,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H91">
         <v>1</v>
@@ -3687,13 +3681,13 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A92" t="s">
-        <v>62</v>
+        <v>153</v>
       </c>
       <c r="B92" t="s">
         <v>156</v>
       </c>
       <c r="C92">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3705,10 +3699,10 @@
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H92">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -3716,7 +3710,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A93" t="s">
-        <v>62</v>
+        <v>153</v>
       </c>
       <c r="B93" t="s">
         <v>157</v>
@@ -3734,7 +3728,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H93">
         <v>1</v>
@@ -3745,13 +3739,13 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A94" t="s">
+        <v>153</v>
+      </c>
+      <c r="B94" t="s">
         <v>158</v>
       </c>
-      <c r="B94" t="s">
-        <v>159</v>
-      </c>
       <c r="C94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3763,10 +3757,10 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -3774,13 +3768,13 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A95" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B95" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3792,10 +3786,10 @@
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -3803,13 +3797,13 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A96" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B96" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C96">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3821,10 +3815,10 @@
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H96">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -3832,10 +3826,10 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A97" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="B97" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -3850,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -3861,13 +3855,13 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A98" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B98" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3879,10 +3873,10 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H98">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -3890,13 +3884,13 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A99" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="B99" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C99">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3908,10 +3902,10 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H99">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -3919,13 +3913,13 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A100" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B100" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3937,10 +3931,10 @@
         <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -3948,10 +3942,10 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A101" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B101" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C101">
         <v>2</v>
@@ -3966,7 +3960,7 @@
         <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H101">
         <v>2</v>
@@ -3977,13 +3971,13 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A102" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B102" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C102">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3995,10 +3989,10 @@
         <v>0</v>
       </c>
       <c r="G102" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H102">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -4006,13 +4000,13 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A103" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B103" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C103">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -4024,10 +4018,10 @@
         <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H103">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -4035,13 +4029,13 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A104" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B104" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -4053,10 +4047,10 @@
         <v>0</v>
       </c>
       <c r="G104" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -4064,13 +4058,13 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A105" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B105" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C105">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -4082,10 +4076,10 @@
         <v>0</v>
       </c>
       <c r="G105" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H105">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -4093,13 +4087,13 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A106" t="s">
-        <v>71</v>
+        <v>175</v>
       </c>
       <c r="B106" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -4111,10 +4105,10 @@
         <v>0</v>
       </c>
       <c r="G106" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -4122,13 +4116,13 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A107" t="s">
-        <v>71</v>
+        <v>177</v>
       </c>
       <c r="B107" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C107">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -4140,10 +4134,10 @@
         <v>0</v>
       </c>
       <c r="G107" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H107">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I107">
         <v>0</v>
@@ -4151,13 +4145,13 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A108" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B108" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C108">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -4169,10 +4163,10 @@
         <v>0</v>
       </c>
       <c r="G108" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H108">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -4180,13 +4174,13 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A109" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B109" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -4198,10 +4192,10 @@
         <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H109">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -4209,13 +4203,13 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A110" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B110" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C110">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -4227,10 +4221,10 @@
         <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H110">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I110">
         <v>0</v>
@@ -4238,13 +4232,13 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A111" t="s">
-        <v>43</v>
+        <v>184</v>
       </c>
       <c r="B111" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -4256,10 +4250,10 @@
         <v>0</v>
       </c>
       <c r="G111" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H111">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I111">
         <v>0</v>
@@ -4267,30 +4261,204 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A112" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="B112" t="s">
+        <v>186</v>
+      </c>
+      <c r="C112">
+        <v>2</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112" t="s">
+        <v>79</v>
+      </c>
+      <c r="H112">
+        <v>2</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A113" t="s">
+        <v>76</v>
+      </c>
+      <c r="B113" t="s">
+        <v>187</v>
+      </c>
+      <c r="C113">
+        <v>24</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113" t="s">
+        <v>79</v>
+      </c>
+      <c r="H113">
+        <v>24</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A114" t="s">
+        <v>188</v>
+      </c>
+      <c r="B114" t="s">
         <v>189</v>
       </c>
-      <c r="C112">
-        <v>1</v>
-      </c>
-      <c r="D112">
-        <v>0</v>
-      </c>
-      <c r="E112">
-        <v>0</v>
-      </c>
-      <c r="F112">
-        <v>0</v>
-      </c>
-      <c r="G112" t="s">
-        <v>76</v>
-      </c>
-      <c r="H112">
-        <v>1</v>
-      </c>
-      <c r="I112">
+      <c r="C114">
+        <v>170</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114" t="s">
+        <v>79</v>
+      </c>
+      <c r="H114">
+        <v>170</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A115" t="s">
+        <v>190</v>
+      </c>
+      <c r="B115" t="s">
+        <v>191</v>
+      </c>
+      <c r="C115">
+        <v>1</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115" t="s">
+        <v>79</v>
+      </c>
+      <c r="H115">
+        <v>1</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A116" t="s">
+        <v>192</v>
+      </c>
+      <c r="B116" t="s">
+        <v>193</v>
+      </c>
+      <c r="C116">
+        <v>15</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116" t="s">
+        <v>79</v>
+      </c>
+      <c r="H116">
+        <v>15</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A117" t="s">
+        <v>69</v>
+      </c>
+      <c r="B117" t="s">
+        <v>194</v>
+      </c>
+      <c r="C117">
+        <v>1</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117" t="s">
+        <v>79</v>
+      </c>
+      <c r="H117">
+        <v>1</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A118" t="s">
+        <v>69</v>
+      </c>
+      <c r="B118" t="s">
+        <v>195</v>
+      </c>
+      <c r="C118">
+        <v>1</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118" t="s">
+        <v>79</v>
+      </c>
+      <c r="H118">
+        <v>1</v>
+      </c>
+      <c r="I118">
         <v>0</v>
       </c>
     </row>

--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB98E9D3AB8AB9AE35E7DB6955471D9EBD6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{172113FB-37B3-46B8-A13E-1B1DEB003088}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB98A3DF594B59BF92FDD33A54870D9E2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{024BA589-42D4-4F11-977F-30C574110B74}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="PO_StatusQry" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$118</definedName>
+    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$121</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="204">
   <si>
     <t>CustName</t>
   </si>
@@ -70,7 +70,7 @@
     <t>4516351202_ASEWH</t>
   </si>
   <si>
-    <t>OverDue by 312 days</t>
+    <t>OverDue by 318 days</t>
   </si>
   <si>
     <t>Texas Instruments SCT</t>
@@ -103,7 +103,7 @@
     <t>Global PO 4516351202</t>
   </si>
   <si>
-    <t>OverDue by 148 days</t>
+    <t>OverDue by 154 days</t>
   </si>
   <si>
     <t>Varies (2026-02-09 → 2026-07-07)</t>
@@ -115,7 +115,7 @@
     <t>4516351202_ARD</t>
   </si>
   <si>
-    <t>OverDue by 102 days</t>
+    <t>OverDue by 108 days</t>
   </si>
   <si>
     <t>Varies (2026-03-27 → 2026-05-19)</t>
@@ -127,7 +127,7 @@
     <t>47270551</t>
   </si>
   <si>
-    <t>OverDue by 71 days</t>
+    <t>OverDue by 77 days</t>
   </si>
   <si>
     <t>Varies (2026-04-27 → 2026-06-30)</t>
@@ -145,25 +145,28 @@
     <t>47318424</t>
   </si>
   <si>
+    <t>OverDue by 61 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-05-13 → 2026-06-09)</t>
+  </si>
+  <si>
+    <t>ASE CO., LTD - PHILIPPINES BRANCH 01-075</t>
+  </si>
+  <si>
+    <t>MO262002496</t>
+  </si>
+  <si>
     <t>OverDue by 28 days</t>
   </si>
   <si>
-    <t>ASE CO., LTD - PHILIPPINES BRANCH 01-075</t>
-  </si>
-  <si>
-    <t>MO262002496</t>
-  </si>
-  <si>
-    <t>OverDue by 22 days</t>
-  </si>
-  <si>
     <t>NXP Malaysia Sdn. Bhd.</t>
   </si>
   <si>
     <t>3T/PO262333</t>
   </si>
   <si>
-    <t>OverDue by 15 days</t>
+    <t>OverDue by 21 days</t>
   </si>
   <si>
     <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
@@ -172,184 +175,205 @@
     <t>4516351202_ASESH</t>
   </si>
   <si>
+    <t>OverDue by 13 days</t>
+  </si>
+  <si>
+    <t>47301012</t>
+  </si>
+  <si>
     <t>OverDue by 7 days</t>
   </si>
   <si>
-    <t>47301012</t>
-  </si>
-  <si>
-    <t>OverDue by 1 days</t>
-  </si>
-  <si>
-    <t>3T/PO262338</t>
-  </si>
-  <si>
-    <t>17 days before Due</t>
-  </si>
-  <si>
-    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
-  </si>
-  <si>
-    <t>4516351202_MIHO</t>
-  </si>
-  <si>
-    <t>13 days before Due</t>
-  </si>
-  <si>
-    <t>TBA_NXP</t>
-  </si>
-  <si>
-    <t>7 days before Due</t>
-  </si>
-  <si>
-    <t>Lingsen Precision Industries Ltd.</t>
-  </si>
-  <si>
-    <t>4516446856</t>
-  </si>
-  <si>
-    <t>6 days before Due</t>
-  </si>
-  <si>
-    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
-  </si>
-  <si>
-    <t>4516351202_TII</t>
-  </si>
-  <si>
-    <t>47364135</t>
-  </si>
-  <si>
-    <t>Texas Instruments DMOS5</t>
-  </si>
-  <si>
-    <t>4516351202_DMOS5</t>
-  </si>
-  <si>
-    <t>Texas Instruments LFAB</t>
-  </si>
-  <si>
-    <t>4516351202_LFAB</t>
-  </si>
-  <si>
-    <t>UTAC Thai Limited ( UTL 3)</t>
-  </si>
-  <si>
-    <t>4516351202_UTL</t>
-  </si>
-  <si>
-    <t>47361669</t>
-  </si>
-  <si>
-    <t>47362207</t>
-  </si>
-  <si>
-    <t>47362715</t>
-  </si>
-  <si>
-    <t>ROCHESTER ELECTRONICS</t>
-  </si>
-  <si>
-    <t>252395</t>
-  </si>
-  <si>
-    <t>Texas Instruments Taiwan Limited</t>
-  </si>
-  <si>
-    <t>4516450237</t>
-  </si>
-  <si>
-    <t>47188646</t>
-  </si>
-  <si>
-    <t>Completed PO</t>
-  </si>
-  <si>
-    <t>47218149</t>
-  </si>
-  <si>
-    <t>47245848</t>
-  </si>
-  <si>
-    <t>47245933</t>
-  </si>
-  <si>
-    <t>47253728</t>
-  </si>
-  <si>
-    <t>47264622</t>
-  </si>
-  <si>
-    <t>47274630</t>
-  </si>
-  <si>
-    <t>47276474</t>
-  </si>
-  <si>
-    <t>47283634</t>
-  </si>
-  <si>
-    <t>47283654</t>
-  </si>
-  <si>
-    <t>47286185</t>
-  </si>
-  <si>
-    <t>47289023</t>
-  </si>
-  <si>
-    <t>47290167</t>
-  </si>
-  <si>
-    <t>47292239</t>
-  </si>
-  <si>
-    <t>47292914</t>
-  </si>
-  <si>
-    <t>47296581</t>
-  </si>
-  <si>
-    <t>47296806</t>
-  </si>
-  <si>
-    <t>47301646</t>
-  </si>
-  <si>
-    <t>47304169</t>
-  </si>
-  <si>
-    <t>47324752</t>
-  </si>
-  <si>
-    <t>47345978</t>
-  </si>
-  <si>
-    <t>47352135</t>
-  </si>
-  <si>
-    <t>47361598</t>
-  </si>
-  <si>
-    <t>TBD_SAMPLE</t>
-  </si>
-  <si>
-    <t>ANALOG DEVICES INC. CAMAS</t>
-  </si>
-  <si>
-    <t>47259467</t>
-  </si>
-  <si>
-    <t>Ardentec Korea Co., Ltd.</t>
-  </si>
-  <si>
-    <t>4516351202_ATK</t>
+    <t>Varies (2026-07-06 → 2026-07-28)</t>
   </si>
   <si>
     <t>AVAGO TECHNOLOGIES_x000D_
 INTERNATIONAL SALES PTE LTD</t>
   </si>
   <si>
+    <t>8541571063</t>
+  </si>
+  <si>
+    <t>16 days before Due</t>
+  </si>
+  <si>
+    <t>3T/PO262338</t>
+  </si>
+  <si>
+    <t>11 days before Due</t>
+  </si>
+  <si>
+    <t>UTAC Thai Limited ( UTL 3)</t>
+  </si>
+  <si>
+    <t>4516351202_UTL</t>
+  </si>
+  <si>
+    <t>10 days before Due</t>
+  </si>
+  <si>
+    <t>PO-468-061326-01</t>
+  </si>
+  <si>
+    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
+  </si>
+  <si>
+    <t>4516351202_MIHO</t>
+  </si>
+  <si>
+    <t>7 days before Due</t>
+  </si>
+  <si>
+    <t>TBA_NXP</t>
+  </si>
+  <si>
+    <t>1 days before Due</t>
+  </si>
+  <si>
+    <t>Lingsen Precision Industries Ltd.</t>
+  </si>
+  <si>
+    <t>4516446856</t>
+  </si>
+  <si>
+    <t>Due Today</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
+  </si>
+  <si>
+    <t>4516351202_TII</t>
+  </si>
+  <si>
+    <t>Texas Instruments DMOS5</t>
+  </si>
+  <si>
+    <t>4516351202_DMOS5</t>
+  </si>
+  <si>
+    <t>Microprecision Calibration Inc.</t>
+  </si>
+  <si>
+    <t>PP26-1051NI</t>
+  </si>
+  <si>
+    <t>47364135</t>
+  </si>
+  <si>
+    <t>Texas Instruments LFAB</t>
+  </si>
+  <si>
+    <t>4516351202_LFAB</t>
+  </si>
+  <si>
+    <t>47362715</t>
+  </si>
+  <si>
+    <t>ROCHESTER ELECTRONICS</t>
+  </si>
+  <si>
+    <t>252395</t>
+  </si>
+  <si>
+    <t>Texas Instruments Taiwan Limited</t>
+  </si>
+  <si>
+    <t>4516450237</t>
+  </si>
+  <si>
+    <t>47188646</t>
+  </si>
+  <si>
+    <t>Completed PO</t>
+  </si>
+  <si>
+    <t>47218149</t>
+  </si>
+  <si>
+    <t>47245848</t>
+  </si>
+  <si>
+    <t>47245933</t>
+  </si>
+  <si>
+    <t>47253728</t>
+  </si>
+  <si>
+    <t>47264622</t>
+  </si>
+  <si>
+    <t>47274630</t>
+  </si>
+  <si>
+    <t>47276474</t>
+  </si>
+  <si>
+    <t>47283634</t>
+  </si>
+  <si>
+    <t>47283654</t>
+  </si>
+  <si>
+    <t>47286185</t>
+  </si>
+  <si>
+    <t>47289023</t>
+  </si>
+  <si>
+    <t>47290167</t>
+  </si>
+  <si>
+    <t>47292239</t>
+  </si>
+  <si>
+    <t>47292914</t>
+  </si>
+  <si>
+    <t>47296581</t>
+  </si>
+  <si>
+    <t>47296806</t>
+  </si>
+  <si>
+    <t>47301646</t>
+  </si>
+  <si>
+    <t>47304169</t>
+  </si>
+  <si>
+    <t>47324752</t>
+  </si>
+  <si>
+    <t>47345978</t>
+  </si>
+  <si>
+    <t>47352135</t>
+  </si>
+  <si>
+    <t>47361598</t>
+  </si>
+  <si>
+    <t>47361669</t>
+  </si>
+  <si>
+    <t>47362207</t>
+  </si>
+  <si>
+    <t>TBD_SAMPLE</t>
+  </si>
+  <si>
+    <t>ANALOG DEVICES INC. CAMAS</t>
+  </si>
+  <si>
+    <t>47259467</t>
+  </si>
+  <si>
+    <t>Ardentec Korea Co., Ltd.</t>
+  </si>
+  <si>
+    <t>4516351202_ATK</t>
+  </si>
+  <si>
     <t>8541541216</t>
   </si>
   <si>
@@ -431,9 +455,6 @@
     <t>LPI-2507174</t>
   </si>
   <si>
-    <t>Microprecision Calibration Inc.</t>
-  </si>
-  <si>
     <t>PP25-1057NI</t>
   </si>
   <si>
@@ -614,7 +635,7 @@
     <t>43156228</t>
   </si>
   <si>
-    <t>Last updated: 2026-07-07 09:24:17</t>
+    <t>Last updated: 2026-07-13 09:11:56</t>
   </si>
 </sst>
 </file>
@@ -959,12 +980,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M118"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.5">
@@ -1037,7 +1058,7 @@
         <v>45898</v>
       </c>
       <c r="K3">
-        <v>-312</v>
+        <v>-318</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -1054,10 +1075,10 @@
         <v>344</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F4">
         <v>11</v>
@@ -1072,7 +1093,7 @@
         <v>45898</v>
       </c>
       <c r="K4">
-        <v>-312</v>
+        <v>-318</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -1110,7 +1131,7 @@
         <v>45898</v>
       </c>
       <c r="K5">
-        <v>-312</v>
+        <v>-318</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -1127,25 +1148,25 @@
         <v>221</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F6">
         <v>9</v>
       </c>
       <c r="H6">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="I6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1">
         <v>45898</v>
       </c>
       <c r="K6">
-        <v>-312</v>
+        <v>-318</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -1183,7 +1204,7 @@
         <v>46062</v>
       </c>
       <c r="K7">
-        <v>-148</v>
+        <v>-154</v>
       </c>
       <c r="L7" t="s">
         <v>26</v>
@@ -1221,7 +1242,7 @@
         <v>46108</v>
       </c>
       <c r="K8">
-        <v>-102</v>
+        <v>-108</v>
       </c>
       <c r="L8" t="s">
         <v>30</v>
@@ -1238,13 +1259,13 @@
         <v>33</v>
       </c>
       <c r="C9">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1259,7 +1280,7 @@
         <v>46139</v>
       </c>
       <c r="K9">
-        <v>-71</v>
+        <v>-77</v>
       </c>
       <c r="L9" t="s">
         <v>34</v>
@@ -1279,10 +1300,10 @@
         <v>646</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1297,7 +1318,7 @@
         <v>46139</v>
       </c>
       <c r="K10">
-        <v>-71</v>
+        <v>-77</v>
       </c>
       <c r="L10" t="s">
         <v>34</v>
@@ -1314,39 +1335,42 @@
         <v>39</v>
       </c>
       <c r="C11">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" s="1">
-        <v>46182</v>
+        <v>46155</v>
       </c>
       <c r="K11">
-        <v>-28</v>
+        <v>-61</v>
       </c>
       <c r="L11" t="s">
         <v>40</v>
       </c>
+      <c r="M11" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1370,18 +1394,18 @@
         <v>46188</v>
       </c>
       <c r="K12">
-        <v>-22</v>
+        <v>-28</v>
       </c>
       <c r="L12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13">
         <v>10</v>
@@ -1405,27 +1429,27 @@
         <v>46195</v>
       </c>
       <c r="K13">
-        <v>-15</v>
+        <v>-21</v>
       </c>
       <c r="L13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C14">
         <v>50</v>
       </c>
       <c r="D14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1440,10 +1464,10 @@
         <v>46203</v>
       </c>
       <c r="K14">
-        <v>-7</v>
+        <v>-13</v>
       </c>
       <c r="L14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.5">
@@ -1451,19 +1475,19 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15">
         <v>20</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H15">
         <v>13</v>
@@ -1475,27 +1499,30 @@
         <v>46209</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="L15" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="M15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1504,86 +1531,86 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="K16">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L16" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C17">
-        <v>172</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="H17">
-        <v>162</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" s="1">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="K17">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C18">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>46217</v>
+        <v>46226</v>
       </c>
       <c r="K18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L18" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.5">
@@ -1591,31 +1618,31 @@
         <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C19">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19" s="1">
-        <v>46216</v>
+        <v>46226</v>
       </c>
       <c r="K19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L19" t="s">
         <v>61</v>
@@ -1623,91 +1650,118 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C20">
-        <v>50</v>
+        <v>172</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>28</v>
+        <v>162</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="J20" s="1">
+        <v>46223</v>
+      </c>
+      <c r="K20">
+        <v>7</v>
+      </c>
+      <c r="L20" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I21">
         <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>46217</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C22">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="I22">
         <v>0</v>
+      </c>
+      <c r="J22" s="1">
+        <v>46216</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1716,10 +1770,10 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1727,13 +1781,13 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C24">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1742,10 +1796,10 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H24">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1753,13 +1807,13 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1768,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -1782,7 +1836,7 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1794,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -1805,25 +1859,25 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1831,25 +1885,25 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C28">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
       <c r="H28">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1857,25 +1911,25 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C29">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="H29">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1883,28 +1937,25 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C30">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
-      <c r="G30" t="s">
-        <v>79</v>
-      </c>
       <c r="H30">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1915,10 +1966,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C31">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1930,10 +1981,10 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H31">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1944,10 +1995,10 @@
         <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -1959,10 +2010,10 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -1973,7 +2024,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1988,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -2002,7 +2053,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -2017,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -2031,7 +2082,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -2046,7 +2097,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -2060,7 +2111,7 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -2075,7 +2126,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -2089,7 +2140,7 @@
         <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -2104,7 +2155,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -2118,10 +2169,10 @@
         <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2133,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H38">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2147,10 +2198,10 @@
         <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2162,10 +2213,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H39">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2176,10 +2227,10 @@
         <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2191,10 +2242,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2205,10 +2256,10 @@
         <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2220,10 +2271,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2234,10 +2285,10 @@
         <v>32</v>
       </c>
       <c r="B42" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2249,10 +2300,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2263,10 +2314,10 @@
         <v>32</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2278,10 +2329,10 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2292,10 +2343,10 @@
         <v>32</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2307,10 +2358,10 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2321,10 +2372,10 @@
         <v>32</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C45">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2336,10 +2387,10 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H45">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2350,10 +2401,10 @@
         <v>32</v>
       </c>
       <c r="B46" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2365,10 +2416,10 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H46">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2379,10 +2430,10 @@
         <v>32</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2394,10 +2445,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2408,10 +2459,10 @@
         <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2423,10 +2474,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2437,10 +2488,10 @@
         <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2452,10 +2503,10 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2466,7 +2517,7 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C50">
         <v>4</v>
@@ -2481,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H50">
         <v>4</v>
@@ -2495,10 +2546,10 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C51">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2510,10 +2561,10 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H51">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2524,10 +2575,10 @@
         <v>32</v>
       </c>
       <c r="B52" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2539,10 +2590,10 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2553,7 +2604,7 @@
         <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -2568,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -2579,10 +2630,10 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="B54" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -2597,7 +2648,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -2608,13 +2659,13 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="B55" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C55">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2626,10 +2677,10 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H55">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2637,10 +2688,10 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="B56" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -2655,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -2666,13 +2717,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B57" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2684,10 +2735,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2695,13 +2746,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B58" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2713,10 +2764,10 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H58">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2724,13 +2775,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A59" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="B59" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2742,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2753,13 +2804,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A60" t="s">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="B60" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2771,10 +2822,10 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2782,13 +2833,13 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A61" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="B61" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2800,10 +2851,10 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2811,13 +2862,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A62" t="s">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="B62" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2829,10 +2880,10 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2840,10 +2891,10 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A63" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B63" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -2858,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -2869,13 +2920,13 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A64" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B64" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C64">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2887,10 +2938,10 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H64">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -2898,13 +2949,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A65" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B65" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C65">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2916,10 +2967,10 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H65">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -2927,10 +2978,10 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A66" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B66" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -2945,7 +2996,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -2956,13 +3007,13 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A67" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B67" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2974,10 +3025,10 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H67">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -2985,13 +3036,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A68" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B68" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C68">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -3003,10 +3054,10 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H68">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3014,13 +3065,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B69" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C69">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -3032,10 +3083,10 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H69">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -3043,13 +3094,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A70" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B70" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C70">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -3061,10 +3112,10 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H70">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -3072,13 +3123,13 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B71" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C71">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -3090,10 +3141,10 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H71">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3101,13 +3152,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A72" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B72" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C72">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3119,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H72">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3130,13 +3181,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A73" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B73" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C73">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -3148,10 +3199,10 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H73">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3159,13 +3210,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A74" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="B74" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C74">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3177,10 +3228,10 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H74">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3188,13 +3239,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A75" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="B75" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -3206,10 +3257,10 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H75">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3217,13 +3268,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A76" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B76" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3235,10 +3286,10 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3246,13 +3297,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A77" t="s">
-        <v>135</v>
+        <v>68</v>
       </c>
       <c r="B77" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3264,10 +3315,10 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3275,10 +3326,10 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A78" t="s">
-        <v>135</v>
+        <v>68</v>
       </c>
       <c r="B78" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -3293,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -3304,13 +3355,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A79" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="B79" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3322,10 +3373,10 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3333,13 +3384,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A80" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="B80" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3351,10 +3402,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3362,13 +3413,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A81" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="B81" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3380,10 +3431,10 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -3391,13 +3442,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A82" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B82" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3409,10 +3460,10 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -3420,10 +3471,10 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B83" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C83">
         <v>3</v>
@@ -3438,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H83">
         <v>3</v>
@@ -3449,13 +3500,13 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A84" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C84">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3467,10 +3518,10 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H84">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -3478,13 +3529,13 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A85" t="s">
-        <v>145</v>
+        <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3496,10 +3547,10 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -3507,13 +3558,13 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A86" t="s">
-        <v>145</v>
+        <v>45</v>
       </c>
       <c r="B86" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C86">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -3525,10 +3576,10 @@
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H86">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -3536,13 +3587,13 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A87" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="B87" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C87">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -3554,10 +3605,10 @@
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H87">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -3565,13 +3616,13 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A88" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B88" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C88">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3583,10 +3634,10 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H88">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -3594,10 +3645,10 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A89" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B89" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C89">
         <v>5</v>
@@ -3612,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H89">
         <v>5</v>
@@ -3623,13 +3674,13 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A90" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B90" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C90">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3641,10 +3692,10 @@
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H90">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -3652,13 +3703,13 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A91" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B91" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3670,10 +3721,10 @@
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H91">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -3681,13 +3732,13 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A92" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B92" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3699,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H92">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -3710,13 +3761,13 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A93" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B93" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3728,10 +3779,10 @@
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H93">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -3739,10 +3790,10 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A94" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B94" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -3757,7 +3808,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -3768,10 +3819,10 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A95" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B95" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -3786,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -3797,10 +3848,10 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A96" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B96" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -3815,7 +3866,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H96">
         <v>1</v>
@@ -3826,10 +3877,10 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A97" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B97" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -3844,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -3855,13 +3906,13 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A98" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B98" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C98">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3873,10 +3924,10 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H98">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -3884,10 +3935,10 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A99" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B99" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -3902,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -3913,13 +3964,13 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A100" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B100" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D100">
         <v>0</v>
@@ -3931,10 +3982,10 @@
         <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -3942,13 +3993,13 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A101" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B101" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C101">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3960,10 +4011,10 @@
         <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H101">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -3971,13 +4022,13 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A102" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B102" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C102">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3989,10 +4040,10 @@
         <v>0</v>
       </c>
       <c r="G102" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H102">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -4000,13 +4051,13 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A103" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B103" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -4018,10 +4069,10 @@
         <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -4032,10 +4083,10 @@
         <v>171</v>
       </c>
       <c r="B104" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -4047,10 +4098,10 @@
         <v>0</v>
       </c>
       <c r="G104" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -4058,13 +4109,13 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A105" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B105" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C105">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -4076,10 +4127,10 @@
         <v>0</v>
       </c>
       <c r="G105" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H105">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -4087,10 +4138,10 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A106" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B106" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -4105,7 +4156,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H106">
         <v>1</v>
@@ -4116,13 +4167,13 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A107" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B107" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -4134,10 +4185,10 @@
         <v>0</v>
       </c>
       <c r="G107" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I107">
         <v>0</v>
@@ -4145,13 +4196,13 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A108" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B108" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C108">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -4163,10 +4214,10 @@
         <v>0</v>
       </c>
       <c r="G108" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H108">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -4174,13 +4225,13 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A109" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B109" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C109">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -4192,10 +4243,10 @@
         <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H109">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -4203,10 +4254,10 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A110" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B110" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C110">
         <v>2</v>
@@ -4221,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H110">
         <v>2</v>
@@ -4235,10 +4286,10 @@
         <v>184</v>
       </c>
       <c r="B111" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C111">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -4250,10 +4301,10 @@
         <v>0</v>
       </c>
       <c r="G111" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H111">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I111">
         <v>0</v>
@@ -4261,13 +4312,13 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A112" t="s">
-        <v>76</v>
+        <v>187</v>
       </c>
       <c r="B112" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C112">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -4279,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="G112" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H112">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -4290,13 +4341,13 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A113" t="s">
-        <v>76</v>
+        <v>189</v>
       </c>
       <c r="B113" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C113">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -4308,10 +4359,10 @@
         <v>0</v>
       </c>
       <c r="G113" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H113">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I113">
         <v>0</v>
@@ -4319,13 +4370,13 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A114" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B114" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C114">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -4337,10 +4388,10 @@
         <v>0</v>
       </c>
       <c r="G114" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H114">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="I114">
         <v>0</v>
@@ -4348,13 +4399,13 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A115" t="s">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="B115" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -4366,10 +4417,10 @@
         <v>0</v>
       </c>
       <c r="G115" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I115">
         <v>0</v>
@@ -4377,13 +4428,13 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A116" t="s">
-        <v>192</v>
+        <v>83</v>
       </c>
       <c r="B116" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C116">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -4395,10 +4446,10 @@
         <v>0</v>
       </c>
       <c r="G116" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H116">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -4406,13 +4457,13 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A117" t="s">
-        <v>69</v>
+        <v>195</v>
       </c>
       <c r="B117" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -4424,10 +4475,10 @@
         <v>0</v>
       </c>
       <c r="G117" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H117">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="I117">
         <v>0</v>
@@ -4435,10 +4486,10 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A118" t="s">
-        <v>69</v>
+        <v>197</v>
       </c>
       <c r="B118" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C118">
         <v>1</v>
@@ -4453,12 +4504,99 @@
         <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H118">
         <v>1</v>
       </c>
       <c r="I118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A119" t="s">
+        <v>199</v>
+      </c>
+      <c r="B119" t="s">
+        <v>200</v>
+      </c>
+      <c r="C119">
+        <v>15</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119" t="s">
+        <v>86</v>
+      </c>
+      <c r="H119">
+        <v>15</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A120" t="s">
+        <v>59</v>
+      </c>
+      <c r="B120" t="s">
+        <v>201</v>
+      </c>
+      <c r="C120">
+        <v>1</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120" t="s">
+        <v>86</v>
+      </c>
+      <c r="H120">
+        <v>1</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A121" t="s">
+        <v>59</v>
+      </c>
+      <c r="B121" t="s">
+        <v>202</v>
+      </c>
+      <c r="C121">
+        <v>1</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121" t="s">
+        <v>86</v>
+      </c>
+      <c r="H121">
+        <v>1</v>
+      </c>
+      <c r="I121">
         <v>0</v>
       </c>
     </row>

--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB98A3DF594B59BF92FDD33A54870D9E2D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{024BA589-42D4-4F11-977F-30C574110B74}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB90795B4EE0D79ECA7653592CA70D9E37A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DB22E8F-3D42-4057-B616-81BCD1EF7549}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="PO_StatusQry" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$121</definedName>
+    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$123</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="201">
   <si>
     <t>CustName</t>
   </si>
@@ -70,7 +70,7 @@
     <t>4516351202_ASEWH</t>
   </si>
   <si>
-    <t>OverDue by 318 days</t>
+    <t>OverDue by 332 days</t>
   </si>
   <si>
     <t>Texas Instruments SCT</t>
@@ -79,7 +79,7 @@
     <t>4516351202_SCT</t>
   </si>
   <si>
-    <t>Varies (2025-08-29 → 2026-07-06)</t>
+    <t>Varies (2025-08-29 → 2026-07-28)</t>
   </si>
   <si>
     <t>Texas Instruments Taiwan</t>
@@ -103,10 +103,7 @@
     <t>Global PO 4516351202</t>
   </si>
   <si>
-    <t>OverDue by 154 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-02-09 → 2026-07-07)</t>
+    <t>OverDue by 168 days</t>
   </si>
   <si>
     <t>ARDENTEC CORPORATION</t>
@@ -115,7 +112,7 @@
     <t>4516351202_ARD</t>
   </si>
   <si>
-    <t>OverDue by 108 days</t>
+    <t>OverDue by 122 days</t>
   </si>
   <si>
     <t>Varies (2026-03-27 → 2026-05-19)</t>
@@ -127,7 +124,7 @@
     <t>47270551</t>
   </si>
   <si>
-    <t>OverDue by 77 days</t>
+    <t>OverDue by 91 days</t>
   </si>
   <si>
     <t>Varies (2026-04-27 → 2026-06-30)</t>
@@ -145,7 +142,7 @@
     <t>47318424</t>
   </si>
   <si>
-    <t>OverDue by 61 days</t>
+    <t>OverDue by 75 days</t>
   </si>
   <si>
     <t>Varies (2026-05-13 → 2026-06-09)</t>
@@ -157,34 +154,34 @@
     <t>MO262002496</t>
   </si>
   <si>
-    <t>OverDue by 28 days</t>
+    <t>OverDue by 42 days</t>
+  </si>
+  <si>
+    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
+  </si>
+  <si>
+    <t>4516351202_MIHO</t>
+  </si>
+  <si>
+    <t>OverDue by 7 days</t>
+  </si>
+  <si>
+    <t>UTAC Thai Limited ( UTL 3)</t>
+  </si>
+  <si>
+    <t>PO-468-061326-01</t>
+  </si>
+  <si>
+    <t>OverDue by 4 days</t>
   </si>
   <si>
     <t>NXP Malaysia Sdn. Bhd.</t>
   </si>
   <si>
-    <t>3T/PO262333</t>
-  </si>
-  <si>
-    <t>OverDue by 21 days</t>
-  </si>
-  <si>
-    <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
-  </si>
-  <si>
-    <t>4516351202_ASESH</t>
-  </si>
-  <si>
-    <t>OverDue by 13 days</t>
-  </si>
-  <si>
-    <t>47301012</t>
-  </si>
-  <si>
-    <t>OverDue by 7 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-07-06 → 2026-07-28)</t>
+    <t>TBA_NXP</t>
+  </si>
+  <si>
+    <t>14 days before Due</t>
   </si>
   <si>
     <t>AVAGO TECHNOLOGIES_x000D_
@@ -194,448 +191,442 @@
     <t>8541571063</t>
   </si>
   <si>
-    <t>16 days before Due</t>
+    <t>2 days before Due</t>
+  </si>
+  <si>
+    <t>Texas Instruments DMOS5</t>
+  </si>
+  <si>
+    <t>4516351202_DMOS5</t>
+  </si>
+  <si>
+    <t>1 days before Due</t>
+  </si>
+  <si>
+    <t>Tongfu Microelectronics Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>4516351202_NFME</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
+  </si>
+  <si>
+    <t>4516351202_TII</t>
+  </si>
+  <si>
+    <t>Texas Instruments AIZU</t>
+  </si>
+  <si>
+    <t>4516351202_AIZU</t>
+  </si>
+  <si>
+    <t>Microprecision Calibration Inc.</t>
+  </si>
+  <si>
+    <t>PP26-1051NI</t>
+  </si>
+  <si>
+    <t>47364135</t>
+  </si>
+  <si>
+    <t>Texas Instruments LFAB</t>
+  </si>
+  <si>
+    <t>4516351202_LFAB</t>
+  </si>
+  <si>
+    <t>ANALOG DEVICES INC.</t>
+  </si>
+  <si>
+    <t>47369322</t>
+  </si>
+  <si>
+    <t>ROCHESTER ELECTRONICS</t>
+  </si>
+  <si>
+    <t>252395</t>
+  </si>
+  <si>
+    <t>Texas Instruments Taiwan Limited</t>
+  </si>
+  <si>
+    <t>4516450237</t>
+  </si>
+  <si>
+    <t>47188646</t>
+  </si>
+  <si>
+    <t>Completed PO</t>
+  </si>
+  <si>
+    <t>47218149</t>
+  </si>
+  <si>
+    <t>47245848</t>
+  </si>
+  <si>
+    <t>47245933</t>
+  </si>
+  <si>
+    <t>47253728</t>
+  </si>
+  <si>
+    <t>47264622</t>
+  </si>
+  <si>
+    <t>47274630</t>
+  </si>
+  <si>
+    <t>47276474</t>
+  </si>
+  <si>
+    <t>47283634</t>
+  </si>
+  <si>
+    <t>47283654</t>
+  </si>
+  <si>
+    <t>47286185</t>
+  </si>
+  <si>
+    <t>47289023</t>
+  </si>
+  <si>
+    <t>47290167</t>
+  </si>
+  <si>
+    <t>47292239</t>
+  </si>
+  <si>
+    <t>47292914</t>
+  </si>
+  <si>
+    <t>47296581</t>
+  </si>
+  <si>
+    <t>47296806</t>
+  </si>
+  <si>
+    <t>47301012</t>
+  </si>
+  <si>
+    <t>47301646</t>
+  </si>
+  <si>
+    <t>47304169</t>
+  </si>
+  <si>
+    <t>47324752</t>
+  </si>
+  <si>
+    <t>47345978</t>
+  </si>
+  <si>
+    <t>47352135</t>
+  </si>
+  <si>
+    <t>47361598</t>
+  </si>
+  <si>
+    <t>47361669</t>
+  </si>
+  <si>
+    <t>47362207</t>
+  </si>
+  <si>
+    <t>47362715</t>
+  </si>
+  <si>
+    <t>TBA_ADGT</t>
+  </si>
+  <si>
+    <t>TBD_SAMPLE</t>
+  </si>
+  <si>
+    <t>ANALOG DEVICES INC. CAMAS</t>
+  </si>
+  <si>
+    <t>47259467</t>
+  </si>
+  <si>
+    <t>Ardentec Korea Co., Ltd.</t>
+  </si>
+  <si>
+    <t>4516351202_ATK</t>
+  </si>
+  <si>
+    <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
+  </si>
+  <si>
+    <t>4516351202_ASESH</t>
+  </si>
+  <si>
+    <t>8541541216</t>
+  </si>
+  <si>
+    <t>8541550629</t>
+  </si>
+  <si>
+    <t>8541550824</t>
+  </si>
+  <si>
+    <t>8541563942</t>
+  </si>
+  <si>
+    <t>Boston Semi Equipment</t>
+  </si>
+  <si>
+    <t>TBDBSEMY</t>
+  </si>
+  <si>
+    <t>Boston Semi Equipment (Thailand) Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>TBA_BSETH</t>
+  </si>
+  <si>
+    <t>Boston Semi Equipment Asia</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>TBD_BSETWN</t>
+  </si>
+  <si>
+    <t>CARDIAC PACEMAKERS INC</t>
+  </si>
+  <si>
+    <t>7000627560</t>
+  </si>
+  <si>
+    <t>7000643410</t>
+  </si>
+  <si>
+    <t>7000667727</t>
+  </si>
+  <si>
+    <t>7000675296</t>
+  </si>
+  <si>
+    <t>7000696372</t>
+  </si>
+  <si>
+    <t>Hana Semiconductor (Ayutthaya) Co., Ltd</t>
+  </si>
+  <si>
+    <t>4910173913</t>
+  </si>
+  <si>
+    <t>TBD_EVALUATION</t>
+  </si>
+  <si>
+    <t>Hana Semiconductor (Ayutthaya) Co., Ltd (HNT)</t>
+  </si>
+  <si>
+    <t>4516351202_HNT</t>
+  </si>
+  <si>
+    <t>4910172298</t>
+  </si>
+  <si>
+    <t>JMC Worldwide Inc.</t>
+  </si>
+  <si>
+    <t>ES072525</t>
+  </si>
+  <si>
+    <t>Lingsen Precision Industries Ltd.</t>
+  </si>
+  <si>
+    <t>4516260169</t>
+  </si>
+  <si>
+    <t>4516446856</t>
+  </si>
+  <si>
+    <t>LPI-2507174</t>
+  </si>
+  <si>
+    <t>PP25-1057NI</t>
+  </si>
+  <si>
+    <t>PP25-1069NI</t>
+  </si>
+  <si>
+    <t>PP26-1025NI</t>
+  </si>
+  <si>
+    <t>3T/PO252272</t>
+  </si>
+  <si>
+    <t>3T/PO252305</t>
+  </si>
+  <si>
+    <t>3T/PO262313</t>
+  </si>
+  <si>
+    <t>3T/PO262321</t>
+  </si>
+  <si>
+    <t>3T/PO262326</t>
+  </si>
+  <si>
+    <t>3T/PO262331</t>
+  </si>
+  <si>
+    <t>3T/PO262333</t>
   </si>
   <si>
     <t>3T/PO262338</t>
   </si>
   <si>
-    <t>11 days before Due</t>
-  </si>
-  <si>
-    <t>UTAC Thai Limited ( UTL 3)</t>
+    <t>ON Semiconductor Philippines Inc</t>
+  </si>
+  <si>
+    <t>561000005506</t>
+  </si>
+  <si>
+    <t>561000006670</t>
+  </si>
+  <si>
+    <t>Rhenus Logistics Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>TBDBSETH</t>
+  </si>
+  <si>
+    <t>ST Microelectronics Pte Ltd.</t>
+  </si>
+  <si>
+    <t>4020007186</t>
+  </si>
+  <si>
+    <t>4020007647</t>
+  </si>
+  <si>
+    <t>STMicroelectronics, Inc.</t>
+  </si>
+  <si>
+    <t>3030012690</t>
+  </si>
+  <si>
+    <t>4010016033</t>
+  </si>
+  <si>
+    <t>4010016949</t>
+  </si>
+  <si>
+    <t>4010017076</t>
+  </si>
+  <si>
+    <t>4010017128</t>
+  </si>
+  <si>
+    <t>4010017970</t>
+  </si>
+  <si>
+    <t>4010018238</t>
+  </si>
+  <si>
+    <t>4010018600</t>
+  </si>
+  <si>
+    <t>4330007739</t>
+  </si>
+  <si>
+    <t>FOR TROUBLE SHOOT</t>
+  </si>
+  <si>
+    <t>SWINDON SILICON SYSTEMS</t>
+  </si>
+  <si>
+    <t>23397</t>
+  </si>
+  <si>
+    <t>BSE-58645</t>
+  </si>
+  <si>
+    <t>Texas Instruments CLAB</t>
+  </si>
+  <si>
+    <t>4516351202_CLAB</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS DE MEXICO</t>
+  </si>
+  <si>
+    <t>4516351202_TMX</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS DEUTSCHLAND GMBH</t>
+  </si>
+  <si>
+    <t>4516351202_FFAB</t>
+  </si>
+  <si>
+    <t>Texas Instruments FTLABS</t>
+  </si>
+  <si>
+    <t>4516351202_FTLABS</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS INCORPORATED</t>
+  </si>
+  <si>
+    <t>4516250020</t>
+  </si>
+  <si>
+    <t>4516317906</t>
+  </si>
+  <si>
+    <t>Texas Instruments Japan Limited (MIHO-ENG)</t>
+  </si>
+  <si>
+    <t>4516351202_MIHO-ENG</t>
+  </si>
+  <si>
+    <t>Texas Instruments RFAB</t>
+  </si>
+  <si>
+    <t>4516351202_RFAB</t>
+  </si>
+  <si>
+    <t>Texas Instruments SFAB</t>
+  </si>
+  <si>
+    <t>4516351202_SFAB</t>
+  </si>
+  <si>
+    <t>4516519979</t>
+  </si>
+  <si>
+    <t>4910171717</t>
+  </si>
+  <si>
+    <t>TI Philippines, Inc - Clark FT</t>
+  </si>
+  <si>
+    <t>4516351202_TICL-FT</t>
+  </si>
+  <si>
+    <t>TKC Enterprises Inc.</t>
+  </si>
+  <si>
+    <t>4516451338</t>
+  </si>
+  <si>
+    <t>43151446</t>
+  </si>
+  <si>
+    <t>43156228</t>
   </si>
   <si>
     <t>4516351202_UTL</t>
   </si>
   <si>
-    <t>10 days before Due</t>
-  </si>
-  <si>
-    <t>PO-468-061326-01</t>
-  </si>
-  <si>
-    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
-  </si>
-  <si>
-    <t>4516351202_MIHO</t>
-  </si>
-  <si>
-    <t>7 days before Due</t>
-  </si>
-  <si>
-    <t>TBA_NXP</t>
-  </si>
-  <si>
-    <t>1 days before Due</t>
-  </si>
-  <si>
-    <t>Lingsen Precision Industries Ltd.</t>
-  </si>
-  <si>
-    <t>4516446856</t>
-  </si>
-  <si>
-    <t>Due Today</t>
-  </si>
-  <si>
-    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
-  </si>
-  <si>
-    <t>4516351202_TII</t>
-  </si>
-  <si>
-    <t>Texas Instruments DMOS5</t>
-  </si>
-  <si>
-    <t>4516351202_DMOS5</t>
-  </si>
-  <si>
-    <t>Microprecision Calibration Inc.</t>
-  </si>
-  <si>
-    <t>PP26-1051NI</t>
-  </si>
-  <si>
-    <t>47364135</t>
-  </si>
-  <si>
-    <t>Texas Instruments LFAB</t>
-  </si>
-  <si>
-    <t>4516351202_LFAB</t>
-  </si>
-  <si>
-    <t>47362715</t>
-  </si>
-  <si>
-    <t>ROCHESTER ELECTRONICS</t>
-  </si>
-  <si>
-    <t>252395</t>
-  </si>
-  <si>
-    <t>Texas Instruments Taiwan Limited</t>
-  </si>
-  <si>
-    <t>4516450237</t>
-  </si>
-  <si>
-    <t>47188646</t>
-  </si>
-  <si>
-    <t>Completed PO</t>
-  </si>
-  <si>
-    <t>47218149</t>
-  </si>
-  <si>
-    <t>47245848</t>
-  </si>
-  <si>
-    <t>47245933</t>
-  </si>
-  <si>
-    <t>47253728</t>
-  </si>
-  <si>
-    <t>47264622</t>
-  </si>
-  <si>
-    <t>47274630</t>
-  </si>
-  <si>
-    <t>47276474</t>
-  </si>
-  <si>
-    <t>47283634</t>
-  </si>
-  <si>
-    <t>47283654</t>
-  </si>
-  <si>
-    <t>47286185</t>
-  </si>
-  <si>
-    <t>47289023</t>
-  </si>
-  <si>
-    <t>47290167</t>
-  </si>
-  <si>
-    <t>47292239</t>
-  </si>
-  <si>
-    <t>47292914</t>
-  </si>
-  <si>
-    <t>47296581</t>
-  </si>
-  <si>
-    <t>47296806</t>
-  </si>
-  <si>
-    <t>47301646</t>
-  </si>
-  <si>
-    <t>47304169</t>
-  </si>
-  <si>
-    <t>47324752</t>
-  </si>
-  <si>
-    <t>47345978</t>
-  </si>
-  <si>
-    <t>47352135</t>
-  </si>
-  <si>
-    <t>47361598</t>
-  </si>
-  <si>
-    <t>47361669</t>
-  </si>
-  <si>
-    <t>47362207</t>
-  </si>
-  <si>
-    <t>TBD_SAMPLE</t>
-  </si>
-  <si>
-    <t>ANALOG DEVICES INC. CAMAS</t>
-  </si>
-  <si>
-    <t>47259467</t>
-  </si>
-  <si>
-    <t>Ardentec Korea Co., Ltd.</t>
-  </si>
-  <si>
-    <t>4516351202_ATK</t>
-  </si>
-  <si>
-    <t>8541541216</t>
-  </si>
-  <si>
-    <t>8541550629</t>
-  </si>
-  <si>
-    <t>8541550824</t>
-  </si>
-  <si>
-    <t>8541563942</t>
-  </si>
-  <si>
-    <t>Boston Semi Equipment</t>
-  </si>
-  <si>
-    <t>TBDBSEMY</t>
-  </si>
-  <si>
-    <t>Boston Semi Equipment (Thailand) Co.,Ltd.</t>
-  </si>
-  <si>
-    <t>TBA_BSETH</t>
-  </si>
-  <si>
-    <t>Boston Semi Equipment Asia</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>TBD_BSETWN</t>
-  </si>
-  <si>
-    <t>CARDIAC PACEMAKERS INC</t>
-  </si>
-  <si>
-    <t>7000627560</t>
-  </si>
-  <si>
-    <t>7000643410</t>
-  </si>
-  <si>
-    <t>7000667727</t>
-  </si>
-  <si>
-    <t>7000675296</t>
-  </si>
-  <si>
-    <t>7000696372</t>
-  </si>
-  <si>
-    <t>Hana Semiconductor (Ayutthaya) Co., Ltd</t>
-  </si>
-  <si>
-    <t>4910173913</t>
-  </si>
-  <si>
-    <t>TBD_EVALUATION</t>
-  </si>
-  <si>
-    <t>Hana Semiconductor (Ayutthaya) Co., Ltd (HNT)</t>
-  </si>
-  <si>
-    <t>4516351202_HNT</t>
-  </si>
-  <si>
-    <t>4910172298</t>
-  </si>
-  <si>
-    <t>JMC Worldwide Inc.</t>
-  </si>
-  <si>
-    <t>ES072525</t>
-  </si>
-  <si>
-    <t>4516260169</t>
-  </si>
-  <si>
-    <t>LPI-2507174</t>
-  </si>
-  <si>
-    <t>PP25-1057NI</t>
-  </si>
-  <si>
-    <t>PP25-1069NI</t>
-  </si>
-  <si>
-    <t>PP26-1025NI</t>
-  </si>
-  <si>
-    <t>3T/PO252272</t>
-  </si>
-  <si>
-    <t>3T/PO252305</t>
-  </si>
-  <si>
-    <t>3T/PO262313</t>
-  </si>
-  <si>
-    <t>3T/PO262321</t>
-  </si>
-  <si>
-    <t>3T/PO262326</t>
-  </si>
-  <si>
-    <t>3T/PO262331</t>
-  </si>
-  <si>
-    <t>ON Semiconductor Philippines Inc</t>
-  </si>
-  <si>
-    <t>561000005506</t>
-  </si>
-  <si>
-    <t>561000006670</t>
-  </si>
-  <si>
-    <t>Rhenus Logistics Co.,Ltd.</t>
-  </si>
-  <si>
-    <t>TBDBSETH</t>
-  </si>
-  <si>
-    <t>ST Microelectronics Pte Ltd.</t>
-  </si>
-  <si>
-    <t>4020007186</t>
-  </si>
-  <si>
-    <t>4020007647</t>
-  </si>
-  <si>
-    <t>STMicroelectronics, Inc.</t>
-  </si>
-  <si>
-    <t>3030012690</t>
-  </si>
-  <si>
-    <t>4010016033</t>
-  </si>
-  <si>
-    <t>4010016949</t>
-  </si>
-  <si>
-    <t>4010017076</t>
-  </si>
-  <si>
-    <t>4010017128</t>
-  </si>
-  <si>
-    <t>4010017970</t>
-  </si>
-  <si>
-    <t>4010018238</t>
-  </si>
-  <si>
-    <t>4010018600</t>
-  </si>
-  <si>
-    <t>4330007739</t>
-  </si>
-  <si>
-    <t>FOR TROUBLE SHOOT</t>
-  </si>
-  <si>
-    <t>SWINDON SILICON SYSTEMS</t>
-  </si>
-  <si>
-    <t>23397</t>
-  </si>
-  <si>
-    <t>BSE-58645</t>
-  </si>
-  <si>
-    <t>Texas Instruments AIZU</t>
-  </si>
-  <si>
-    <t>4516351202_AIZU</t>
-  </si>
-  <si>
-    <t>Texas Instruments CLAB</t>
-  </si>
-  <si>
-    <t>4516351202_CLAB</t>
-  </si>
-  <si>
-    <t>TEXAS INSTRUMENTS DE MEXICO</t>
-  </si>
-  <si>
-    <t>4516351202_TMX</t>
-  </si>
-  <si>
-    <t>TEXAS INSTRUMENTS DEUTSCHLAND GMBH</t>
-  </si>
-  <si>
-    <t>4516351202_FFAB</t>
-  </si>
-  <si>
-    <t>Texas Instruments FTLABS</t>
-  </si>
-  <si>
-    <t>4516351202_FTLABS</t>
-  </si>
-  <si>
-    <t>TEXAS INSTRUMENTS INCORPORATED</t>
-  </si>
-  <si>
-    <t>4516250020</t>
-  </si>
-  <si>
-    <t>4516317906</t>
-  </si>
-  <si>
-    <t>Texas Instruments Japan Limited (MIHO-ENG)</t>
-  </si>
-  <si>
-    <t>4516351202_MIHO-ENG</t>
-  </si>
-  <si>
-    <t>Texas Instruments RFAB</t>
-  </si>
-  <si>
-    <t>4516351202_RFAB</t>
-  </si>
-  <si>
-    <t>Texas Instruments SFAB</t>
-  </si>
-  <si>
-    <t>4516351202_SFAB</t>
-  </si>
-  <si>
-    <t>4516519979</t>
-  </si>
-  <si>
-    <t>4910171717</t>
-  </si>
-  <si>
-    <t>TI Philippines, Inc - Clark FT</t>
-  </si>
-  <si>
-    <t>4516351202_TICL-FT</t>
-  </si>
-  <si>
-    <t>TKC Enterprises Inc.</t>
-  </si>
-  <si>
-    <t>4516451338</t>
-  </si>
-  <si>
-    <t>Tongfu Microelectronics Co.,Ltd.</t>
-  </si>
-  <si>
-    <t>4516351202_NFME</t>
-  </si>
-  <si>
-    <t>43151446</t>
-  </si>
-  <si>
-    <t>43156228</t>
-  </si>
-  <si>
-    <t>Last updated: 2026-07-13 09:11:56</t>
+    <t>Last updated: 2026-07-27 08:57:13</t>
   </si>
 </sst>
 </file>
@@ -980,12 +971,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:M123"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.5">
@@ -1058,7 +1049,7 @@
         <v>45898</v>
       </c>
       <c r="K3">
-        <v>-318</v>
+        <v>-332</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -1072,19 +1063,19 @@
         <v>17</v>
       </c>
       <c r="C4">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>11</v>
       </c>
       <c r="H4">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1093,7 +1084,7 @@
         <v>45898</v>
       </c>
       <c r="K4">
-        <v>-318</v>
+        <v>-332</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -1110,7 +1101,7 @@
         <v>20</v>
       </c>
       <c r="C5">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1122,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1131,7 +1122,7 @@
         <v>45898</v>
       </c>
       <c r="K5">
-        <v>-318</v>
+        <v>-332</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -1145,28 +1136,28 @@
         <v>22</v>
       </c>
       <c r="C6">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J6" s="1">
         <v>45898</v>
       </c>
       <c r="K6">
-        <v>-318</v>
+        <v>-332</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -1183,19 +1174,19 @@
         <v>25</v>
       </c>
       <c r="C7">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1204,21 +1195,18 @@
         <v>46062</v>
       </c>
       <c r="K7">
-        <v>-154</v>
+        <v>-168</v>
       </c>
       <c r="L7" t="s">
         <v>26</v>
       </c>
-      <c r="M7" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
         <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
       </c>
       <c r="C8">
         <v>259</v>
@@ -1242,36 +1230,36 @@
         <v>46108</v>
       </c>
       <c r="K8">
-        <v>-108</v>
+        <v>-122</v>
       </c>
       <c r="L8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s">
         <v>30</v>
-      </c>
-      <c r="M8" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
         <v>32</v>
       </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
       <c r="C9">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1280,36 +1268,36 @@
         <v>46139</v>
       </c>
       <c r="K9">
-        <v>-77</v>
+        <v>-91</v>
       </c>
       <c r="L9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M9" t="s">
         <v>34</v>
-      </c>
-      <c r="M9" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
         <v>36</v>
-      </c>
-      <c r="B10" t="s">
-        <v>37</v>
       </c>
       <c r="C10">
         <v>646</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1318,59 +1306,59 @@
         <v>46139</v>
       </c>
       <c r="K10">
-        <v>-77</v>
+        <v>-91</v>
       </c>
       <c r="L10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J11" s="1">
         <v>46155</v>
       </c>
       <c r="K11">
-        <v>-61</v>
+        <v>-75</v>
       </c>
       <c r="L11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M11" t="s">
         <v>40</v>
-      </c>
-      <c r="M11" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
         <v>42</v>
-      </c>
-      <c r="B12" t="s">
-        <v>43</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1394,126 +1382,123 @@
         <v>46188</v>
       </c>
       <c r="K12">
-        <v>-28</v>
+        <v>-42</v>
       </c>
       <c r="L12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
         <v>45</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13">
+        <v>172</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>169</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13" s="1">
+        <v>46223</v>
+      </c>
+      <c r="K13">
+        <v>-7</v>
+      </c>
+      <c r="L13" t="s">
         <v>46</v>
-      </c>
-      <c r="C13">
-        <v>10</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>9</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>46195</v>
-      </c>
-      <c r="K13">
-        <v>-21</v>
-      </c>
-      <c r="L13" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
         <v>48</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>46226</v>
+      </c>
+      <c r="K14">
+        <v>-4</v>
+      </c>
+      <c r="L14" t="s">
         <v>49</v>
-      </c>
-      <c r="C14">
-        <v>50</v>
-      </c>
-      <c r="D14">
-        <v>16</v>
-      </c>
-      <c r="E14">
-        <v>4</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>30</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14" s="1">
-        <v>46203</v>
-      </c>
-      <c r="K14">
-        <v>-13</v>
-      </c>
-      <c r="L14" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
         <v>51</v>
       </c>
       <c r="C15">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>46209</v>
+        <v>46244</v>
       </c>
       <c r="K15">
-        <v>-7</v>
+        <v>14</v>
       </c>
       <c r="L15" t="s">
         <v>52</v>
       </c>
-      <c r="M15" t="s">
-        <v>53</v>
-      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" t="s">
         <v>54</v>
-      </c>
-      <c r="B16" t="s">
-        <v>55</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1537,21 +1522,21 @@
         <v>46232</v>
       </c>
       <c r="K16">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="L16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
         <v>57</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1560,19 +1545,19 @@
         <v>2</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="I17">
         <v>2</v>
       </c>
       <c r="J17" s="1">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="K17">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L17" t="s">
         <v>58</v>
@@ -1586,66 +1571,57 @@
         <v>60</v>
       </c>
       <c r="C18">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="K18">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
         <v>62</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I19">
         <v>0</v>
-      </c>
-      <c r="J19" s="1">
-        <v>46226</v>
-      </c>
-      <c r="K19">
-        <v>10</v>
-      </c>
-      <c r="L19" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.5">
@@ -1656,112 +1632,85 @@
         <v>64</v>
       </c>
       <c r="C20">
-        <v>172</v>
+        <v>51</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H20">
-        <v>162</v>
+        <v>47</v>
       </c>
       <c r="I20">
-        <v>7</v>
-      </c>
-      <c r="J20" s="1">
-        <v>46223</v>
-      </c>
-      <c r="K20">
-        <v>7</v>
-      </c>
-      <c r="L20" t="s">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
         <v>66</v>
       </c>
       <c r="C21">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>2</v>
       </c>
       <c r="H21">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I21">
         <v>0</v>
-      </c>
-      <c r="J21" s="1">
-        <v>46217</v>
-      </c>
-      <c r="K21">
-        <v>1</v>
-      </c>
-      <c r="L21" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C22">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I22">
         <v>0</v>
-      </c>
-      <c r="J22" s="1">
-        <v>46216</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C23">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1770,10 +1719,10 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1781,25 +1730,25 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C24">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1807,25 +1756,25 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1833,25 +1782,25 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1859,13 +1808,13 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1874,10 +1823,13 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G27" t="s">
+        <v>77</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1885,16 +1837,16 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1902,8 +1854,11 @@
       <c r="F28">
         <v>0</v>
       </c>
+      <c r="G28" t="s">
+        <v>77</v>
+      </c>
       <c r="H28">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1911,25 +1866,28 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A29" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C29">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
+      <c r="G29" t="s">
+        <v>77</v>
+      </c>
       <c r="H29">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1937,25 +1895,28 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C30">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
+      <c r="G30" t="s">
+        <v>77</v>
+      </c>
       <c r="H30">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1963,13 +1924,13 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C31">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1981,10 +1942,10 @@
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H31">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1992,13 +1953,13 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C32">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -2010,10 +1971,10 @@
         <v>0</v>
       </c>
       <c r="G32" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H32">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -2021,10 +1982,10 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -2039,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -2050,10 +2011,10 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -2068,7 +2029,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -2079,13 +2040,13 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -2097,10 +2058,10 @@
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2108,13 +2069,13 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2126,10 +2087,10 @@
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2137,10 +2098,10 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -2155,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -2166,13 +2127,13 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2184,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2195,13 +2156,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2213,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H39">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2224,10 +2185,10 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B40" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C40">
         <v>2</v>
@@ -2242,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H40">
         <v>2</v>
@@ -2253,10 +2214,10 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A41" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B41" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -2271,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -2282,13 +2243,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2300,10 +2261,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H42">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2311,13 +2272,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2329,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2340,13 +2301,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2358,10 +2319,10 @@
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H44">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2369,13 +2330,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B45" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2387,10 +2348,10 @@
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2398,13 +2359,13 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B46" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C46">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2416,10 +2377,10 @@
         <v>0</v>
       </c>
       <c r="G46" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H46">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2427,10 +2388,10 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C47">
         <v>4</v>
@@ -2445,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H47">
         <v>4</v>
@@ -2456,13 +2417,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B48" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2474,10 +2435,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2485,13 +2446,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B49" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2503,10 +2464,10 @@
         <v>0</v>
       </c>
       <c r="G49" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2514,13 +2475,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B50" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2532,10 +2493,10 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2543,13 +2504,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B51" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2561,10 +2522,10 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2572,13 +2533,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B52" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C52">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2590,10 +2551,10 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H52">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2601,13 +2562,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B53" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2619,10 +2580,10 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2630,13 +2591,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B54" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2648,10 +2609,10 @@
         <v>0</v>
       </c>
       <c r="G54" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2659,10 +2620,10 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B55" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -2677,7 +2638,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -2688,10 +2649,10 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="B56" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -2706,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -2717,13 +2678,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B57" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2735,10 +2696,10 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2746,13 +2707,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B58" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C58">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2764,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H58">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2775,10 +2736,10 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B59" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -2793,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -2804,10 +2765,10 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B60" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -2822,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H60">
         <v>2</v>
@@ -2833,10 +2794,10 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B61" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C61">
         <v>7</v>
@@ -2851,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H61">
         <v>7</v>
@@ -2862,10 +2823,10 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A62" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B62" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C62">
         <v>3</v>
@@ -2880,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H62">
         <v>3</v>
@@ -2891,10 +2852,10 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A63" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B63" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -2909,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -2920,10 +2881,10 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A64" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B64" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -2938,7 +2899,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -2949,10 +2910,10 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A65" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B65" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C65">
         <v>2</v>
@@ -2967,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H65">
         <v>2</v>
@@ -2978,10 +2939,10 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A66" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B66" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -2996,7 +2957,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -3007,10 +2968,10 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A67" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B67" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C67">
         <v>30</v>
@@ -3025,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H67">
         <v>30</v>
@@ -3036,10 +2997,10 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A68" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B68" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C68">
         <v>17</v>
@@ -3054,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H68">
         <v>17</v>
@@ -3065,10 +3026,10 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B69" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -3083,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -3094,10 +3055,10 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A70" t="s">
+        <v>123</v>
+      </c>
+      <c r="B70" t="s">
         <v>127</v>
-      </c>
-      <c r="B70" t="s">
-        <v>131</v>
       </c>
       <c r="C70">
         <v>2</v>
@@ -3112,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H70">
         <v>2</v>
@@ -3123,10 +3084,10 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B71" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C71">
         <v>10</v>
@@ -3141,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H71">
         <v>10</v>
@@ -3152,10 +3113,10 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A72" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B72" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C72">
         <v>6</v>
@@ -3170,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H72">
         <v>6</v>
@@ -3181,10 +3142,10 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A73" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B73" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C73">
         <v>5</v>
@@ -3199,7 +3160,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H73">
         <v>5</v>
@@ -3210,10 +3171,10 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A74" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B74" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C74">
         <v>19</v>
@@ -3228,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H74">
         <v>19</v>
@@ -3239,10 +3200,10 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A75" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B75" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C75">
         <v>10</v>
@@ -3257,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H75">
         <v>10</v>
@@ -3268,10 +3229,10 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A76" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B76" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C76">
         <v>2</v>
@@ -3286,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H76">
         <v>2</v>
@@ -3297,10 +3258,10 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A77" t="s">
-        <v>68</v>
+        <v>137</v>
       </c>
       <c r="B77" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C77">
         <v>28</v>
@@ -3315,7 +3276,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H77">
         <v>28</v>
@@ -3326,13 +3287,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A78" t="s">
-        <v>68</v>
+        <v>137</v>
       </c>
       <c r="B78" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3344,10 +3305,10 @@
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3355,13 +3316,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A79" t="s">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="B79" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3373,10 +3334,10 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3384,13 +3345,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A80" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B80" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3402,10 +3363,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3413,10 +3374,10 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A81" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B81" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -3431,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -3442,10 +3403,10 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A82" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B82" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -3460,7 +3421,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -3471,13 +3432,13 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B83" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -3489,10 +3450,10 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -3500,10 +3461,10 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A84" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B84" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C84">
         <v>3</v>
@@ -3518,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H84">
         <v>3</v>
@@ -3529,10 +3490,10 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A85" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B85" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C85">
         <v>3</v>
@@ -3547,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H85">
         <v>3</v>
@@ -3558,10 +3519,10 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A86" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B86" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C86">
         <v>3</v>
@@ -3576,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H86">
         <v>3</v>
@@ -3587,13 +3548,13 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A87" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B87" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C87">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -3605,10 +3566,10 @@
         <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H87">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -3616,13 +3577,13 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A88" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B88" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3634,10 +3595,10 @@
         <v>0</v>
       </c>
       <c r="G88" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H88">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -3645,13 +3606,13 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A89" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="B89" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C89">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3663,10 +3624,10 @@
         <v>0</v>
       </c>
       <c r="G89" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H89">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -3674,13 +3635,13 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A90" t="s">
-        <v>155</v>
+        <v>50</v>
       </c>
       <c r="B90" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C90">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3692,10 +3653,10 @@
         <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H90">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -3703,13 +3664,13 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A91" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B91" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C91">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3721,10 +3682,10 @@
         <v>0</v>
       </c>
       <c r="G91" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H91">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -3732,10 +3693,10 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A92" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B92" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C92">
         <v>5</v>
@@ -3750,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H92">
         <v>5</v>
@@ -3761,13 +3722,13 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A93" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B93" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C93">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3779,10 +3740,10 @@
         <v>0</v>
       </c>
       <c r="G93" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H93">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -3790,13 +3751,13 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A94" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B94" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3808,10 +3769,10 @@
         <v>0</v>
       </c>
       <c r="G94" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H94">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -3819,13 +3780,13 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A95" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B95" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3837,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="G95" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H95">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -3851,10 +3812,10 @@
         <v>160</v>
       </c>
       <c r="B96" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3866,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="G96" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H96">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -3880,7 +3841,7 @@
         <v>160</v>
       </c>
       <c r="B97" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -3895,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -3909,7 +3870,7 @@
         <v>160</v>
       </c>
       <c r="B98" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -3924,7 +3885,7 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -3938,7 +3899,7 @@
         <v>160</v>
       </c>
       <c r="B99" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -3953,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="G99" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -3967,7 +3928,7 @@
         <v>160</v>
       </c>
       <c r="B100" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -3982,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -3996,10 +3957,10 @@
         <v>160</v>
       </c>
       <c r="B101" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C101">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -4011,10 +3972,10 @@
         <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H101">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -4025,7 +3986,7 @@
         <v>160</v>
       </c>
       <c r="B102" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C102">
         <v>1</v>
@@ -4040,7 +4001,7 @@
         <v>0</v>
       </c>
       <c r="G102" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -4051,13 +4012,13 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A103" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="B103" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -4069,10 +4030,10 @@
         <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -4080,13 +4041,13 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A104" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="B104" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C104">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -4098,10 +4059,10 @@
         <v>0</v>
       </c>
       <c r="G104" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H104">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -4109,13 +4070,13 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A105" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="B105" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C105">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -4127,10 +4088,10 @@
         <v>0</v>
       </c>
       <c r="G105" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H105">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -4138,13 +4099,13 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A106" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B106" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -4156,10 +4117,10 @@
         <v>0</v>
       </c>
       <c r="G106" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -4167,13 +4128,13 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A107" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B107" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -4185,10 +4146,10 @@
         <v>0</v>
       </c>
       <c r="G107" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I107">
         <v>0</v>
@@ -4196,13 +4157,13 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A108" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B108" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C108">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -4214,10 +4175,10 @@
         <v>0</v>
       </c>
       <c r="G108" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H108">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -4225,10 +4186,10 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A109" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B109" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C109">
         <v>1</v>
@@ -4243,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H109">
         <v>1</v>
@@ -4254,13 +4215,13 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A110" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B110" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C110">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -4272,10 +4233,10 @@
         <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H110">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I110">
         <v>0</v>
@@ -4283,13 +4244,13 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A111" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B111" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D111">
         <v>0</v>
@@ -4301,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="G111" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I111">
         <v>0</v>
@@ -4312,13 +4273,13 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A112" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B112" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C112">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -4330,10 +4291,10 @@
         <v>0</v>
       </c>
       <c r="G112" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H112">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -4341,10 +4302,10 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A113" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B113" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C113">
         <v>2</v>
@@ -4359,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H113">
         <v>2</v>
@@ -4370,10 +4331,10 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A114" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B114" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C114">
         <v>9</v>
@@ -4388,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H114">
         <v>9</v>
@@ -4399,10 +4360,10 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A115" t="s">
-        <v>83</v>
+        <v>187</v>
       </c>
       <c r="B115" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C115">
         <v>2</v>
@@ -4417,7 +4378,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H115">
         <v>2</v>
@@ -4428,13 +4389,13 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A116" t="s">
-        <v>83</v>
+        <v>189</v>
       </c>
       <c r="B116" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C116">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -4446,10 +4407,10 @@
         <v>0</v>
       </c>
       <c r="G116" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H116">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -4457,13 +4418,13 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A117" t="s">
-        <v>195</v>
+        <v>74</v>
       </c>
       <c r="B117" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C117">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -4475,10 +4436,10 @@
         <v>0</v>
       </c>
       <c r="G117" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H117">
-        <v>170</v>
+        <v>2</v>
       </c>
       <c r="I117">
         <v>0</v>
@@ -4486,13 +4447,13 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A118" t="s">
-        <v>197</v>
+        <v>74</v>
       </c>
       <c r="B118" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C118">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -4504,10 +4465,10 @@
         <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H118">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I118">
         <v>0</v>
@@ -4515,13 +4476,13 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A119" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B119" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C119">
-        <v>15</v>
+        <v>170</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -4533,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="G119" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H119">
-        <v>15</v>
+        <v>170</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -4544,10 +4505,10 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A120" t="s">
-        <v>59</v>
+        <v>195</v>
       </c>
       <c r="B120" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C120">
         <v>1</v>
@@ -4562,7 +4523,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H120">
         <v>1</v>
@@ -4573,10 +4534,10 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A121" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B121" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C121">
         <v>1</v>
@@ -4591,12 +4552,70 @@
         <v>0</v>
       </c>
       <c r="G121" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H121">
         <v>1</v>
       </c>
       <c r="I121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A122" t="s">
+        <v>47</v>
+      </c>
+      <c r="B122" t="s">
+        <v>198</v>
+      </c>
+      <c r="C122">
+        <v>1</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122" t="s">
+        <v>77</v>
+      </c>
+      <c r="H122">
+        <v>1</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A123" t="s">
+        <v>47</v>
+      </c>
+      <c r="B123" t="s">
+        <v>199</v>
+      </c>
+      <c r="C123">
+        <v>15</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123" t="s">
+        <v>77</v>
+      </c>
+      <c r="H123">
+        <v>15</v>
+      </c>
+      <c r="I123">
         <v>0</v>
       </c>
     </row>

--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB90795B4EE0D79ECA7653592CA70D9E37A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DB22E8F-3D42-4057-B616-81BCD1EF7549}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB99C2D77CC8F78EC887DB0AE8470D9E34B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C899468-6068-4630-B367-6992FD3D9E26}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70,7 +70,7 @@
     <t>4516351202_ASEWH</t>
   </si>
   <si>
-    <t>OverDue by 332 days</t>
+    <t>OverDue by 333 days</t>
   </si>
   <si>
     <t>Texas Instruments SCT</t>
@@ -103,7 +103,7 @@
     <t>Global PO 4516351202</t>
   </si>
   <si>
-    <t>OverDue by 168 days</t>
+    <t>OverDue by 169 days</t>
   </si>
   <si>
     <t>ARDENTEC CORPORATION</t>
@@ -112,7 +112,7 @@
     <t>4516351202_ARD</t>
   </si>
   <si>
-    <t>OverDue by 122 days</t>
+    <t>OverDue by 123 days</t>
   </si>
   <si>
     <t>Varies (2026-03-27 → 2026-05-19)</t>
@@ -124,7 +124,7 @@
     <t>47270551</t>
   </si>
   <si>
-    <t>OverDue by 91 days</t>
+    <t>OverDue by 92 days</t>
   </si>
   <si>
     <t>Varies (2026-04-27 → 2026-06-30)</t>
@@ -142,7 +142,7 @@
     <t>47318424</t>
   </si>
   <si>
-    <t>OverDue by 75 days</t>
+    <t>OverDue by 76 days</t>
   </si>
   <si>
     <t>Varies (2026-05-13 → 2026-06-09)</t>
@@ -154,7 +154,7 @@
     <t>MO262002496</t>
   </si>
   <si>
-    <t>OverDue by 42 days</t>
+    <t>OverDue by 43 days</t>
   </si>
   <si>
     <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
@@ -163,7 +163,7 @@
     <t>4516351202_MIHO</t>
   </si>
   <si>
-    <t>OverDue by 7 days</t>
+    <t>OverDue by 8 days</t>
   </si>
   <si>
     <t>UTAC Thai Limited ( UTL 3)</t>
@@ -172,7 +172,7 @@
     <t>PO-468-061326-01</t>
   </si>
   <si>
-    <t>OverDue by 4 days</t>
+    <t>OverDue by 5 days</t>
   </si>
   <si>
     <t>NXP Malaysia Sdn. Bhd.</t>
@@ -181,7 +181,7 @@
     <t>TBA_NXP</t>
   </si>
   <si>
-    <t>14 days before Due</t>
+    <t>13 days before Due</t>
   </si>
   <si>
     <t>AVAGO TECHNOLOGIES_x000D_
@@ -191,7 +191,7 @@
     <t>8541571063</t>
   </si>
   <si>
-    <t>2 days before Due</t>
+    <t>1 days before Due</t>
   </si>
   <si>
     <t>Texas Instruments DMOS5</t>
@@ -200,7 +200,7 @@
     <t>4516351202_DMOS5</t>
   </si>
   <si>
-    <t>1 days before Due</t>
+    <t>Due Today</t>
   </si>
   <si>
     <t>Tongfu Microelectronics Co.,Ltd.</t>
@@ -626,7 +626,7 @@
     <t>4516351202_UTL</t>
   </si>
   <si>
-    <t>Last updated: 2026-07-27 08:57:13</t>
+    <t>Last updated: 2026-07-28 09:33:59</t>
   </si>
 </sst>
 </file>
@@ -1049,7 +1049,7 @@
         <v>45898</v>
       </c>
       <c r="K3">
-        <v>-332</v>
+        <v>-333</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -1066,10 +1066,10 @@
         <v>355</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4">
         <v>11</v>
@@ -1084,7 +1084,7 @@
         <v>45898</v>
       </c>
       <c r="K4">
-        <v>-332</v>
+        <v>-333</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -1122,7 +1122,7 @@
         <v>45898</v>
       </c>
       <c r="K5">
-        <v>-332</v>
+        <v>-333</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -1139,25 +1139,25 @@
         <v>222</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F6">
         <v>10</v>
       </c>
       <c r="H6">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1">
         <v>45898</v>
       </c>
       <c r="K6">
-        <v>-332</v>
+        <v>-333</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -1195,7 +1195,7 @@
         <v>46062</v>
       </c>
       <c r="K7">
-        <v>-168</v>
+        <v>-169</v>
       </c>
       <c r="L7" t="s">
         <v>26</v>
@@ -1230,7 +1230,7 @@
         <v>46108</v>
       </c>
       <c r="K8">
-        <v>-122</v>
+        <v>-123</v>
       </c>
       <c r="L8" t="s">
         <v>29</v>
@@ -1268,7 +1268,7 @@
         <v>46139</v>
       </c>
       <c r="K9">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="L9" t="s">
         <v>33</v>
@@ -1285,16 +1285,16 @@
         <v>36</v>
       </c>
       <c r="C10">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H10">
         <v>637</v>
@@ -1306,7 +1306,7 @@
         <v>46139</v>
       </c>
       <c r="K10">
-        <v>-91</v>
+        <v>-92</v>
       </c>
       <c r="L10" t="s">
         <v>33</v>
@@ -1326,10 +1326,10 @@
         <v>25</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1344,7 +1344,7 @@
         <v>46155</v>
       </c>
       <c r="K11">
-        <v>-75</v>
+        <v>-76</v>
       </c>
       <c r="L11" t="s">
         <v>39</v>
@@ -1382,7 +1382,7 @@
         <v>46188</v>
       </c>
       <c r="K12">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="L12" t="s">
         <v>43</v>
@@ -1408,16 +1408,16 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="1">
         <v>46223</v>
       </c>
       <c r="K13">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="L13" t="s">
         <v>46</v>
@@ -1434,10 +1434,10 @@
         <v>5</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1452,7 +1452,7 @@
         <v>46226</v>
       </c>
       <c r="K14">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="L14" t="s">
         <v>49</v>
@@ -1487,7 +1487,7 @@
         <v>46244</v>
       </c>
       <c r="K15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L15" t="s">
         <v>52</v>
@@ -1522,7 +1522,7 @@
         <v>46232</v>
       </c>
       <c r="K16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L16" t="s">
         <v>55</v>
@@ -1548,16 +1548,16 @@
         <v>1</v>
       </c>
       <c r="H17">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" s="1">
         <v>46231</v>
       </c>
       <c r="K17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="s">
         <v>58</v>
@@ -1592,7 +1592,7 @@
         <v>46231</v>
       </c>
       <c r="K18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="s">
         <v>58</v>

--- a/po-status.xlsx
+++ b/po-status.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mvtstechnologies-my.sharepoint.com/personal/edsel_solon_bsegroup_com/Documents/Github Projects/PO_Status/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB99C2D77CC8F78EC887DB0AE8470D9E34B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C899468-6068-4630-B367-6992FD3D9E26}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_BEA61AB913BD779C031AE933BD3190EA71D9FE0D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD7D6D67-BEDE-49CD-9B9E-0FC8126ACC79}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13986" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="PO_StatusQry" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$123</definedName>
+    <definedName name="PO_StatusQry">PO_StatusQry!$A$2:$M$125</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="203">
   <si>
     <t>CustName</t>
   </si>
@@ -70,7 +70,7 @@
     <t>4516351202_ASEWH</t>
   </si>
   <si>
-    <t>OverDue by 333 days</t>
+    <t>OverDue by 340 days</t>
   </si>
   <si>
     <t>Texas Instruments SCT</t>
@@ -103,7 +103,7 @@
     <t>Global PO 4516351202</t>
   </si>
   <si>
-    <t>OverDue by 169 days</t>
+    <t>OverDue by 176 days</t>
   </si>
   <si>
     <t>ARDENTEC CORPORATION</t>
@@ -112,7 +112,7 @@
     <t>4516351202_ARD</t>
   </si>
   <si>
-    <t>OverDue by 123 days</t>
+    <t>OverDue by 130 days</t>
   </si>
   <si>
     <t>Varies (2026-03-27 → 2026-05-19)</t>
@@ -124,10 +124,7 @@
     <t>47270551</t>
   </si>
   <si>
-    <t>OverDue by 92 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-04-27 → 2026-06-30)</t>
+    <t>OverDue by 99 days</t>
   </si>
   <si>
     <t>TI (Philippines) Inc.</t>
@@ -136,16 +133,16 @@
     <t>4516351202_TIPI</t>
   </si>
   <si>
-    <t>Varies (2026-04-27 → 2026-07-13)</t>
+    <t>Varies (2026-04-27 → 2026-06-25)</t>
   </si>
   <si>
     <t>47318424</t>
   </si>
   <si>
-    <t>OverDue by 76 days</t>
-  </si>
-  <si>
-    <t>Varies (2026-05-13 → 2026-06-09)</t>
+    <t>OverDue by 83 days</t>
+  </si>
+  <si>
+    <t>Varies (2026-05-13 → 2026-08-25)</t>
   </si>
   <si>
     <t>ASE CO., LTD - PHILIPPINES BRANCH 01-075</t>
@@ -154,16 +151,7 @@
     <t>MO262002496</t>
   </si>
   <si>
-    <t>OverDue by 43 days</t>
-  </si>
-  <si>
-    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
-  </si>
-  <si>
-    <t>4516351202_MIHO</t>
-  </si>
-  <si>
-    <t>OverDue by 8 days</t>
+    <t>OverDue by 50 days</t>
   </si>
   <si>
     <t>UTAC Thai Limited ( UTL 3)</t>
@@ -172,16 +160,16 @@
     <t>PO-468-061326-01</t>
   </si>
   <si>
-    <t>OverDue by 5 days</t>
-  </si>
-  <si>
-    <t>NXP Malaysia Sdn. Bhd.</t>
-  </si>
-  <si>
-    <t>TBA_NXP</t>
-  </si>
-  <si>
-    <t>13 days before Due</t>
+    <t>OverDue by 12 days</t>
+  </si>
+  <si>
+    <t>Tongfu Microelectronics Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>4516351202_NFME</t>
+  </si>
+  <si>
+    <t>OverDue by 7 days</t>
   </si>
   <si>
     <t>AVAGO TECHNOLOGIES_x000D_
@@ -191,7 +179,52 @@
     <t>8541571063</t>
   </si>
   <si>
-    <t>1 days before Due</t>
+    <t>OverDue by 6 days</t>
+  </si>
+  <si>
+    <t>47364135</t>
+  </si>
+  <si>
+    <t>14 days before Due</t>
+  </si>
+  <si>
+    <t>Texas Instruments AIZU</t>
+  </si>
+  <si>
+    <t>4516351202_AIZU</t>
+  </si>
+  <si>
+    <t>9 days before Due</t>
+  </si>
+  <si>
+    <t>NXP Malaysia Sdn. Bhd.</t>
+  </si>
+  <si>
+    <t>TBA_NXP</t>
+  </si>
+  <si>
+    <t>6 days before Due</t>
+  </si>
+  <si>
+    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
+  </si>
+  <si>
+    <t>4516351202_TII</t>
+  </si>
+  <si>
+    <t>3T/PO262348</t>
+  </si>
+  <si>
+    <t>Texas Instruments Taiwan Limited</t>
+  </si>
+  <si>
+    <t>4516450237</t>
+  </si>
+  <si>
+    <t>3T/PO262347</t>
+  </si>
+  <si>
+    <t>4516351202_UTL</t>
   </si>
   <si>
     <t>Texas Instruments DMOS5</t>
@@ -200,264 +233,240 @@
     <t>4516351202_DMOS5</t>
   </si>
   <si>
-    <t>Due Today</t>
-  </si>
-  <si>
-    <t>Tongfu Microelectronics Co.,Ltd.</t>
-  </si>
-  <si>
-    <t>4516351202_NFME</t>
-  </si>
-  <si>
-    <t>TEXAS INSTRUMENTS (INDIA) Pvt. Ltd</t>
-  </si>
-  <si>
-    <t>4516351202_TII</t>
-  </si>
-  <si>
-    <t>Texas Instruments AIZU</t>
-  </si>
-  <si>
-    <t>4516351202_AIZU</t>
+    <t>Texas Instruments LFAB</t>
+  </si>
+  <si>
+    <t>4516351202_LFAB</t>
+  </si>
+  <si>
+    <t>ANALOG DEVICES INC.</t>
+  </si>
+  <si>
+    <t>47369322</t>
+  </si>
+  <si>
+    <t>ROCHESTER ELECTRONICS</t>
+  </si>
+  <si>
+    <t>252395</t>
+  </si>
+  <si>
+    <t>Texas Instruments Japan Limited MIHO Plant (MIHO 8 FAB)</t>
+  </si>
+  <si>
+    <t>4516351202_MIHO</t>
+  </si>
+  <si>
+    <t>Completed PO</t>
+  </si>
+  <si>
+    <t>47188646</t>
+  </si>
+  <si>
+    <t>47218149</t>
+  </si>
+  <si>
+    <t>47245848</t>
+  </si>
+  <si>
+    <t>47245933</t>
+  </si>
+  <si>
+    <t>47253728</t>
+  </si>
+  <si>
+    <t>47264622</t>
+  </si>
+  <si>
+    <t>47274630</t>
+  </si>
+  <si>
+    <t>47276474</t>
+  </si>
+  <si>
+    <t>47283634</t>
+  </si>
+  <si>
+    <t>47283654</t>
+  </si>
+  <si>
+    <t>47286185</t>
+  </si>
+  <si>
+    <t>47289023</t>
+  </si>
+  <si>
+    <t>47290167</t>
+  </si>
+  <si>
+    <t>47292239</t>
+  </si>
+  <si>
+    <t>47292914</t>
+  </si>
+  <si>
+    <t>47296581</t>
+  </si>
+  <si>
+    <t>47296806</t>
+  </si>
+  <si>
+    <t>47301012</t>
+  </si>
+  <si>
+    <t>47301646</t>
+  </si>
+  <si>
+    <t>47304169</t>
+  </si>
+  <si>
+    <t>47324752</t>
+  </si>
+  <si>
+    <t>47345978</t>
+  </si>
+  <si>
+    <t>47352135</t>
+  </si>
+  <si>
+    <t>47361598</t>
+  </si>
+  <si>
+    <t>47361669</t>
+  </si>
+  <si>
+    <t>47362207</t>
+  </si>
+  <si>
+    <t>47362715</t>
+  </si>
+  <si>
+    <t>TBA_ADGT</t>
+  </si>
+  <si>
+    <t>TBD_SAMPLE</t>
+  </si>
+  <si>
+    <t>ANALOG DEVICES INC. CAMAS</t>
+  </si>
+  <si>
+    <t>47259467</t>
+  </si>
+  <si>
+    <t>Ardentec Korea Co., Ltd.</t>
+  </si>
+  <si>
+    <t>4516351202_ATK</t>
+  </si>
+  <si>
+    <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
+  </si>
+  <si>
+    <t>4516351202_ASESH</t>
+  </si>
+  <si>
+    <t>8541541216</t>
+  </si>
+  <si>
+    <t>8541550629</t>
+  </si>
+  <si>
+    <t>8541550824</t>
+  </si>
+  <si>
+    <t>8541563942</t>
+  </si>
+  <si>
+    <t>Boston Semi Equipment</t>
+  </si>
+  <si>
+    <t>TBDBSEMY</t>
+  </si>
+  <si>
+    <t>Boston Semi Equipment (Thailand) Co.,Ltd.</t>
+  </si>
+  <si>
+    <t>TBA_BSETH</t>
+  </si>
+  <si>
+    <t>Boston Semi Equipment Asia</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>TBD_BSETWN</t>
+  </si>
+  <si>
+    <t>CARDIAC PACEMAKERS INC</t>
+  </si>
+  <si>
+    <t>7000627560</t>
+  </si>
+  <si>
+    <t>7000643410</t>
+  </si>
+  <si>
+    <t>7000667727</t>
+  </si>
+  <si>
+    <t>7000675296</t>
+  </si>
+  <si>
+    <t>7000696372</t>
+  </si>
+  <si>
+    <t>Hana Semiconductor (Ayutthaya) Co., Ltd</t>
+  </si>
+  <si>
+    <t>4910173913</t>
+  </si>
+  <si>
+    <t>TBD_EVALUATION</t>
+  </si>
+  <si>
+    <t>Hana Semiconductor (Ayutthaya) Co., Ltd (HNT)</t>
+  </si>
+  <si>
+    <t>4516351202_HNT</t>
+  </si>
+  <si>
+    <t>4910172298</t>
+  </si>
+  <si>
+    <t>JMC Worldwide Inc.</t>
+  </si>
+  <si>
+    <t>ES072525</t>
+  </si>
+  <si>
+    <t>Lingsen Precision Industries Ltd.</t>
+  </si>
+  <si>
+    <t>4516260169</t>
+  </si>
+  <si>
+    <t>4516446856</t>
+  </si>
+  <si>
+    <t>LPI-2507174</t>
   </si>
   <si>
     <t>Microprecision Calibration Inc.</t>
   </si>
   <si>
+    <t>PP25-1057NI</t>
+  </si>
+  <si>
+    <t>PP25-1069NI</t>
+  </si>
+  <si>
+    <t>PP26-1025NI</t>
+  </si>
+  <si>
     <t>PP26-1051NI</t>
   </si>
   <si>
-    <t>47364135</t>
-  </si>
-  <si>
-    <t>Texas Instruments LFAB</t>
-  </si>
-  <si>
-    <t>4516351202_LFAB</t>
-  </si>
-  <si>
-    <t>ANALOG DEVICES INC.</t>
-  </si>
-  <si>
-    <t>47369322</t>
-  </si>
-  <si>
-    <t>ROCHESTER ELECTRONICS</t>
-  </si>
-  <si>
-    <t>252395</t>
-  </si>
-  <si>
-    <t>Texas Instruments Taiwan Limited</t>
-  </si>
-  <si>
-    <t>4516450237</t>
-  </si>
-  <si>
-    <t>47188646</t>
-  </si>
-  <si>
-    <t>Completed PO</t>
-  </si>
-  <si>
-    <t>47218149</t>
-  </si>
-  <si>
-    <t>47245848</t>
-  </si>
-  <si>
-    <t>47245933</t>
-  </si>
-  <si>
-    <t>47253728</t>
-  </si>
-  <si>
-    <t>47264622</t>
-  </si>
-  <si>
-    <t>47274630</t>
-  </si>
-  <si>
-    <t>47276474</t>
-  </si>
-  <si>
-    <t>47283634</t>
-  </si>
-  <si>
-    <t>47283654</t>
-  </si>
-  <si>
-    <t>47286185</t>
-  </si>
-  <si>
-    <t>47289023</t>
-  </si>
-  <si>
-    <t>47290167</t>
-  </si>
-  <si>
-    <t>47292239</t>
-  </si>
-  <si>
-    <t>47292914</t>
-  </si>
-  <si>
-    <t>47296581</t>
-  </si>
-  <si>
-    <t>47296806</t>
-  </si>
-  <si>
-    <t>47301012</t>
-  </si>
-  <si>
-    <t>47301646</t>
-  </si>
-  <si>
-    <t>47304169</t>
-  </si>
-  <si>
-    <t>47324752</t>
-  </si>
-  <si>
-    <t>47345978</t>
-  </si>
-  <si>
-    <t>47352135</t>
-  </si>
-  <si>
-    <t>47361598</t>
-  </si>
-  <si>
-    <t>47361669</t>
-  </si>
-  <si>
-    <t>47362207</t>
-  </si>
-  <si>
-    <t>47362715</t>
-  </si>
-  <si>
-    <t>TBA_ADGT</t>
-  </si>
-  <si>
-    <t>TBD_SAMPLE</t>
-  </si>
-  <si>
-    <t>ANALOG DEVICES INC. CAMAS</t>
-  </si>
-  <si>
-    <t>47259467</t>
-  </si>
-  <si>
-    <t>Ardentec Korea Co., Ltd.</t>
-  </si>
-  <si>
-    <t>4516351202_ATK</t>
-  </si>
-  <si>
-    <t>ATX SEMICONDUCTOR (SHANGHAI) CO.,LTD.</t>
-  </si>
-  <si>
-    <t>4516351202_ASESH</t>
-  </si>
-  <si>
-    <t>8541541216</t>
-  </si>
-  <si>
-    <t>8541550629</t>
-  </si>
-  <si>
-    <t>8541550824</t>
-  </si>
-  <si>
-    <t>8541563942</t>
-  </si>
-  <si>
-    <t>Boston Semi Equipment</t>
-  </si>
-  <si>
-    <t>TBDBSEMY</t>
-  </si>
-  <si>
-    <t>Boston Semi Equipment (Thailand) Co.,Ltd.</t>
-  </si>
-  <si>
-    <t>TBA_BSETH</t>
-  </si>
-  <si>
-    <t>Boston Semi Equipment Asia</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>TBD_BSETWN</t>
-  </si>
-  <si>
-    <t>CARDIAC PACEMAKERS INC</t>
-  </si>
-  <si>
-    <t>7000627560</t>
-  </si>
-  <si>
-    <t>7000643410</t>
-  </si>
-  <si>
-    <t>7000667727</t>
-  </si>
-  <si>
-    <t>7000675296</t>
-  </si>
-  <si>
-    <t>7000696372</t>
-  </si>
-  <si>
-    <t>Hana Semiconductor (Ayutthaya) Co., Ltd</t>
-  </si>
-  <si>
-    <t>4910173913</t>
-  </si>
-  <si>
-    <t>TBD_EVALUATION</t>
-  </si>
-  <si>
-    <t>Hana Semiconductor (Ayutthaya) Co., Ltd (HNT)</t>
-  </si>
-  <si>
-    <t>4516351202_HNT</t>
-  </si>
-  <si>
-    <t>4910172298</t>
-  </si>
-  <si>
-    <t>JMC Worldwide Inc.</t>
-  </si>
-  <si>
-    <t>ES072525</t>
-  </si>
-  <si>
-    <t>Lingsen Precision Industries Ltd.</t>
-  </si>
-  <si>
-    <t>4516260169</t>
-  </si>
-  <si>
-    <t>4516446856</t>
-  </si>
-  <si>
-    <t>LPI-2507174</t>
-  </si>
-  <si>
-    <t>PP25-1057NI</t>
-  </si>
-  <si>
-    <t>PP25-1069NI</t>
-  </si>
-  <si>
-    <t>PP26-1025NI</t>
-  </si>
-  <si>
     <t>3T/PO252272</t>
   </si>
   <si>
@@ -623,10 +632,7 @@
     <t>43156228</t>
   </si>
   <si>
-    <t>4516351202_UTL</t>
-  </si>
-  <si>
-    <t>Last updated: 2026-07-28 09:33:59</t>
+    <t>Last updated: 2026-08-04 14:04:31</t>
   </si>
 </sst>
 </file>
@@ -971,12 +977,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M123"/>
+  <dimension ref="A1:M125"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.5">
@@ -1049,7 +1055,7 @@
         <v>45898</v>
       </c>
       <c r="K3">
-        <v>-333</v>
+        <v>-340</v>
       </c>
       <c r="L3" t="s">
         <v>15</v>
@@ -1066,16 +1072,16 @@
         <v>355</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F4">
         <v>11</v>
       </c>
       <c r="H4">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1084,7 +1090,7 @@
         <v>45898</v>
       </c>
       <c r="K4">
-        <v>-333</v>
+        <v>-340</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -1122,7 +1128,7 @@
         <v>45898</v>
       </c>
       <c r="K5">
-        <v>-333</v>
+        <v>-340</v>
       </c>
       <c r="L5" t="s">
         <v>15</v>
@@ -1139,16 +1145,16 @@
         <v>222</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>10</v>
       </c>
       <c r="H6">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1157,7 +1163,7 @@
         <v>45898</v>
       </c>
       <c r="K6">
-        <v>-333</v>
+        <v>-340</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -1195,7 +1201,7 @@
         <v>46062</v>
       </c>
       <c r="K7">
-        <v>-169</v>
+        <v>-176</v>
       </c>
       <c r="L7" t="s">
         <v>26</v>
@@ -1212,10 +1218,10 @@
         <v>259</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1230,7 +1236,7 @@
         <v>46108</v>
       </c>
       <c r="K8">
-        <v>-123</v>
+        <v>-130</v>
       </c>
       <c r="L8" t="s">
         <v>29</v>
@@ -1253,13 +1259,13 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1268,36 +1274,33 @@
         <v>46139</v>
       </c>
       <c r="K9">
-        <v>-92</v>
+        <v>-99</v>
       </c>
       <c r="L9" t="s">
         <v>33</v>
       </c>
-      <c r="M9" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
         <v>35</v>
-      </c>
-      <c r="B10" t="s">
-        <v>36</v>
       </c>
       <c r="C10">
         <v>666</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F10">
         <v>20</v>
       </c>
       <c r="H10">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1306,13 +1309,13 @@
         <v>46139</v>
       </c>
       <c r="K10">
-        <v>-92</v>
+        <v>-99</v>
       </c>
       <c r="L10" t="s">
         <v>33</v>
       </c>
       <c r="M10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.5">
@@ -1320,22 +1323,22 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1344,21 +1347,21 @@
         <v>46155</v>
       </c>
       <c r="K11">
-        <v>-76</v>
+        <v>-83</v>
       </c>
       <c r="L11" t="s">
+        <v>38</v>
+      </c>
+      <c r="M11" t="s">
         <v>39</v>
-      </c>
-      <c r="M11" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s">
         <v>41</v>
-      </c>
-      <c r="B12" t="s">
-        <v>42</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1382,56 +1385,56 @@
         <v>46188</v>
       </c>
       <c r="K12">
-        <v>-43</v>
+        <v>-50</v>
       </c>
       <c r="L12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
         <v>44</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>46226</v>
+      </c>
+      <c r="K13">
+        <v>-12</v>
+      </c>
+      <c r="L13" t="s">
         <v>45</v>
-      </c>
-      <c r="C13">
-        <v>172</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>171</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>46223</v>
-      </c>
-      <c r="K13">
-        <v>-8</v>
-      </c>
-      <c r="L13" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s">
         <v>47</v>
       </c>
-      <c r="B14" t="s">
-        <v>48</v>
-      </c>
       <c r="C14">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="D14">
         <v>4</v>
@@ -1443,167 +1446,167 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="K14">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="L14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s">
         <v>50</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>46232</v>
+      </c>
+      <c r="K15">
+        <v>-6</v>
+      </c>
+      <c r="L15" t="s">
         <v>51</v>
-      </c>
-      <c r="C15">
-        <v>59</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="H15">
-        <v>56</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15" s="1">
-        <v>46244</v>
-      </c>
-      <c r="K15">
-        <v>13</v>
-      </c>
-      <c r="L15" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>46252</v>
+      </c>
+      <c r="K16">
+        <v>14</v>
+      </c>
+      <c r="L16" t="s">
         <v>53</v>
-      </c>
-      <c r="B16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16" s="1">
-        <v>46232</v>
-      </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17">
+        <v>55</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+      <c r="F17">
+        <v>4</v>
+      </c>
+      <c r="H17">
+        <v>47</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>46247</v>
+      </c>
+      <c r="K17">
+        <v>9</v>
+      </c>
+      <c r="L17" t="s">
         <v>56</v>
-      </c>
-      <c r="B17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17">
-        <v>54</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>2</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="H17">
-        <v>51</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1">
-        <v>46231</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18">
         <v>59</v>
       </c>
-      <c r="B18" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18">
-        <v>34</v>
-      </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18" s="1">
-        <v>46231</v>
+        <v>46244</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" t="s">
         <v>61</v>
-      </c>
-      <c r="B19" t="s">
-        <v>62</v>
       </c>
       <c r="C19">
         <v>50</v>
@@ -1626,13 +1629,13 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C20">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1641,10 +1644,10 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H20">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1652,25 +1655,25 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C21">
+        <v>26</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
         <v>2</v>
       </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
       <c r="F21">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1678,13 +1681,13 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1693,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -1704,25 +1707,25 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C23">
+        <v>17</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
         <v>2</v>
       </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
       <c r="H23">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1730,25 +1733,25 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C24">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="D24">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1756,25 +1759,25 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C25">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1782,25 +1785,25 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C26">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="H26">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1808,28 +1811,25 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C27">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
-      <c r="G27" t="s">
-        <v>77</v>
-      </c>
       <c r="H27">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1837,16 +1837,16 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C28">
-        <v>30</v>
+        <v>172</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1858,7 +1858,7 @@
         <v>77</v>
       </c>
       <c r="H28">
-        <v>30</v>
+        <v>171</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>77</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -1898,10 +1898,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1916,7 +1916,7 @@
         <v>77</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1927,7 +1927,7 @@
         <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1956,7 +1956,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1985,7 +1985,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -2014,7 +2014,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -2043,10 +2043,10 @@
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -2061,7 +2061,7 @@
         <v>77</v>
       </c>
       <c r="H35">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -2072,10 +2072,10 @@
         <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2090,7 +2090,7 @@
         <v>77</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -2101,10 +2101,10 @@
         <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2119,7 +2119,7 @@
         <v>77</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2130,10 +2130,10 @@
         <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>77</v>
       </c>
       <c r="H38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2159,7 +2159,7 @@
         <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -2188,10 +2188,10 @@
         <v>31</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2206,7 +2206,7 @@
         <v>77</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2217,7 +2217,7 @@
         <v>31</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -2246,10 +2246,10 @@
         <v>31</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C42">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2264,7 +2264,7 @@
         <v>77</v>
       </c>
       <c r="H42">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2275,10 +2275,10 @@
         <v>31</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2293,7 +2293,7 @@
         <v>77</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>31</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C44">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2322,7 +2322,7 @@
         <v>77</v>
       </c>
       <c r="H44">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2333,10 +2333,10 @@
         <v>31</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2351,7 +2351,7 @@
         <v>77</v>
       </c>
       <c r="H45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -2362,10 +2362,10 @@
         <v>31</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2380,7 +2380,7 @@
         <v>77</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -2391,10 +2391,10 @@
         <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>77</v>
       </c>
       <c r="H47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -2420,10 +2420,10 @@
         <v>31</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2438,7 +2438,7 @@
         <v>77</v>
       </c>
       <c r="H48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -2449,10 +2449,10 @@
         <v>31</v>
       </c>
       <c r="B49" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C49">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2467,7 +2467,7 @@
         <v>77</v>
       </c>
       <c r="H49">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -2478,10 +2478,10 @@
         <v>31</v>
       </c>
       <c r="B50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2496,7 +2496,7 @@
         <v>77</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2507,10 +2507,10 @@
         <v>31</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2525,7 +2525,7 @@
         <v>77</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -2536,7 +2536,7 @@
         <v>31</v>
       </c>
       <c r="B52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -2565,10 +2565,10 @@
         <v>31</v>
       </c>
       <c r="B53" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2583,7 +2583,7 @@
         <v>77</v>
       </c>
       <c r="H53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2594,10 +2594,10 @@
         <v>31</v>
       </c>
       <c r="B54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2612,7 +2612,7 @@
         <v>77</v>
       </c>
       <c r="H54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -2623,10 +2623,10 @@
         <v>31</v>
       </c>
       <c r="B55" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2641,7 +2641,7 @@
         <v>77</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="B56" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2670,7 +2670,7 @@
         <v>77</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2678,13 +2678,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="B57" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C57">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2699,7 +2699,7 @@
         <v>77</v>
       </c>
       <c r="H57">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -2707,13 +2707,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B58" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C58">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -2728,7 +2728,7 @@
         <v>77</v>
       </c>
       <c r="H58">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2736,13 +2736,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A59" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="B59" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2757,7 +2757,7 @@
         <v>77</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2765,13 +2765,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A60" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="B60" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C60">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2786,7 +2786,7 @@
         <v>77</v>
       </c>
       <c r="H60">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -2794,13 +2794,13 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A61" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B61" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C61">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2815,7 +2815,7 @@
         <v>77</v>
       </c>
       <c r="H61">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -2823,13 +2823,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A62" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B62" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>77</v>
       </c>
       <c r="H62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -2852,13 +2852,13 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A63" t="s">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="B63" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>77</v>
       </c>
       <c r="H63">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -2881,13 +2881,13 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A64" t="s">
-        <v>118</v>
+        <v>49</v>
       </c>
       <c r="B64" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2902,7 +2902,7 @@
         <v>77</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -2910,13 +2910,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A65" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B65" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2931,7 +2931,7 @@
         <v>77</v>
       </c>
       <c r="H65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A66" t="s">
+        <v>119</v>
+      </c>
+      <c r="B66" t="s">
         <v>120</v>
-      </c>
-      <c r="B66" t="s">
-        <v>122</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -2968,13 +2968,13 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A67" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B67" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C67">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>77</v>
       </c>
       <c r="H67">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -2997,13 +2997,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A68" t="s">
+        <v>121</v>
+      </c>
+      <c r="B68" t="s">
         <v>123</v>
       </c>
-      <c r="B68" t="s">
-        <v>125</v>
-      </c>
       <c r="C68">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -3018,7 +3018,7 @@
         <v>77</v>
       </c>
       <c r="H68">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3026,13 +3026,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B69" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -3047,7 +3047,7 @@
         <v>77</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -3055,13 +3055,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A70" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B70" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -3076,7 +3076,7 @@
         <v>77</v>
       </c>
       <c r="H70">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -3084,13 +3084,13 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B71" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C71">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>77</v>
       </c>
       <c r="H71">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -3113,13 +3113,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A72" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B72" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C72">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3134,7 +3134,7 @@
         <v>77</v>
       </c>
       <c r="H72">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3142,13 +3142,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A73" t="s">
+        <v>124</v>
+      </c>
+      <c r="B73" t="s">
         <v>129</v>
       </c>
-      <c r="B73" t="s">
-        <v>131</v>
-      </c>
       <c r="C73">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>77</v>
       </c>
       <c r="H73">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3171,13 +3171,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A74" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B74" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C74">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3192,7 +3192,7 @@
         <v>77</v>
       </c>
       <c r="H74">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -3200,13 +3200,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A75" t="s">
+        <v>130</v>
+      </c>
+      <c r="B75" t="s">
         <v>132</v>
       </c>
-      <c r="B75" t="s">
-        <v>134</v>
-      </c>
       <c r="C75">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -3221,7 +3221,7 @@
         <v>77</v>
       </c>
       <c r="H75">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -3229,13 +3229,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A76" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B76" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C76">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3250,7 +3250,7 @@
         <v>77</v>
       </c>
       <c r="H76">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -3258,13 +3258,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A77" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B77" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C77">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3279,7 +3279,7 @@
         <v>77</v>
       </c>
       <c r="H77">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3287,13 +3287,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A78" t="s">
+        <v>136</v>
+      </c>
+      <c r="B78" t="s">
         <v>137</v>
       </c>
-      <c r="B78" t="s">
-        <v>139</v>
-      </c>
       <c r="C78">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3308,7 +3308,7 @@
         <v>77</v>
       </c>
       <c r="H78">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3316,13 +3316,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A79" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B79" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3337,7 +3337,7 @@
         <v>77</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -3345,13 +3345,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A80" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="B80" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C80">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3366,7 +3366,7 @@
         <v>77</v>
       </c>
       <c r="H80">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -3374,10 +3374,10 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A81" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="B81" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -3403,13 +3403,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A82" t="s">
-        <v>65</v>
+        <v>142</v>
       </c>
       <c r="B82" t="s">
         <v>143</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3424,7 +3424,7 @@
         <v>77</v>
       </c>
       <c r="H82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="B83" t="s">
         <v>144</v>
@@ -3461,13 +3461,13 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A84" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="B84" t="s">
         <v>145</v>
       </c>
       <c r="C84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3482,7 +3482,7 @@
         <v>77</v>
       </c>
       <c r="H84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -3490,13 +3490,13 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A85" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="B85" t="s">
         <v>146</v>
       </c>
       <c r="C85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3511,7 +3511,7 @@
         <v>77</v>
       </c>
       <c r="H85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -3519,13 +3519,13 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A86" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B86" t="s">
         <v>147</v>
       </c>
       <c r="C86">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -3540,7 +3540,7 @@
         <v>77</v>
       </c>
       <c r="H86">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -3548,7 +3548,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A87" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B87" t="s">
         <v>148</v>
@@ -3577,13 +3577,13 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A88" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B88" t="s">
         <v>149</v>
       </c>
       <c r="C88">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         <v>77</v>
       </c>
       <c r="H88">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -3606,13 +3606,13 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A89" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B89" t="s">
         <v>150</v>
       </c>
       <c r="C89">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3627,7 +3627,7 @@
         <v>77</v>
       </c>
       <c r="H89">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -3635,13 +3635,13 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A90" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B90" t="s">
         <v>151</v>
       </c>
       <c r="C90">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3656,7 +3656,7 @@
         <v>77</v>
       </c>
       <c r="H90">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -3664,13 +3664,13 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A91" t="s">
+        <v>57</v>
+      </c>
+      <c r="B91" t="s">
         <v>152</v>
       </c>
-      <c r="B91" t="s">
-        <v>153</v>
-      </c>
       <c r="C91">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3685,7 +3685,7 @@
         <v>77</v>
       </c>
       <c r="H91">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -3693,13 +3693,13 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A92" t="s">
-        <v>152</v>
+        <v>57</v>
       </c>
       <c r="B92" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C92">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3714,7 +3714,7 @@
         <v>77</v>
       </c>
       <c r="H92">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -3722,13 +3722,13 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A93" t="s">
-        <v>155</v>
+        <v>57</v>
       </c>
       <c r="B93" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C93">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -3743,7 +3743,7 @@
         <v>77</v>
       </c>
       <c r="H93">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -3751,13 +3751,13 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A94" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B94" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C94">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>77</v>
       </c>
       <c r="H94">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -3780,10 +3780,10 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A95" t="s">
+        <v>155</v>
+      </c>
+      <c r="B95" t="s">
         <v>157</v>
-      </c>
-      <c r="B95" t="s">
-        <v>159</v>
       </c>
       <c r="C95">
         <v>5</v>
@@ -3809,13 +3809,13 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A96" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B96" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C96">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -3830,7 +3830,7 @@
         <v>77</v>
       </c>
       <c r="H96">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -3841,10 +3841,10 @@
         <v>160</v>
       </c>
       <c r="B97" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -3859,7 +3859,7 @@
         <v>77</v>
       </c>
       <c r="H97">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -3870,10 +3870,10 @@
         <v>160</v>
       </c>
       <c r="B98" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3888,7 +3888,7 @@
         <v>77</v>
       </c>
       <c r="H98">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -3896,13 +3896,13 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A99" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B99" t="s">
         <v>164</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -3917,7 +3917,7 @@
         <v>77</v>
       </c>
       <c r="H99">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -3925,7 +3925,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A100" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B100" t="s">
         <v>165</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A101" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B101" t="s">
         <v>166</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A102" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B102" t="s">
         <v>167</v>
@@ -4012,7 +4012,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A103" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B103" t="s">
         <v>168</v>
@@ -4041,13 +4041,13 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A104" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B104" t="s">
         <v>169</v>
       </c>
       <c r="C104">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -4062,7 +4062,7 @@
         <v>77</v>
       </c>
       <c r="H104">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A105" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B105" t="s">
         <v>170</v>
@@ -4099,13 +4099,13 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A106" t="s">
+        <v>163</v>
+      </c>
+      <c r="B106" t="s">
         <v>171</v>
       </c>
-      <c r="B106" t="s">
-        <v>172</v>
-      </c>
       <c r="C106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -4120,7 +4120,7 @@
         <v>77</v>
       </c>
       <c r="H106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -4128,13 +4128,13 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A107" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B107" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C107">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -4149,7 +4149,7 @@
         <v>77</v>
       </c>
       <c r="H107">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I107">
         <v>0</v>
@@ -4157,10 +4157,10 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A108" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="B108" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C108">
         <v>1</v>
@@ -4186,13 +4186,13 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A109" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B109" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -4207,7 +4207,7 @@
         <v>77</v>
       </c>
       <c r="H109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -4215,13 +4215,13 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A110" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B110" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C110">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -4236,7 +4236,7 @@
         <v>77</v>
       </c>
       <c r="H110">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I110">
         <v>0</v>
@@ -4244,10 +4244,10 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A111" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B111" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C111">
         <v>1</v>
@@ -4273,13 +4273,13 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A112" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B112" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -4294,7 +4294,7 @@
         <v>77</v>
       </c>
       <c r="H112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -4302,13 +4302,13 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A113" t="s">
+        <v>181</v>
+      </c>
+      <c r="B113" t="s">
         <v>182</v>
       </c>
-      <c r="B113" t="s">
-        <v>184</v>
-      </c>
       <c r="C113">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D113">
         <v>0</v>
@@ -4323,7 +4323,7 @@
         <v>77</v>
       </c>
       <c r="H113">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I113">
         <v>0</v>
@@ -4331,13 +4331,13 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A114" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B114" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C114">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D114">
         <v>0</v>
@@ -4352,7 +4352,7 @@
         <v>77</v>
       </c>
       <c r="H114">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I114">
         <v>0</v>
@@ -4360,10 +4360,10 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A115" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B115" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C115">
         <v>2</v>
@@ -4389,13 +4389,13 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A116" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B116" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C116">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -4410,7 +4410,7 @@
         <v>77</v>
       </c>
       <c r="H116">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -4418,13 +4418,13 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A117" t="s">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="B117" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C117">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -4439,7 +4439,7 @@
         <v>77</v>
       </c>
       <c r="H117">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I117">
         <v>0</v>
@@ -4447,13 +4447,13 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A118" t="s">
-        <v>74</v>
+        <v>190</v>
       </c>
       <c r="B118" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C118">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -4468,7 +4468,7 @@
         <v>77</v>
       </c>
       <c r="H118">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I118">
         <v>0</v>
@@ -4476,13 +4476,13 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A119" t="s">
+        <v>192</v>
+      </c>
+      <c r="B119" t="s">
         <v>193</v>
       </c>
-      <c r="B119" t="s">
-        <v>194</v>
-      </c>
       <c r="C119">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -4497,7 +4497,7 @@
         <v>77</v>
       </c>
       <c r="H119">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -4505,13 +4505,13 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A120" t="s">
-        <v>195</v>
+        <v>63</v>
       </c>
       <c r="B120" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -4526,7 +4526,7 @@
         <v>77</v>
       </c>
       <c r="H120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I120">
         <v>0</v>
@@ -4534,13 +4534,13 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A121" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B121" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -4555,7 +4555,7 @@
         <v>77</v>
       </c>
       <c r="H121">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I121">
         <v>0</v>
@@ -4563,13 +4563,13 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A122" t="s">
-        <v>47</v>
+        <v>196</v>
       </c>
       <c r="B122" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C122">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -4584,7 +4584,7 @@
         <v>77</v>
       </c>
       <c r="H122">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="I122">
         <v>0</v>
@@ -4592,13 +4592,13 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.5">
       <c r="A123" t="s">
-        <v>47</v>
+        <v>198</v>
       </c>
       <c r="B123" t="s">
         <v>199</v>
       </c>
       <c r="C123">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -4613,9 +4613,67 @@
         <v>77</v>
       </c>
       <c r="H123">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A124" t="s">
+        <v>43</v>
+      </c>
+      <c r="B124" t="s">
+        <v>200</v>
+      </c>
+      <c r="C124">
+        <v>1</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124" t="s">
+        <v>77</v>
+      </c>
+      <c r="H124">
+        <v>1</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.5">
+      <c r="A125" t="s">
+        <v>43</v>
+      </c>
+      <c r="B125" t="s">
+        <v>201</v>
+      </c>
+      <c r="C125">
+        <v>1</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <v>0</v>
+      </c>
+      <c r="G125" t="s">
+        <v>77</v>
+      </c>
+      <c r="H125">
+        <v>1</v>
+      </c>
+      <c r="I125">
         <v>0</v>
       </c>
     </row>
